--- a/doc/bug-report.xlsx
+++ b/doc/bug-report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asher\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AFF301B-233C-42EB-9D60-3744CE5CCD76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0939DFFC-33A1-47D0-9C3A-03D6DF902872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27675" yWindow="-1170" windowWidth="24075" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Tracker" sheetId="2" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="98">
   <si>
     <t>Matt</t>
   </si>
@@ -390,6 +390,18 @@
   </si>
   <si>
     <t>character should stop moving when in dialogue</t>
+  </si>
+  <si>
+    <t>X not scrapping item</t>
+  </si>
+  <si>
+    <t>1) launch game
+2) get to an item
+3) press X
+4) observe that item is not being scrapped</t>
+  </si>
+  <si>
+    <t>item should be scrapped and disspear</t>
   </si>
 </sst>
 </file>
@@ -712,12 +724,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L1000"/>
-  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="19.90625" customWidth="1"/>
+    <col min="1" max="1" width="19.85546875" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="26.90625" customWidth="1"/>
-    <col min="8" max="8" width="15.08984375" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" customWidth="1"/>
+    <col min="8" max="8" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -787,7 +799,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.75" customHeight="1">
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
@@ -816,7 +828,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="15.75" customHeight="1">
+    <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
         <v>25</v>
       </c>
@@ -845,7 +857,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="15.75" customHeight="1">
+    <row r="5" spans="1:12">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -874,7 +886,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="15.75" customHeight="1">
+    <row r="6" spans="1:12">
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
@@ -903,7 +915,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="15.75" customHeight="1">
+    <row r="7" spans="1:12">
       <c r="A7" s="1" t="s">
         <v>36</v>
       </c>
@@ -932,7 +944,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="15.75" customHeight="1">
+    <row r="8" spans="1:12">
       <c r="A8" s="1" t="s">
         <v>40</v>
       </c>
@@ -961,7 +973,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="15.75" customHeight="1">
+    <row r="9" spans="1:12">
       <c r="A9" s="1" t="s">
         <v>43</v>
       </c>
@@ -990,7 +1002,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="15.75" customHeight="1">
+    <row r="10" spans="1:12">
       <c r="A10" s="1" t="s">
         <v>47</v>
       </c>
@@ -1019,7 +1031,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15.75" customHeight="1">
+    <row r="11" spans="1:12">
       <c r="A11" s="1" t="s">
         <v>50</v>
       </c>
@@ -1048,7 +1060,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="15.75" customHeight="1">
+    <row r="12" spans="1:12">
       <c r="A12" s="1" t="s">
         <v>53</v>
       </c>
@@ -1077,7 +1089,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="15.75" customHeight="1">
+    <row r="13" spans="1:12">
       <c r="A13" s="1" t="s">
         <v>56</v>
       </c>
@@ -1109,7 +1121,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="15.75" customHeight="1">
+    <row r="14" spans="1:12">
       <c r="A14" s="1" t="s">
         <v>61</v>
       </c>
@@ -1138,7 +1150,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="15.75" customHeight="1">
+    <row r="15" spans="1:12">
       <c r="A15" s="1" t="s">
         <v>64</v>
       </c>
@@ -1167,7 +1179,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="15.75" customHeight="1">
+    <row r="16" spans="1:12">
       <c r="A16" s="1" t="s">
         <v>67</v>
       </c>
@@ -1196,7 +1208,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="15.75" customHeight="1">
+    <row r="17" spans="1:11">
       <c r="A17" s="1" t="s">
         <v>71</v>
       </c>
@@ -1225,7 +1237,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15.75" customHeight="1">
+    <row r="18" spans="1:11">
       <c r="A18" s="1" t="s">
         <v>74</v>
       </c>
@@ -1254,7 +1266,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15.75" customHeight="1">
+    <row r="19" spans="1:11">
       <c r="A19" s="1" t="s">
         <v>77</v>
       </c>
@@ -1283,7 +1295,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15.75" customHeight="1">
+    <row r="20" spans="1:11">
       <c r="A20" s="1" t="s">
         <v>80</v>
       </c>
@@ -1312,7 +1324,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="37.5">
+    <row r="21" spans="1:11">
       <c r="A21" s="1" t="s">
         <v>83</v>
       </c>
@@ -1341,7 +1353,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="12.5">
+    <row r="22" spans="1:11">
       <c r="A22" s="1" t="s">
         <v>86</v>
       </c>
@@ -1370,7 +1382,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="25">
+    <row r="23" spans="1:11">
       <c r="A23" s="1" t="s">
         <v>89</v>
       </c>
@@ -1399,7 +1411,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="100">
+    <row r="24" spans="1:11">
       <c r="A24" s="1" t="s">
         <v>92</v>
       </c>
@@ -1425,4255 +1437,4279 @@
         <v>1</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" ht="12.5">
-      <c r="A25" s="1"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-    </row>
-    <row r="26" spans="1:11" ht="12.5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" s="9">
+        <v>45615</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="1"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
     </row>
-    <row r="27" spans="1:11" ht="12.5">
+    <row r="27" spans="1:11">
       <c r="A27" s="1"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
     </row>
-    <row r="28" spans="1:11" ht="12.5">
+    <row r="28" spans="1:11">
       <c r="A28" s="1"/>
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="1:11" ht="12.5">
+    <row r="29" spans="1:11">
       <c r="A29" s="1"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
     </row>
-    <row r="30" spans="1:11" ht="12.5">
+    <row r="30" spans="1:11">
       <c r="A30" s="1"/>
       <c r="G30" s="2"/>
       <c r="H30" s="2"/>
     </row>
-    <row r="31" spans="1:11" ht="12.5">
+    <row r="31" spans="1:11">
       <c r="A31" s="1"/>
       <c r="G31" s="2"/>
       <c r="H31" s="2"/>
     </row>
-    <row r="32" spans="1:11" ht="12.5">
+    <row r="32" spans="1:11">
       <c r="A32" s="1"/>
       <c r="G32" s="2"/>
       <c r="H32" s="2"/>
     </row>
-    <row r="33" spans="1:8" ht="12.5">
+    <row r="33" spans="1:8">
       <c r="A33" s="1"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
     </row>
-    <row r="34" spans="1:8" ht="12.5">
+    <row r="34" spans="1:8">
       <c r="A34" s="1"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
     </row>
-    <row r="35" spans="1:8" ht="12.5">
+    <row r="35" spans="1:8">
       <c r="A35" s="1"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
     </row>
-    <row r="36" spans="1:8" ht="12.5">
+    <row r="36" spans="1:8">
       <c r="A36" s="1"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
     </row>
-    <row r="37" spans="1:8" ht="12.5">
+    <row r="37" spans="1:8">
       <c r="A37" s="1"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
     </row>
-    <row r="38" spans="1:8" ht="12.5">
+    <row r="38" spans="1:8">
       <c r="A38" s="1"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:8" ht="12.5">
+    <row r="39" spans="1:8">
       <c r="A39" s="1"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
     </row>
-    <row r="40" spans="1:8" ht="12.5">
+    <row r="40" spans="1:8">
       <c r="A40" s="1"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
     </row>
-    <row r="41" spans="1:8" ht="12.5">
+    <row r="41" spans="1:8">
       <c r="A41" s="1"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
     </row>
-    <row r="42" spans="1:8" ht="12.5">
+    <row r="42" spans="1:8">
       <c r="A42" s="1"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
     </row>
-    <row r="43" spans="1:8" ht="12.5">
+    <row r="43" spans="1:8">
       <c r="A43" s="1"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
     </row>
-    <row r="44" spans="1:8" ht="12.5">
+    <row r="44" spans="1:8">
       <c r="A44" s="1"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
     </row>
-    <row r="45" spans="1:8" ht="12.5">
+    <row r="45" spans="1:8">
       <c r="A45" s="1"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
     </row>
-    <row r="46" spans="1:8" ht="12.5">
+    <row r="46" spans="1:8">
       <c r="A46" s="1"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
     </row>
-    <row r="47" spans="1:8" ht="12.5">
+    <row r="47" spans="1:8">
       <c r="A47" s="1"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
     </row>
-    <row r="48" spans="1:8" ht="12.5">
+    <row r="48" spans="1:8">
       <c r="A48" s="1"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
     </row>
-    <row r="49" spans="1:8" ht="12.5">
+    <row r="49" spans="1:8">
       <c r="A49" s="1"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
     </row>
-    <row r="50" spans="1:8" ht="12.5">
+    <row r="50" spans="1:8">
       <c r="A50" s="1"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
     </row>
-    <row r="51" spans="1:8" ht="12.5">
+    <row r="51" spans="1:8">
       <c r="A51" s="1"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
     </row>
-    <row r="52" spans="1:8" ht="12.5">
+    <row r="52" spans="1:8">
       <c r="A52" s="1"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
     </row>
-    <row r="53" spans="1:8" ht="12.5">
+    <row r="53" spans="1:8">
       <c r="A53" s="1"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
     </row>
-    <row r="54" spans="1:8" ht="12.5">
+    <row r="54" spans="1:8">
       <c r="A54" s="1"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
     </row>
-    <row r="55" spans="1:8" ht="12.5">
+    <row r="55" spans="1:8">
       <c r="A55" s="1"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
     </row>
-    <row r="56" spans="1:8" ht="12.5">
+    <row r="56" spans="1:8">
       <c r="A56" s="1"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="1:8" ht="12.5">
+    <row r="57" spans="1:8">
       <c r="A57" s="1"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
     </row>
-    <row r="58" spans="1:8" ht="12.5">
+    <row r="58" spans="1:8">
       <c r="A58" s="1"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
     </row>
-    <row r="59" spans="1:8" ht="12.5">
+    <row r="59" spans="1:8">
       <c r="A59" s="1"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
     </row>
-    <row r="60" spans="1:8" ht="12.5">
+    <row r="60" spans="1:8">
       <c r="A60" s="1"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
     </row>
-    <row r="61" spans="1:8" ht="12.5">
+    <row r="61" spans="1:8">
       <c r="A61" s="1"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
     </row>
-    <row r="62" spans="1:8" ht="12.5">
+    <row r="62" spans="1:8">
       <c r="A62" s="1"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
     </row>
-    <row r="63" spans="1:8" ht="12.5">
+    <row r="63" spans="1:8">
       <c r="A63" s="1"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
     </row>
-    <row r="64" spans="1:8" ht="12.5">
+    <row r="64" spans="1:8">
       <c r="A64" s="1"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
     </row>
-    <row r="65" spans="1:8" ht="12.5">
+    <row r="65" spans="1:8">
       <c r="A65" s="1"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
     </row>
-    <row r="66" spans="1:8" ht="12.5">
+    <row r="66" spans="1:8">
       <c r="A66" s="1"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
     </row>
-    <row r="67" spans="1:8" ht="12.5">
+    <row r="67" spans="1:8">
       <c r="A67" s="1"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
     </row>
-    <row r="68" spans="1:8" ht="12.5">
+    <row r="68" spans="1:8">
       <c r="A68" s="1"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
     </row>
-    <row r="69" spans="1:8" ht="12.5">
+    <row r="69" spans="1:8">
       <c r="A69" s="1"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="1:8" ht="12.5">
+    <row r="70" spans="1:8">
       <c r="A70" s="1"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
     </row>
-    <row r="71" spans="1:8" ht="12.5">
+    <row r="71" spans="1:8">
       <c r="A71" s="1"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
     </row>
-    <row r="72" spans="1:8" ht="12.5">
+    <row r="72" spans="1:8">
       <c r="A72" s="1"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
     </row>
-    <row r="73" spans="1:8" ht="12.5">
+    <row r="73" spans="1:8">
       <c r="A73" s="1"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
     </row>
-    <row r="74" spans="1:8" ht="12.5">
+    <row r="74" spans="1:8">
       <c r="A74" s="1"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
     </row>
-    <row r="75" spans="1:8" ht="12.5">
+    <row r="75" spans="1:8">
       <c r="A75" s="1"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
     </row>
-    <row r="76" spans="1:8" ht="12.5">
+    <row r="76" spans="1:8">
       <c r="A76" s="1"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
     </row>
-    <row r="77" spans="1:8" ht="12.5">
+    <row r="77" spans="1:8">
       <c r="A77" s="1"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
     </row>
-    <row r="78" spans="1:8" ht="12.5">
+    <row r="78" spans="1:8">
       <c r="A78" s="1"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
     </row>
-    <row r="79" spans="1:8" ht="12.5">
+    <row r="79" spans="1:8">
       <c r="A79" s="1"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
     </row>
-    <row r="80" spans="1:8" ht="12.5">
+    <row r="80" spans="1:8">
       <c r="A80" s="1"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
     </row>
-    <row r="81" spans="1:8" ht="12.5">
+    <row r="81" spans="1:8">
       <c r="A81" s="1"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
     </row>
-    <row r="82" spans="1:8" ht="12.5">
+    <row r="82" spans="1:8">
       <c r="A82" s="1"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
     </row>
-    <row r="83" spans="1:8" ht="12.5">
+    <row r="83" spans="1:8">
       <c r="A83" s="1"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
     </row>
-    <row r="84" spans="1:8" ht="12.5">
+    <row r="84" spans="1:8">
       <c r="A84" s="1"/>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
     </row>
-    <row r="85" spans="1:8" ht="12.5">
+    <row r="85" spans="1:8">
       <c r="A85" s="1"/>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
     </row>
-    <row r="86" spans="1:8" ht="12.5">
+    <row r="86" spans="1:8">
       <c r="A86" s="1"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
     </row>
-    <row r="87" spans="1:8" ht="12.5">
+    <row r="87" spans="1:8">
       <c r="A87" s="1"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
     </row>
-    <row r="88" spans="1:8" ht="12.5">
+    <row r="88" spans="1:8">
       <c r="A88" s="1"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
     </row>
-    <row r="89" spans="1:8" ht="12.5">
+    <row r="89" spans="1:8">
       <c r="A89" s="1"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
     </row>
-    <row r="90" spans="1:8" ht="12.5">
+    <row r="90" spans="1:8">
       <c r="A90" s="1"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
     </row>
-    <row r="91" spans="1:8" ht="12.5">
+    <row r="91" spans="1:8">
       <c r="A91" s="1"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
     </row>
-    <row r="92" spans="1:8" ht="12.5">
+    <row r="92" spans="1:8">
       <c r="A92" s="1"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
     </row>
-    <row r="93" spans="1:8" ht="12.5">
+    <row r="93" spans="1:8">
       <c r="A93" s="1"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
     </row>
-    <row r="94" spans="1:8" ht="12.5">
+    <row r="94" spans="1:8">
       <c r="A94" s="1"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
     </row>
-    <row r="95" spans="1:8" ht="12.5">
+    <row r="95" spans="1:8">
       <c r="A95" s="1"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
     </row>
-    <row r="96" spans="1:8" ht="12.5">
+    <row r="96" spans="1:8">
       <c r="A96" s="1"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
     </row>
-    <row r="97" spans="1:8" ht="12.5">
+    <row r="97" spans="1:8">
       <c r="A97" s="1"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
     </row>
-    <row r="98" spans="1:8" ht="12.5">
+    <row r="98" spans="1:8">
       <c r="A98" s="1"/>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
     </row>
-    <row r="99" spans="1:8" ht="12.5">
+    <row r="99" spans="1:8">
       <c r="A99" s="1"/>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
     </row>
-    <row r="100" spans="1:8" ht="12.5">
+    <row r="100" spans="1:8">
       <c r="A100" s="1"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
     </row>
-    <row r="101" spans="1:8" ht="12.5">
+    <row r="101" spans="1:8">
       <c r="A101" s="1"/>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
     </row>
-    <row r="102" spans="1:8" ht="12.5">
+    <row r="102" spans="1:8">
       <c r="A102" s="1"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
     </row>
-    <row r="103" spans="1:8" ht="12.5">
+    <row r="103" spans="1:8">
       <c r="A103" s="1"/>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
     </row>
-    <row r="104" spans="1:8" ht="12.5">
+    <row r="104" spans="1:8">
       <c r="A104" s="1"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
     </row>
-    <row r="105" spans="1:8" ht="12.5">
+    <row r="105" spans="1:8">
       <c r="A105" s="1"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
     </row>
-    <row r="106" spans="1:8" ht="12.5">
+    <row r="106" spans="1:8">
       <c r="A106" s="1"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
     </row>
-    <row r="107" spans="1:8" ht="12.5">
+    <row r="107" spans="1:8">
       <c r="A107" s="1"/>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
     </row>
-    <row r="108" spans="1:8" ht="12.5">
+    <row r="108" spans="1:8">
       <c r="A108" s="1"/>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
     </row>
-    <row r="109" spans="1:8" ht="12.5">
+    <row r="109" spans="1:8">
       <c r="A109" s="1"/>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
     </row>
-    <row r="110" spans="1:8" ht="12.5">
+    <row r="110" spans="1:8">
       <c r="A110" s="1"/>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
     </row>
-    <row r="111" spans="1:8" ht="12.5">
+    <row r="111" spans="1:8">
       <c r="A111" s="1"/>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
     </row>
-    <row r="112" spans="1:8" ht="12.5">
+    <row r="112" spans="1:8">
       <c r="A112" s="1"/>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
     </row>
-    <row r="113" spans="1:8" ht="12.5">
+    <row r="113" spans="1:8">
       <c r="A113" s="1"/>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
     </row>
-    <row r="114" spans="1:8" ht="12.5">
+    <row r="114" spans="1:8">
       <c r="A114" s="1"/>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
     </row>
-    <row r="115" spans="1:8" ht="12.5">
+    <row r="115" spans="1:8">
       <c r="A115" s="1"/>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
     </row>
-    <row r="116" spans="1:8" ht="12.5">
+    <row r="116" spans="1:8">
       <c r="A116" s="1"/>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
     </row>
-    <row r="117" spans="1:8" ht="12.5">
+    <row r="117" spans="1:8">
       <c r="A117" s="1"/>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
     </row>
-    <row r="118" spans="1:8" ht="12.5">
+    <row r="118" spans="1:8">
       <c r="A118" s="1"/>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
     </row>
-    <row r="119" spans="1:8" ht="12.5">
+    <row r="119" spans="1:8">
       <c r="A119" s="1"/>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
     </row>
-    <row r="120" spans="1:8" ht="12.5">
+    <row r="120" spans="1:8">
       <c r="A120" s="1"/>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
     </row>
-    <row r="121" spans="1:8" ht="12.5">
+    <row r="121" spans="1:8">
       <c r="A121" s="1"/>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
     </row>
-    <row r="122" spans="1:8" ht="12.5">
+    <row r="122" spans="1:8">
       <c r="A122" s="1"/>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
     </row>
-    <row r="123" spans="1:8" ht="12.5">
+    <row r="123" spans="1:8">
       <c r="A123" s="1"/>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
     </row>
-    <row r="124" spans="1:8" ht="12.5">
+    <row r="124" spans="1:8">
       <c r="A124" s="1"/>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
     </row>
-    <row r="125" spans="1:8" ht="12.5">
+    <row r="125" spans="1:8">
       <c r="A125" s="1"/>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
     </row>
-    <row r="126" spans="1:8" ht="12.5">
+    <row r="126" spans="1:8">
       <c r="A126" s="1"/>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
     </row>
-    <row r="127" spans="1:8" ht="12.5">
+    <row r="127" spans="1:8">
       <c r="A127" s="1"/>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
     </row>
-    <row r="128" spans="1:8" ht="12.5">
+    <row r="128" spans="1:8">
       <c r="A128" s="1"/>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
     </row>
-    <row r="129" spans="1:8" ht="12.5">
+    <row r="129" spans="1:8">
       <c r="A129" s="1"/>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
     </row>
-    <row r="130" spans="1:8" ht="12.5">
+    <row r="130" spans="1:8">
       <c r="A130" s="1"/>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
     </row>
-    <row r="131" spans="1:8" ht="12.5">
+    <row r="131" spans="1:8">
       <c r="A131" s="1"/>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
     </row>
-    <row r="132" spans="1:8" ht="12.5">
+    <row r="132" spans="1:8">
       <c r="A132" s="1"/>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
     </row>
-    <row r="133" spans="1:8" ht="12.5">
+    <row r="133" spans="1:8">
       <c r="A133" s="1"/>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
     </row>
-    <row r="134" spans="1:8" ht="12.5">
+    <row r="134" spans="1:8">
       <c r="A134" s="1"/>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
     </row>
-    <row r="135" spans="1:8" ht="12.5">
+    <row r="135" spans="1:8">
       <c r="A135" s="1"/>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
     </row>
-    <row r="136" spans="1:8" ht="12.5">
+    <row r="136" spans="1:8">
       <c r="A136" s="1"/>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
     </row>
-    <row r="137" spans="1:8" ht="12.5">
+    <row r="137" spans="1:8">
       <c r="A137" s="1"/>
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
     </row>
-    <row r="138" spans="1:8" ht="12.5">
+    <row r="138" spans="1:8">
       <c r="A138" s="1"/>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
     </row>
-    <row r="139" spans="1:8" ht="12.5">
+    <row r="139" spans="1:8">
       <c r="A139" s="1"/>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
     </row>
-    <row r="140" spans="1:8" ht="12.5">
+    <row r="140" spans="1:8">
       <c r="A140" s="1"/>
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
     </row>
-    <row r="141" spans="1:8" ht="12.5">
+    <row r="141" spans="1:8">
       <c r="A141" s="1"/>
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
     </row>
-    <row r="142" spans="1:8" ht="12.5">
+    <row r="142" spans="1:8">
       <c r="A142" s="1"/>
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
     </row>
-    <row r="143" spans="1:8" ht="12.5">
+    <row r="143" spans="1:8">
       <c r="A143" s="1"/>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
     </row>
-    <row r="144" spans="1:8" ht="12.5">
+    <row r="144" spans="1:8">
       <c r="A144" s="1"/>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
     </row>
-    <row r="145" spans="1:8" ht="12.5">
+    <row r="145" spans="1:8">
       <c r="A145" s="1"/>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
     </row>
-    <row r="146" spans="1:8" ht="12.5">
+    <row r="146" spans="1:8">
       <c r="A146" s="1"/>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
     </row>
-    <row r="147" spans="1:8" ht="12.5">
+    <row r="147" spans="1:8">
       <c r="A147" s="1"/>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
     </row>
-    <row r="148" spans="1:8" ht="12.5">
+    <row r="148" spans="1:8">
       <c r="A148" s="1"/>
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
     </row>
-    <row r="149" spans="1:8" ht="12.5">
+    <row r="149" spans="1:8">
       <c r="A149" s="1"/>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
     </row>
-    <row r="150" spans="1:8" ht="12.5">
+    <row r="150" spans="1:8">
       <c r="A150" s="1"/>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
     </row>
-    <row r="151" spans="1:8" ht="12.5">
+    <row r="151" spans="1:8">
       <c r="A151" s="1"/>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
     </row>
-    <row r="152" spans="1:8" ht="12.5">
+    <row r="152" spans="1:8">
       <c r="A152" s="1"/>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
     </row>
-    <row r="153" spans="1:8" ht="12.5">
+    <row r="153" spans="1:8">
       <c r="A153" s="1"/>
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
     </row>
-    <row r="154" spans="1:8" ht="12.5">
+    <row r="154" spans="1:8">
       <c r="A154" s="1"/>
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
     </row>
-    <row r="155" spans="1:8" ht="12.5">
+    <row r="155" spans="1:8">
       <c r="A155" s="1"/>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
     </row>
-    <row r="156" spans="1:8" ht="12.5">
+    <row r="156" spans="1:8">
       <c r="A156" s="1"/>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
     </row>
-    <row r="157" spans="1:8" ht="12.5">
+    <row r="157" spans="1:8">
       <c r="A157" s="1"/>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
     </row>
-    <row r="158" spans="1:8" ht="12.5">
+    <row r="158" spans="1:8">
       <c r="A158" s="1"/>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
     </row>
-    <row r="159" spans="1:8" ht="12.5">
+    <row r="159" spans="1:8">
       <c r="A159" s="1"/>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
     </row>
-    <row r="160" spans="1:8" ht="12.5">
+    <row r="160" spans="1:8">
       <c r="A160" s="1"/>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
     </row>
-    <row r="161" spans="1:8" ht="12.5">
+    <row r="161" spans="1:8">
       <c r="A161" s="1"/>
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
     </row>
-    <row r="162" spans="1:8" ht="12.5">
+    <row r="162" spans="1:8">
       <c r="A162" s="1"/>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
     </row>
-    <row r="163" spans="1:8" ht="12.5">
+    <row r="163" spans="1:8">
       <c r="A163" s="1"/>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
     </row>
-    <row r="164" spans="1:8" ht="12.5">
+    <row r="164" spans="1:8">
       <c r="A164" s="1"/>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
     </row>
-    <row r="165" spans="1:8" ht="12.5">
+    <row r="165" spans="1:8">
       <c r="A165" s="1"/>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
     </row>
-    <row r="166" spans="1:8" ht="12.5">
+    <row r="166" spans="1:8">
       <c r="A166" s="1"/>
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
     </row>
-    <row r="167" spans="1:8" ht="12.5">
+    <row r="167" spans="1:8">
       <c r="A167" s="1"/>
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
     </row>
-    <row r="168" spans="1:8" ht="12.5">
+    <row r="168" spans="1:8">
       <c r="A168" s="1"/>
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
     </row>
-    <row r="169" spans="1:8" ht="12.5">
+    <row r="169" spans="1:8">
       <c r="A169" s="1"/>
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
     </row>
-    <row r="170" spans="1:8" ht="12.5">
+    <row r="170" spans="1:8">
       <c r="A170" s="1"/>
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
     </row>
-    <row r="171" spans="1:8" ht="12.5">
+    <row r="171" spans="1:8">
       <c r="A171" s="1"/>
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
     </row>
-    <row r="172" spans="1:8" ht="12.5">
+    <row r="172" spans="1:8">
       <c r="A172" s="1"/>
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
     </row>
-    <row r="173" spans="1:8" ht="12.5">
+    <row r="173" spans="1:8">
       <c r="A173" s="1"/>
       <c r="G173" s="2"/>
       <c r="H173" s="2"/>
     </row>
-    <row r="174" spans="1:8" ht="12.5">
+    <row r="174" spans="1:8">
       <c r="A174" s="1"/>
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
     </row>
-    <row r="175" spans="1:8" ht="12.5">
+    <row r="175" spans="1:8">
       <c r="A175" s="1"/>
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
     </row>
-    <row r="176" spans="1:8" ht="12.5">
+    <row r="176" spans="1:8">
       <c r="A176" s="1"/>
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
     </row>
-    <row r="177" spans="1:8" ht="12.5">
+    <row r="177" spans="1:8">
       <c r="A177" s="1"/>
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
     </row>
-    <row r="178" spans="1:8" ht="12.5">
+    <row r="178" spans="1:8">
       <c r="A178" s="1"/>
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
     </row>
-    <row r="179" spans="1:8" ht="12.5">
+    <row r="179" spans="1:8">
       <c r="A179" s="1"/>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
     </row>
-    <row r="180" spans="1:8" ht="12.5">
+    <row r="180" spans="1:8">
       <c r="A180" s="1"/>
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
     </row>
-    <row r="181" spans="1:8" ht="12.5">
+    <row r="181" spans="1:8">
       <c r="A181" s="1"/>
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
     </row>
-    <row r="182" spans="1:8" ht="12.5">
+    <row r="182" spans="1:8">
       <c r="A182" s="1"/>
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
     </row>
-    <row r="183" spans="1:8" ht="12.5">
+    <row r="183" spans="1:8">
       <c r="A183" s="1"/>
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
     </row>
-    <row r="184" spans="1:8" ht="12.5">
+    <row r="184" spans="1:8">
       <c r="A184" s="1"/>
       <c r="G184" s="2"/>
       <c r="H184" s="2"/>
     </row>
-    <row r="185" spans="1:8" ht="12.5">
+    <row r="185" spans="1:8">
       <c r="A185" s="1"/>
       <c r="G185" s="2"/>
       <c r="H185" s="2"/>
     </row>
-    <row r="186" spans="1:8" ht="12.5">
+    <row r="186" spans="1:8">
       <c r="A186" s="1"/>
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
     </row>
-    <row r="187" spans="1:8" ht="12.5">
+    <row r="187" spans="1:8">
       <c r="A187" s="1"/>
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
     </row>
-    <row r="188" spans="1:8" ht="12.5">
+    <row r="188" spans="1:8">
       <c r="A188" s="1"/>
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
     </row>
-    <row r="189" spans="1:8" ht="12.5">
+    <row r="189" spans="1:8">
       <c r="A189" s="1"/>
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
     </row>
-    <row r="190" spans="1:8" ht="12.5">
+    <row r="190" spans="1:8">
       <c r="A190" s="1"/>
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
     </row>
-    <row r="191" spans="1:8" ht="12.5">
+    <row r="191" spans="1:8">
       <c r="A191" s="1"/>
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
     </row>
-    <row r="192" spans="1:8" ht="12.5">
+    <row r="192" spans="1:8">
       <c r="A192" s="1"/>
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
     </row>
-    <row r="193" spans="1:8" ht="12.5">
+    <row r="193" spans="1:8">
       <c r="A193" s="1"/>
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
     </row>
-    <row r="194" spans="1:8" ht="12.5">
+    <row r="194" spans="1:8">
       <c r="A194" s="1"/>
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
     </row>
-    <row r="195" spans="1:8" ht="12.5">
+    <row r="195" spans="1:8">
       <c r="A195" s="1"/>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
     </row>
-    <row r="196" spans="1:8" ht="12.5">
+    <row r="196" spans="1:8">
       <c r="A196" s="1"/>
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
     </row>
-    <row r="197" spans="1:8" ht="12.5">
+    <row r="197" spans="1:8">
       <c r="A197" s="1"/>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
     </row>
-    <row r="198" spans="1:8" ht="12.5">
+    <row r="198" spans="1:8">
       <c r="A198" s="1"/>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
     </row>
-    <row r="199" spans="1:8" ht="12.5">
+    <row r="199" spans="1:8">
       <c r="A199" s="1"/>
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
     </row>
-    <row r="200" spans="1:8" ht="12.5">
+    <row r="200" spans="1:8">
       <c r="A200" s="1"/>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
     </row>
-    <row r="201" spans="1:8" ht="12.5">
+    <row r="201" spans="1:8">
       <c r="A201" s="1"/>
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
     </row>
-    <row r="202" spans="1:8" ht="12.5">
+    <row r="202" spans="1:8">
       <c r="A202" s="1"/>
       <c r="G202" s="2"/>
       <c r="H202" s="2"/>
     </row>
-    <row r="203" spans="1:8" ht="12.5">
+    <row r="203" spans="1:8">
       <c r="A203" s="1"/>
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
     </row>
-    <row r="204" spans="1:8" ht="12.5">
+    <row r="204" spans="1:8">
       <c r="A204" s="1"/>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
     </row>
-    <row r="205" spans="1:8" ht="12.5">
+    <row r="205" spans="1:8">
       <c r="A205" s="1"/>
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
     </row>
-    <row r="206" spans="1:8" ht="12.5">
+    <row r="206" spans="1:8">
       <c r="A206" s="1"/>
       <c r="G206" s="2"/>
       <c r="H206" s="2"/>
     </row>
-    <row r="207" spans="1:8" ht="12.5">
+    <row r="207" spans="1:8">
       <c r="A207" s="1"/>
       <c r="G207" s="2"/>
       <c r="H207" s="2"/>
     </row>
-    <row r="208" spans="1:8" ht="12.5">
+    <row r="208" spans="1:8">
       <c r="A208" s="1"/>
       <c r="G208" s="2"/>
       <c r="H208" s="2"/>
     </row>
-    <row r="209" spans="1:8" ht="12.5">
+    <row r="209" spans="1:8">
       <c r="A209" s="1"/>
       <c r="G209" s="2"/>
       <c r="H209" s="2"/>
     </row>
-    <row r="210" spans="1:8" ht="12.5">
+    <row r="210" spans="1:8">
       <c r="A210" s="1"/>
       <c r="G210" s="2"/>
       <c r="H210" s="2"/>
     </row>
-    <row r="211" spans="1:8" ht="12.5">
+    <row r="211" spans="1:8">
       <c r="A211" s="1"/>
       <c r="G211" s="2"/>
       <c r="H211" s="2"/>
     </row>
-    <row r="212" spans="1:8" ht="12.5">
+    <row r="212" spans="1:8">
       <c r="A212" s="1"/>
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
     </row>
-    <row r="213" spans="1:8" ht="12.5">
+    <row r="213" spans="1:8">
       <c r="A213" s="1"/>
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
     </row>
-    <row r="214" spans="1:8" ht="12.5">
+    <row r="214" spans="1:8">
       <c r="A214" s="1"/>
       <c r="G214" s="2"/>
       <c r="H214" s="2"/>
     </row>
-    <row r="215" spans="1:8" ht="12.5">
+    <row r="215" spans="1:8">
       <c r="A215" s="1"/>
       <c r="G215" s="2"/>
       <c r="H215" s="2"/>
     </row>
-    <row r="216" spans="1:8" ht="12.5">
+    <row r="216" spans="1:8">
       <c r="A216" s="1"/>
       <c r="G216" s="2"/>
       <c r="H216" s="2"/>
     </row>
-    <row r="217" spans="1:8" ht="12.5">
+    <row r="217" spans="1:8">
       <c r="A217" s="1"/>
       <c r="G217" s="2"/>
       <c r="H217" s="2"/>
     </row>
-    <row r="218" spans="1:8" ht="12.5">
+    <row r="218" spans="1:8">
       <c r="A218" s="1"/>
       <c r="G218" s="2"/>
       <c r="H218" s="2"/>
     </row>
-    <row r="219" spans="1:8" ht="12.5">
+    <row r="219" spans="1:8">
       <c r="A219" s="1"/>
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
     </row>
-    <row r="220" spans="1:8" ht="12.5">
+    <row r="220" spans="1:8">
       <c r="A220" s="1"/>
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
     </row>
-    <row r="221" spans="1:8" ht="12.5">
+    <row r="221" spans="1:8">
       <c r="A221" s="1"/>
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
     </row>
-    <row r="222" spans="1:8" ht="12.5">
+    <row r="222" spans="1:8">
       <c r="A222" s="1"/>
       <c r="G222" s="2"/>
       <c r="H222" s="2"/>
     </row>
-    <row r="223" spans="1:8" ht="12.5">
+    <row r="223" spans="1:8">
       <c r="A223" s="1"/>
       <c r="G223" s="2"/>
       <c r="H223" s="2"/>
     </row>
-    <row r="224" spans="1:8" ht="12.5">
+    <row r="224" spans="1:8">
       <c r="A224" s="1"/>
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
     </row>
-    <row r="225" spans="1:8" ht="12.5">
+    <row r="225" spans="1:8">
       <c r="A225" s="1"/>
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
     </row>
-    <row r="226" spans="1:8" ht="12.5">
+    <row r="226" spans="1:8">
       <c r="A226" s="1"/>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
     </row>
-    <row r="227" spans="1:8" ht="12.5">
+    <row r="227" spans="1:8">
       <c r="A227" s="1"/>
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
     </row>
-    <row r="228" spans="1:8" ht="12.5">
+    <row r="228" spans="1:8">
       <c r="A228" s="1"/>
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
     </row>
-    <row r="229" spans="1:8" ht="12.5">
+    <row r="229" spans="1:8">
       <c r="A229" s="1"/>
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
     </row>
-    <row r="230" spans="1:8" ht="12.5">
+    <row r="230" spans="1:8">
       <c r="A230" s="1"/>
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
     </row>
-    <row r="231" spans="1:8" ht="12.5">
+    <row r="231" spans="1:8">
       <c r="A231" s="1"/>
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
     </row>
-    <row r="232" spans="1:8" ht="12.5">
+    <row r="232" spans="1:8">
       <c r="A232" s="1"/>
       <c r="G232" s="2"/>
       <c r="H232" s="2"/>
     </row>
-    <row r="233" spans="1:8" ht="12.5">
+    <row r="233" spans="1:8">
       <c r="A233" s="1"/>
       <c r="G233" s="2"/>
       <c r="H233" s="2"/>
     </row>
-    <row r="234" spans="1:8" ht="12.5">
+    <row r="234" spans="1:8">
       <c r="A234" s="1"/>
       <c r="G234" s="2"/>
       <c r="H234" s="2"/>
     </row>
-    <row r="235" spans="1:8" ht="12.5">
+    <row r="235" spans="1:8">
       <c r="A235" s="1"/>
       <c r="G235" s="2"/>
       <c r="H235" s="2"/>
     </row>
-    <row r="236" spans="1:8" ht="12.5">
+    <row r="236" spans="1:8">
       <c r="A236" s="1"/>
       <c r="G236" s="2"/>
       <c r="H236" s="2"/>
     </row>
-    <row r="237" spans="1:8" ht="12.5">
+    <row r="237" spans="1:8">
       <c r="A237" s="1"/>
       <c r="G237" s="2"/>
       <c r="H237" s="2"/>
     </row>
-    <row r="238" spans="1:8" ht="12.5">
+    <row r="238" spans="1:8">
       <c r="A238" s="1"/>
       <c r="G238" s="2"/>
       <c r="H238" s="2"/>
     </row>
-    <row r="239" spans="1:8" ht="12.5">
+    <row r="239" spans="1:8">
       <c r="A239" s="1"/>
       <c r="G239" s="2"/>
       <c r="H239" s="2"/>
     </row>
-    <row r="240" spans="1:8" ht="12.5">
+    <row r="240" spans="1:8">
       <c r="A240" s="1"/>
       <c r="G240" s="2"/>
       <c r="H240" s="2"/>
     </row>
-    <row r="241" spans="1:8" ht="12.5">
+    <row r="241" spans="1:8">
       <c r="A241" s="1"/>
       <c r="G241" s="2"/>
       <c r="H241" s="2"/>
     </row>
-    <row r="242" spans="1:8" ht="12.5">
+    <row r="242" spans="1:8">
       <c r="A242" s="1"/>
       <c r="G242" s="2"/>
       <c r="H242" s="2"/>
     </row>
-    <row r="243" spans="1:8" ht="12.5">
+    <row r="243" spans="1:8">
       <c r="A243" s="1"/>
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
     </row>
-    <row r="244" spans="1:8" ht="12.5">
+    <row r="244" spans="1:8">
       <c r="A244" s="1"/>
       <c r="G244" s="2"/>
       <c r="H244" s="2"/>
     </row>
-    <row r="245" spans="1:8" ht="12.5">
+    <row r="245" spans="1:8">
       <c r="A245" s="1"/>
       <c r="G245" s="2"/>
       <c r="H245" s="2"/>
     </row>
-    <row r="246" spans="1:8" ht="12.5">
+    <row r="246" spans="1:8">
       <c r="A246" s="1"/>
       <c r="G246" s="2"/>
       <c r="H246" s="2"/>
     </row>
-    <row r="247" spans="1:8" ht="12.5">
+    <row r="247" spans="1:8">
       <c r="A247" s="1"/>
       <c r="G247" s="2"/>
       <c r="H247" s="2"/>
     </row>
-    <row r="248" spans="1:8" ht="12.5">
+    <row r="248" spans="1:8">
       <c r="A248" s="1"/>
       <c r="G248" s="2"/>
       <c r="H248" s="2"/>
     </row>
-    <row r="249" spans="1:8" ht="12.5">
+    <row r="249" spans="1:8">
       <c r="A249" s="1"/>
       <c r="G249" s="2"/>
       <c r="H249" s="2"/>
     </row>
-    <row r="250" spans="1:8" ht="12.5">
+    <row r="250" spans="1:8">
       <c r="A250" s="1"/>
       <c r="G250" s="2"/>
       <c r="H250" s="2"/>
     </row>
-    <row r="251" spans="1:8" ht="12.5">
+    <row r="251" spans="1:8">
       <c r="A251" s="1"/>
       <c r="G251" s="2"/>
       <c r="H251" s="2"/>
     </row>
-    <row r="252" spans="1:8" ht="12.5">
+    <row r="252" spans="1:8">
       <c r="A252" s="1"/>
       <c r="G252" s="2"/>
       <c r="H252" s="2"/>
     </row>
-    <row r="253" spans="1:8" ht="12.5">
+    <row r="253" spans="1:8">
       <c r="A253" s="1"/>
       <c r="G253" s="2"/>
       <c r="H253" s="2"/>
     </row>
-    <row r="254" spans="1:8" ht="12.5">
+    <row r="254" spans="1:8">
       <c r="A254" s="1"/>
       <c r="G254" s="2"/>
       <c r="H254" s="2"/>
     </row>
-    <row r="255" spans="1:8" ht="12.5">
+    <row r="255" spans="1:8">
       <c r="A255" s="1"/>
       <c r="G255" s="2"/>
       <c r="H255" s="2"/>
     </row>
-    <row r="256" spans="1:8" ht="12.5">
+    <row r="256" spans="1:8">
       <c r="A256" s="1"/>
       <c r="G256" s="2"/>
       <c r="H256" s="2"/>
     </row>
-    <row r="257" spans="1:8" ht="12.5">
+    <row r="257" spans="1:8">
       <c r="A257" s="1"/>
       <c r="G257" s="2"/>
       <c r="H257" s="2"/>
     </row>
-    <row r="258" spans="1:8" ht="12.5">
+    <row r="258" spans="1:8">
       <c r="A258" s="1"/>
       <c r="G258" s="2"/>
       <c r="H258" s="2"/>
     </row>
-    <row r="259" spans="1:8" ht="12.5">
+    <row r="259" spans="1:8">
       <c r="A259" s="1"/>
       <c r="G259" s="2"/>
       <c r="H259" s="2"/>
     </row>
-    <row r="260" spans="1:8" ht="12.5">
+    <row r="260" spans="1:8">
       <c r="A260" s="1"/>
       <c r="G260" s="2"/>
       <c r="H260" s="2"/>
     </row>
-    <row r="261" spans="1:8" ht="12.5">
+    <row r="261" spans="1:8">
       <c r="A261" s="1"/>
       <c r="G261" s="2"/>
       <c r="H261" s="2"/>
     </row>
-    <row r="262" spans="1:8" ht="12.5">
+    <row r="262" spans="1:8">
       <c r="A262" s="1"/>
       <c r="G262" s="2"/>
       <c r="H262" s="2"/>
     </row>
-    <row r="263" spans="1:8" ht="12.5">
+    <row r="263" spans="1:8">
       <c r="A263" s="1"/>
       <c r="G263" s="2"/>
       <c r="H263" s="2"/>
     </row>
-    <row r="264" spans="1:8" ht="12.5">
+    <row r="264" spans="1:8">
       <c r="A264" s="1"/>
       <c r="G264" s="2"/>
       <c r="H264" s="2"/>
     </row>
-    <row r="265" spans="1:8" ht="12.5">
+    <row r="265" spans="1:8">
       <c r="A265" s="1"/>
       <c r="G265" s="2"/>
       <c r="H265" s="2"/>
     </row>
-    <row r="266" spans="1:8" ht="12.5">
+    <row r="266" spans="1:8">
       <c r="A266" s="1"/>
       <c r="G266" s="2"/>
       <c r="H266" s="2"/>
     </row>
-    <row r="267" spans="1:8" ht="12.5">
+    <row r="267" spans="1:8">
       <c r="A267" s="1"/>
       <c r="G267" s="2"/>
       <c r="H267" s="2"/>
     </row>
-    <row r="268" spans="1:8" ht="12.5">
+    <row r="268" spans="1:8">
       <c r="A268" s="1"/>
       <c r="G268" s="2"/>
       <c r="H268" s="2"/>
     </row>
-    <row r="269" spans="1:8" ht="12.5">
+    <row r="269" spans="1:8">
       <c r="A269" s="1"/>
       <c r="G269" s="2"/>
       <c r="H269" s="2"/>
     </row>
-    <row r="270" spans="1:8" ht="12.5">
+    <row r="270" spans="1:8">
       <c r="A270" s="1"/>
       <c r="G270" s="2"/>
       <c r="H270" s="2"/>
     </row>
-    <row r="271" spans="1:8" ht="12.5">
+    <row r="271" spans="1:8">
       <c r="A271" s="1"/>
       <c r="G271" s="2"/>
       <c r="H271" s="2"/>
     </row>
-    <row r="272" spans="1:8" ht="12.5">
+    <row r="272" spans="1:8">
       <c r="A272" s="1"/>
       <c r="G272" s="2"/>
       <c r="H272" s="2"/>
     </row>
-    <row r="273" spans="1:8" ht="12.5">
+    <row r="273" spans="1:8">
       <c r="A273" s="1"/>
       <c r="G273" s="2"/>
       <c r="H273" s="2"/>
     </row>
-    <row r="274" spans="1:8" ht="12.5">
+    <row r="274" spans="1:8">
       <c r="A274" s="1"/>
       <c r="G274" s="2"/>
       <c r="H274" s="2"/>
     </row>
-    <row r="275" spans="1:8" ht="12.5">
+    <row r="275" spans="1:8">
       <c r="A275" s="1"/>
       <c r="G275" s="2"/>
       <c r="H275" s="2"/>
     </row>
-    <row r="276" spans="1:8" ht="12.5">
+    <row r="276" spans="1:8">
       <c r="A276" s="1"/>
       <c r="G276" s="2"/>
       <c r="H276" s="2"/>
     </row>
-    <row r="277" spans="1:8" ht="12.5">
+    <row r="277" spans="1:8">
       <c r="A277" s="1"/>
       <c r="G277" s="2"/>
       <c r="H277" s="2"/>
     </row>
-    <row r="278" spans="1:8" ht="12.5">
+    <row r="278" spans="1:8">
       <c r="A278" s="1"/>
       <c r="G278" s="2"/>
       <c r="H278" s="2"/>
     </row>
-    <row r="279" spans="1:8" ht="12.5">
+    <row r="279" spans="1:8">
       <c r="A279" s="1"/>
       <c r="G279" s="2"/>
       <c r="H279" s="2"/>
     </row>
-    <row r="280" spans="1:8" ht="12.5">
+    <row r="280" spans="1:8">
       <c r="A280" s="1"/>
       <c r="G280" s="2"/>
       <c r="H280" s="2"/>
     </row>
-    <row r="281" spans="1:8" ht="12.5">
+    <row r="281" spans="1:8">
       <c r="A281" s="1"/>
       <c r="G281" s="2"/>
       <c r="H281" s="2"/>
     </row>
-    <row r="282" spans="1:8" ht="12.5">
+    <row r="282" spans="1:8">
       <c r="A282" s="1"/>
       <c r="G282" s="2"/>
       <c r="H282" s="2"/>
     </row>
-    <row r="283" spans="1:8" ht="12.5">
+    <row r="283" spans="1:8">
       <c r="A283" s="1"/>
       <c r="G283" s="2"/>
       <c r="H283" s="2"/>
     </row>
-    <row r="284" spans="1:8" ht="12.5">
+    <row r="284" spans="1:8">
       <c r="A284" s="1"/>
       <c r="G284" s="2"/>
       <c r="H284" s="2"/>
     </row>
-    <row r="285" spans="1:8" ht="12.5">
+    <row r="285" spans="1:8">
       <c r="A285" s="1"/>
       <c r="G285" s="2"/>
       <c r="H285" s="2"/>
     </row>
-    <row r="286" spans="1:8" ht="12.5">
+    <row r="286" spans="1:8">
       <c r="A286" s="1"/>
       <c r="G286" s="2"/>
       <c r="H286" s="2"/>
     </row>
-    <row r="287" spans="1:8" ht="12.5">
+    <row r="287" spans="1:8">
       <c r="A287" s="1"/>
       <c r="G287" s="2"/>
       <c r="H287" s="2"/>
     </row>
-    <row r="288" spans="1:8" ht="12.5">
+    <row r="288" spans="1:8">
       <c r="A288" s="1"/>
       <c r="G288" s="2"/>
       <c r="H288" s="2"/>
     </row>
-    <row r="289" spans="1:8" ht="12.5">
+    <row r="289" spans="1:8">
       <c r="A289" s="1"/>
       <c r="G289" s="2"/>
       <c r="H289" s="2"/>
     </row>
-    <row r="290" spans="1:8" ht="12.5">
+    <row r="290" spans="1:8">
       <c r="A290" s="1"/>
       <c r="G290" s="2"/>
       <c r="H290" s="2"/>
     </row>
-    <row r="291" spans="1:8" ht="12.5">
+    <row r="291" spans="1:8">
       <c r="A291" s="1"/>
       <c r="G291" s="2"/>
       <c r="H291" s="2"/>
     </row>
-    <row r="292" spans="1:8" ht="12.5">
+    <row r="292" spans="1:8">
       <c r="A292" s="1"/>
       <c r="G292" s="2"/>
       <c r="H292" s="2"/>
     </row>
-    <row r="293" spans="1:8" ht="12.5">
+    <row r="293" spans="1:8">
       <c r="A293" s="1"/>
       <c r="G293" s="2"/>
       <c r="H293" s="2"/>
     </row>
-    <row r="294" spans="1:8" ht="12.5">
+    <row r="294" spans="1:8">
       <c r="A294" s="1"/>
       <c r="G294" s="2"/>
       <c r="H294" s="2"/>
     </row>
-    <row r="295" spans="1:8" ht="12.5">
+    <row r="295" spans="1:8">
       <c r="A295" s="1"/>
       <c r="G295" s="2"/>
       <c r="H295" s="2"/>
     </row>
-    <row r="296" spans="1:8" ht="12.5">
+    <row r="296" spans="1:8">
       <c r="A296" s="1"/>
       <c r="G296" s="2"/>
       <c r="H296" s="2"/>
     </row>
-    <row r="297" spans="1:8" ht="12.5">
+    <row r="297" spans="1:8">
       <c r="A297" s="1"/>
       <c r="G297" s="2"/>
       <c r="H297" s="2"/>
     </row>
-    <row r="298" spans="1:8" ht="12.5">
+    <row r="298" spans="1:8">
       <c r="A298" s="1"/>
       <c r="G298" s="2"/>
       <c r="H298" s="2"/>
     </row>
-    <row r="299" spans="1:8" ht="12.5">
+    <row r="299" spans="1:8">
       <c r="A299" s="1"/>
       <c r="G299" s="2"/>
       <c r="H299" s="2"/>
     </row>
-    <row r="300" spans="1:8" ht="12.5">
+    <row r="300" spans="1:8">
       <c r="A300" s="1"/>
       <c r="G300" s="2"/>
       <c r="H300" s="2"/>
     </row>
-    <row r="301" spans="1:8" ht="12.5">
+    <row r="301" spans="1:8">
       <c r="A301" s="1"/>
       <c r="G301" s="2"/>
       <c r="H301" s="2"/>
     </row>
-    <row r="302" spans="1:8" ht="12.5">
+    <row r="302" spans="1:8">
       <c r="A302" s="1"/>
       <c r="G302" s="2"/>
       <c r="H302" s="2"/>
     </row>
-    <row r="303" spans="1:8" ht="12.5">
+    <row r="303" spans="1:8">
       <c r="A303" s="1"/>
       <c r="G303" s="2"/>
       <c r="H303" s="2"/>
     </row>
-    <row r="304" spans="1:8" ht="12.5">
+    <row r="304" spans="1:8">
       <c r="A304" s="1"/>
       <c r="G304" s="2"/>
       <c r="H304" s="2"/>
     </row>
-    <row r="305" spans="1:8" ht="12.5">
+    <row r="305" spans="1:8">
       <c r="A305" s="1"/>
       <c r="G305" s="2"/>
       <c r="H305" s="2"/>
     </row>
-    <row r="306" spans="1:8" ht="12.5">
+    <row r="306" spans="1:8">
       <c r="A306" s="1"/>
       <c r="G306" s="2"/>
       <c r="H306" s="2"/>
     </row>
-    <row r="307" spans="1:8" ht="12.5">
+    <row r="307" spans="1:8">
       <c r="A307" s="1"/>
       <c r="G307" s="2"/>
       <c r="H307" s="2"/>
     </row>
-    <row r="308" spans="1:8" ht="12.5">
+    <row r="308" spans="1:8">
       <c r="A308" s="1"/>
       <c r="G308" s="2"/>
       <c r="H308" s="2"/>
     </row>
-    <row r="309" spans="1:8" ht="12.5">
+    <row r="309" spans="1:8">
       <c r="A309" s="1"/>
       <c r="G309" s="2"/>
       <c r="H309" s="2"/>
     </row>
-    <row r="310" spans="1:8" ht="12.5">
+    <row r="310" spans="1:8">
       <c r="A310" s="1"/>
       <c r="G310" s="2"/>
       <c r="H310" s="2"/>
     </row>
-    <row r="311" spans="1:8" ht="12.5">
+    <row r="311" spans="1:8">
       <c r="A311" s="1"/>
       <c r="G311" s="2"/>
       <c r="H311" s="2"/>
     </row>
-    <row r="312" spans="1:8" ht="12.5">
+    <row r="312" spans="1:8">
       <c r="A312" s="1"/>
       <c r="G312" s="2"/>
       <c r="H312" s="2"/>
     </row>
-    <row r="313" spans="1:8" ht="12.5">
+    <row r="313" spans="1:8">
       <c r="A313" s="1"/>
       <c r="G313" s="2"/>
       <c r="H313" s="2"/>
     </row>
-    <row r="314" spans="1:8" ht="12.5">
+    <row r="314" spans="1:8">
       <c r="A314" s="1"/>
       <c r="G314" s="2"/>
       <c r="H314" s="2"/>
     </row>
-    <row r="315" spans="1:8" ht="12.5">
+    <row r="315" spans="1:8">
       <c r="A315" s="1"/>
       <c r="G315" s="2"/>
       <c r="H315" s="2"/>
     </row>
-    <row r="316" spans="1:8" ht="12.5">
+    <row r="316" spans="1:8">
       <c r="A316" s="1"/>
       <c r="G316" s="2"/>
       <c r="H316" s="2"/>
     </row>
-    <row r="317" spans="1:8" ht="12.5">
+    <row r="317" spans="1:8">
       <c r="A317" s="1"/>
       <c r="G317" s="2"/>
       <c r="H317" s="2"/>
     </row>
-    <row r="318" spans="1:8" ht="12.5">
+    <row r="318" spans="1:8">
       <c r="A318" s="1"/>
       <c r="G318" s="2"/>
       <c r="H318" s="2"/>
     </row>
-    <row r="319" spans="1:8" ht="12.5">
+    <row r="319" spans="1:8">
       <c r="A319" s="1"/>
       <c r="G319" s="2"/>
       <c r="H319" s="2"/>
     </row>
-    <row r="320" spans="1:8" ht="12.5">
+    <row r="320" spans="1:8">
       <c r="A320" s="1"/>
       <c r="G320" s="2"/>
       <c r="H320" s="2"/>
     </row>
-    <row r="321" spans="1:8" ht="12.5">
+    <row r="321" spans="1:8">
       <c r="A321" s="1"/>
       <c r="G321" s="2"/>
       <c r="H321" s="2"/>
     </row>
-    <row r="322" spans="1:8" ht="12.5">
+    <row r="322" spans="1:8">
       <c r="A322" s="1"/>
       <c r="G322" s="2"/>
       <c r="H322" s="2"/>
     </row>
-    <row r="323" spans="1:8" ht="12.5">
+    <row r="323" spans="1:8">
       <c r="A323" s="1"/>
       <c r="G323" s="2"/>
       <c r="H323" s="2"/>
     </row>
-    <row r="324" spans="1:8" ht="12.5">
+    <row r="324" spans="1:8">
       <c r="A324" s="1"/>
       <c r="G324" s="2"/>
       <c r="H324" s="2"/>
     </row>
-    <row r="325" spans="1:8" ht="12.5">
+    <row r="325" spans="1:8">
       <c r="A325" s="1"/>
       <c r="G325" s="2"/>
       <c r="H325" s="2"/>
     </row>
-    <row r="326" spans="1:8" ht="12.5">
+    <row r="326" spans="1:8">
       <c r="A326" s="1"/>
       <c r="G326" s="2"/>
       <c r="H326" s="2"/>
     </row>
-    <row r="327" spans="1:8" ht="12.5">
+    <row r="327" spans="1:8">
       <c r="A327" s="1"/>
       <c r="G327" s="2"/>
       <c r="H327" s="2"/>
     </row>
-    <row r="328" spans="1:8" ht="12.5">
+    <row r="328" spans="1:8">
       <c r="A328" s="1"/>
       <c r="G328" s="2"/>
       <c r="H328" s="2"/>
     </row>
-    <row r="329" spans="1:8" ht="12.5">
+    <row r="329" spans="1:8">
       <c r="A329" s="1"/>
       <c r="G329" s="2"/>
       <c r="H329" s="2"/>
     </row>
-    <row r="330" spans="1:8" ht="12.5">
+    <row r="330" spans="1:8">
       <c r="A330" s="1"/>
       <c r="G330" s="2"/>
       <c r="H330" s="2"/>
     </row>
-    <row r="331" spans="1:8" ht="12.5">
+    <row r="331" spans="1:8">
       <c r="A331" s="1"/>
       <c r="G331" s="2"/>
       <c r="H331" s="2"/>
     </row>
-    <row r="332" spans="1:8" ht="12.5">
+    <row r="332" spans="1:8">
       <c r="A332" s="1"/>
       <c r="G332" s="2"/>
       <c r="H332" s="2"/>
     </row>
-    <row r="333" spans="1:8" ht="12.5">
+    <row r="333" spans="1:8">
       <c r="A333" s="1"/>
       <c r="G333" s="2"/>
       <c r="H333" s="2"/>
     </row>
-    <row r="334" spans="1:8" ht="12.5">
+    <row r="334" spans="1:8">
       <c r="A334" s="1"/>
       <c r="G334" s="2"/>
       <c r="H334" s="2"/>
     </row>
-    <row r="335" spans="1:8" ht="12.5">
+    <row r="335" spans="1:8">
       <c r="A335" s="1"/>
       <c r="G335" s="2"/>
       <c r="H335" s="2"/>
     </row>
-    <row r="336" spans="1:8" ht="12.5">
+    <row r="336" spans="1:8">
       <c r="A336" s="1"/>
       <c r="G336" s="2"/>
       <c r="H336" s="2"/>
     </row>
-    <row r="337" spans="1:8" ht="12.5">
+    <row r="337" spans="1:8">
       <c r="A337" s="1"/>
       <c r="G337" s="2"/>
       <c r="H337" s="2"/>
     </row>
-    <row r="338" spans="1:8" ht="12.5">
+    <row r="338" spans="1:8">
       <c r="A338" s="1"/>
       <c r="G338" s="2"/>
       <c r="H338" s="2"/>
     </row>
-    <row r="339" spans="1:8" ht="12.5">
+    <row r="339" spans="1:8">
       <c r="A339" s="1"/>
       <c r="G339" s="2"/>
       <c r="H339" s="2"/>
     </row>
-    <row r="340" spans="1:8" ht="12.5">
+    <row r="340" spans="1:8">
       <c r="A340" s="1"/>
       <c r="G340" s="2"/>
       <c r="H340" s="2"/>
     </row>
-    <row r="341" spans="1:8" ht="12.5">
+    <row r="341" spans="1:8">
       <c r="A341" s="1"/>
       <c r="G341" s="2"/>
       <c r="H341" s="2"/>
     </row>
-    <row r="342" spans="1:8" ht="12.5">
+    <row r="342" spans="1:8">
       <c r="A342" s="1"/>
       <c r="G342" s="2"/>
       <c r="H342" s="2"/>
     </row>
-    <row r="343" spans="1:8" ht="12.5">
+    <row r="343" spans="1:8">
       <c r="A343" s="1"/>
       <c r="G343" s="2"/>
       <c r="H343" s="2"/>
     </row>
-    <row r="344" spans="1:8" ht="12.5">
+    <row r="344" spans="1:8">
       <c r="A344" s="1"/>
       <c r="G344" s="2"/>
       <c r="H344" s="2"/>
     </row>
-    <row r="345" spans="1:8" ht="12.5">
+    <row r="345" spans="1:8">
       <c r="A345" s="1"/>
       <c r="G345" s="2"/>
       <c r="H345" s="2"/>
     </row>
-    <row r="346" spans="1:8" ht="12.5">
+    <row r="346" spans="1:8">
       <c r="A346" s="1"/>
       <c r="G346" s="2"/>
       <c r="H346" s="2"/>
     </row>
-    <row r="347" spans="1:8" ht="12.5">
+    <row r="347" spans="1:8">
       <c r="A347" s="1"/>
       <c r="G347" s="2"/>
       <c r="H347" s="2"/>
     </row>
-    <row r="348" spans="1:8" ht="12.5">
+    <row r="348" spans="1:8">
       <c r="A348" s="1"/>
       <c r="G348" s="2"/>
       <c r="H348" s="2"/>
     </row>
-    <row r="349" spans="1:8" ht="12.5">
+    <row r="349" spans="1:8">
       <c r="A349" s="1"/>
       <c r="G349" s="2"/>
       <c r="H349" s="2"/>
     </row>
-    <row r="350" spans="1:8" ht="12.5">
+    <row r="350" spans="1:8">
       <c r="A350" s="1"/>
       <c r="G350" s="2"/>
       <c r="H350" s="2"/>
     </row>
-    <row r="351" spans="1:8" ht="12.5">
+    <row r="351" spans="1:8">
       <c r="A351" s="1"/>
       <c r="G351" s="2"/>
       <c r="H351" s="2"/>
     </row>
-    <row r="352" spans="1:8" ht="12.5">
+    <row r="352" spans="1:8">
       <c r="A352" s="1"/>
       <c r="G352" s="2"/>
       <c r="H352" s="2"/>
     </row>
-    <row r="353" spans="1:8" ht="12.5">
+    <row r="353" spans="1:8">
       <c r="A353" s="1"/>
       <c r="G353" s="2"/>
       <c r="H353" s="2"/>
     </row>
-    <row r="354" spans="1:8" ht="12.5">
+    <row r="354" spans="1:8">
       <c r="A354" s="1"/>
       <c r="G354" s="2"/>
       <c r="H354" s="2"/>
     </row>
-    <row r="355" spans="1:8" ht="12.5">
+    <row r="355" spans="1:8">
       <c r="A355" s="1"/>
       <c r="G355" s="2"/>
       <c r="H355" s="2"/>
     </row>
-    <row r="356" spans="1:8" ht="12.5">
+    <row r="356" spans="1:8">
       <c r="A356" s="1"/>
       <c r="G356" s="2"/>
       <c r="H356" s="2"/>
     </row>
-    <row r="357" spans="1:8" ht="12.5">
+    <row r="357" spans="1:8">
       <c r="A357" s="1"/>
       <c r="G357" s="2"/>
       <c r="H357" s="2"/>
     </row>
-    <row r="358" spans="1:8" ht="12.5">
+    <row r="358" spans="1:8">
       <c r="A358" s="1"/>
       <c r="G358" s="2"/>
       <c r="H358" s="2"/>
     </row>
-    <row r="359" spans="1:8" ht="12.5">
+    <row r="359" spans="1:8">
       <c r="A359" s="1"/>
       <c r="G359" s="2"/>
       <c r="H359" s="2"/>
     </row>
-    <row r="360" spans="1:8" ht="12.5">
+    <row r="360" spans="1:8">
       <c r="A360" s="1"/>
       <c r="G360" s="2"/>
       <c r="H360" s="2"/>
     </row>
-    <row r="361" spans="1:8" ht="12.5">
+    <row r="361" spans="1:8">
       <c r="A361" s="1"/>
       <c r="G361" s="2"/>
       <c r="H361" s="2"/>
     </row>
-    <row r="362" spans="1:8" ht="12.5">
+    <row r="362" spans="1:8">
       <c r="A362" s="1"/>
       <c r="G362" s="2"/>
       <c r="H362" s="2"/>
     </row>
-    <row r="363" spans="1:8" ht="12.5">
+    <row r="363" spans="1:8">
       <c r="A363" s="1"/>
       <c r="G363" s="2"/>
       <c r="H363" s="2"/>
     </row>
-    <row r="364" spans="1:8" ht="12.5">
+    <row r="364" spans="1:8">
       <c r="A364" s="1"/>
       <c r="G364" s="2"/>
       <c r="H364" s="2"/>
     </row>
-    <row r="365" spans="1:8" ht="12.5">
+    <row r="365" spans="1:8">
       <c r="A365" s="1"/>
       <c r="G365" s="2"/>
       <c r="H365" s="2"/>
     </row>
-    <row r="366" spans="1:8" ht="12.5">
+    <row r="366" spans="1:8">
       <c r="A366" s="1"/>
       <c r="G366" s="2"/>
       <c r="H366" s="2"/>
     </row>
-    <row r="367" spans="1:8" ht="12.5">
+    <row r="367" spans="1:8">
       <c r="A367" s="1"/>
       <c r="G367" s="2"/>
       <c r="H367" s="2"/>
     </row>
-    <row r="368" spans="1:8" ht="12.5">
+    <row r="368" spans="1:8">
       <c r="A368" s="1"/>
       <c r="G368" s="2"/>
       <c r="H368" s="2"/>
     </row>
-    <row r="369" spans="1:8" ht="12.5">
+    <row r="369" spans="1:8">
       <c r="A369" s="1"/>
       <c r="G369" s="2"/>
       <c r="H369" s="2"/>
     </row>
-    <row r="370" spans="1:8" ht="12.5">
+    <row r="370" spans="1:8">
       <c r="G370" s="2"/>
       <c r="H370" s="2"/>
     </row>
-    <row r="371" spans="1:8" ht="12.5">
+    <row r="371" spans="1:8">
       <c r="G371" s="2"/>
       <c r="H371" s="2"/>
     </row>
-    <row r="372" spans="1:8" ht="12.5">
+    <row r="372" spans="1:8">
       <c r="G372" s="2"/>
       <c r="H372" s="2"/>
     </row>
-    <row r="373" spans="1:8" ht="12.5">
+    <row r="373" spans="1:8">
       <c r="G373" s="2"/>
       <c r="H373" s="2"/>
     </row>
-    <row r="374" spans="1:8" ht="12.5">
+    <row r="374" spans="1:8">
       <c r="G374" s="2"/>
       <c r="H374" s="2"/>
     </row>
-    <row r="375" spans="1:8" ht="12.5">
+    <row r="375" spans="1:8">
       <c r="G375" s="2"/>
       <c r="H375" s="2"/>
     </row>
-    <row r="376" spans="1:8" ht="12.5">
+    <row r="376" spans="1:8">
       <c r="G376" s="2"/>
       <c r="H376" s="2"/>
     </row>
-    <row r="377" spans="1:8" ht="12.5">
+    <row r="377" spans="1:8">
       <c r="G377" s="2"/>
       <c r="H377" s="2"/>
     </row>
-    <row r="378" spans="1:8" ht="12.5">
+    <row r="378" spans="1:8">
       <c r="G378" s="2"/>
       <c r="H378" s="2"/>
     </row>
-    <row r="379" spans="1:8" ht="12.5">
+    <row r="379" spans="1:8">
       <c r="G379" s="2"/>
       <c r="H379" s="2"/>
     </row>
-    <row r="380" spans="1:8" ht="12.5">
+    <row r="380" spans="1:8">
       <c r="G380" s="2"/>
       <c r="H380" s="2"/>
     </row>
-    <row r="381" spans="1:8" ht="12.5">
+    <row r="381" spans="1:8">
       <c r="G381" s="2"/>
       <c r="H381" s="2"/>
     </row>
-    <row r="382" spans="1:8" ht="12.5">
+    <row r="382" spans="1:8">
       <c r="G382" s="2"/>
       <c r="H382" s="2"/>
     </row>
-    <row r="383" spans="1:8" ht="12.5">
+    <row r="383" spans="1:8">
       <c r="G383" s="2"/>
       <c r="H383" s="2"/>
     </row>
-    <row r="384" spans="1:8" ht="12.5">
+    <row r="384" spans="1:8">
       <c r="G384" s="2"/>
       <c r="H384" s="2"/>
     </row>
-    <row r="385" spans="7:8" ht="12.5">
+    <row r="385" spans="7:8">
       <c r="G385" s="2"/>
       <c r="H385" s="2"/>
     </row>
-    <row r="386" spans="7:8" ht="12.5">
+    <row r="386" spans="7:8">
       <c r="G386" s="2"/>
       <c r="H386" s="2"/>
     </row>
-    <row r="387" spans="7:8" ht="12.5">
+    <row r="387" spans="7:8">
       <c r="G387" s="2"/>
       <c r="H387" s="2"/>
     </row>
-    <row r="388" spans="7:8" ht="12.5">
+    <row r="388" spans="7:8">
       <c r="G388" s="2"/>
       <c r="H388" s="2"/>
     </row>
-    <row r="389" spans="7:8" ht="12.5">
+    <row r="389" spans="7:8">
       <c r="G389" s="2"/>
       <c r="H389" s="2"/>
     </row>
-    <row r="390" spans="7:8" ht="12.5">
+    <row r="390" spans="7:8">
       <c r="G390" s="2"/>
       <c r="H390" s="2"/>
     </row>
-    <row r="391" spans="7:8" ht="12.5">
+    <row r="391" spans="7:8">
       <c r="G391" s="2"/>
       <c r="H391" s="2"/>
     </row>
-    <row r="392" spans="7:8" ht="12.5">
+    <row r="392" spans="7:8">
       <c r="G392" s="2"/>
       <c r="H392" s="2"/>
     </row>
-    <row r="393" spans="7:8" ht="12.5">
+    <row r="393" spans="7:8">
       <c r="G393" s="2"/>
       <c r="H393" s="2"/>
     </row>
-    <row r="394" spans="7:8" ht="12.5">
+    <row r="394" spans="7:8">
       <c r="G394" s="2"/>
       <c r="H394" s="2"/>
     </row>
-    <row r="395" spans="7:8" ht="12.5">
+    <row r="395" spans="7:8">
       <c r="G395" s="2"/>
       <c r="H395" s="2"/>
     </row>
-    <row r="396" spans="7:8" ht="12.5">
+    <row r="396" spans="7:8">
       <c r="G396" s="2"/>
       <c r="H396" s="2"/>
     </row>
-    <row r="397" spans="7:8" ht="12.5">
+    <row r="397" spans="7:8">
       <c r="G397" s="2"/>
       <c r="H397" s="2"/>
     </row>
-    <row r="398" spans="7:8" ht="12.5">
+    <row r="398" spans="7:8">
       <c r="G398" s="2"/>
       <c r="H398" s="2"/>
     </row>
-    <row r="399" spans="7:8" ht="12.5">
+    <row r="399" spans="7:8">
       <c r="G399" s="2"/>
       <c r="H399" s="2"/>
     </row>
-    <row r="400" spans="7:8" ht="12.5">
+    <row r="400" spans="7:8">
       <c r="G400" s="2"/>
       <c r="H400" s="2"/>
     </row>
-    <row r="401" spans="7:8" ht="12.5">
+    <row r="401" spans="7:8">
       <c r="G401" s="2"/>
       <c r="H401" s="2"/>
     </row>
-    <row r="402" spans="7:8" ht="12.5">
+    <row r="402" spans="7:8">
       <c r="G402" s="2"/>
       <c r="H402" s="2"/>
     </row>
-    <row r="403" spans="7:8" ht="12.5">
+    <row r="403" spans="7:8">
       <c r="G403" s="2"/>
       <c r="H403" s="2"/>
     </row>
-    <row r="404" spans="7:8" ht="12.5">
+    <row r="404" spans="7:8">
       <c r="G404" s="2"/>
       <c r="H404" s="2"/>
     </row>
-    <row r="405" spans="7:8" ht="12.5">
+    <row r="405" spans="7:8">
       <c r="G405" s="2"/>
       <c r="H405" s="2"/>
     </row>
-    <row r="406" spans="7:8" ht="12.5">
+    <row r="406" spans="7:8">
       <c r="G406" s="2"/>
       <c r="H406" s="2"/>
     </row>
-    <row r="407" spans="7:8" ht="12.5">
+    <row r="407" spans="7:8">
       <c r="G407" s="2"/>
       <c r="H407" s="2"/>
     </row>
-    <row r="408" spans="7:8" ht="12.5">
+    <row r="408" spans="7:8">
       <c r="G408" s="2"/>
       <c r="H408" s="2"/>
     </row>
-    <row r="409" spans="7:8" ht="12.5">
+    <row r="409" spans="7:8">
       <c r="G409" s="2"/>
       <c r="H409" s="2"/>
     </row>
-    <row r="410" spans="7:8" ht="12.5">
+    <row r="410" spans="7:8">
       <c r="G410" s="2"/>
       <c r="H410" s="2"/>
     </row>
-    <row r="411" spans="7:8" ht="12.5">
+    <row r="411" spans="7:8">
       <c r="G411" s="2"/>
       <c r="H411" s="2"/>
     </row>
-    <row r="412" spans="7:8" ht="12.5">
+    <row r="412" spans="7:8">
       <c r="G412" s="2"/>
       <c r="H412" s="2"/>
     </row>
-    <row r="413" spans="7:8" ht="12.5">
+    <row r="413" spans="7:8">
       <c r="G413" s="2"/>
       <c r="H413" s="2"/>
     </row>
-    <row r="414" spans="7:8" ht="12.5">
+    <row r="414" spans="7:8">
       <c r="G414" s="2"/>
       <c r="H414" s="2"/>
     </row>
-    <row r="415" spans="7:8" ht="12.5">
+    <row r="415" spans="7:8">
       <c r="G415" s="2"/>
       <c r="H415" s="2"/>
     </row>
-    <row r="416" spans="7:8" ht="12.5">
+    <row r="416" spans="7:8">
       <c r="G416" s="2"/>
       <c r="H416" s="2"/>
     </row>
-    <row r="417" spans="7:8" ht="12.5">
+    <row r="417" spans="7:8">
       <c r="G417" s="2"/>
       <c r="H417" s="2"/>
     </row>
-    <row r="418" spans="7:8" ht="12.5">
+    <row r="418" spans="7:8">
       <c r="G418" s="2"/>
       <c r="H418" s="2"/>
     </row>
-    <row r="419" spans="7:8" ht="12.5">
+    <row r="419" spans="7:8">
       <c r="G419" s="2"/>
       <c r="H419" s="2"/>
     </row>
-    <row r="420" spans="7:8" ht="12.5">
+    <row r="420" spans="7:8">
       <c r="G420" s="2"/>
       <c r="H420" s="2"/>
     </row>
-    <row r="421" spans="7:8" ht="12.5">
+    <row r="421" spans="7:8">
       <c r="G421" s="2"/>
       <c r="H421" s="2"/>
     </row>
-    <row r="422" spans="7:8" ht="12.5">
+    <row r="422" spans="7:8">
       <c r="G422" s="2"/>
       <c r="H422" s="2"/>
     </row>
-    <row r="423" spans="7:8" ht="12.5">
+    <row r="423" spans="7:8">
       <c r="G423" s="2"/>
       <c r="H423" s="2"/>
     </row>
-    <row r="424" spans="7:8" ht="12.5">
+    <row r="424" spans="7:8">
       <c r="G424" s="2"/>
       <c r="H424" s="2"/>
     </row>
-    <row r="425" spans="7:8" ht="12.5">
+    <row r="425" spans="7:8">
       <c r="G425" s="2"/>
       <c r="H425" s="2"/>
     </row>
-    <row r="426" spans="7:8" ht="12.5">
+    <row r="426" spans="7:8">
       <c r="G426" s="2"/>
       <c r="H426" s="2"/>
     </row>
-    <row r="427" spans="7:8" ht="12.5">
+    <row r="427" spans="7:8">
       <c r="G427" s="2"/>
       <c r="H427" s="2"/>
     </row>
-    <row r="428" spans="7:8" ht="12.5">
+    <row r="428" spans="7:8">
       <c r="G428" s="2"/>
       <c r="H428" s="2"/>
     </row>
-    <row r="429" spans="7:8" ht="12.5">
+    <row r="429" spans="7:8">
       <c r="G429" s="2"/>
       <c r="H429" s="2"/>
     </row>
-    <row r="430" spans="7:8" ht="12.5">
+    <row r="430" spans="7:8">
       <c r="G430" s="2"/>
       <c r="H430" s="2"/>
     </row>
-    <row r="431" spans="7:8" ht="12.5">
+    <row r="431" spans="7:8">
       <c r="G431" s="2"/>
       <c r="H431" s="2"/>
     </row>
-    <row r="432" spans="7:8" ht="12.5">
+    <row r="432" spans="7:8">
       <c r="G432" s="2"/>
       <c r="H432" s="2"/>
     </row>
-    <row r="433" spans="7:8" ht="12.5">
+    <row r="433" spans="7:8">
       <c r="G433" s="2"/>
       <c r="H433" s="2"/>
     </row>
-    <row r="434" spans="7:8" ht="12.5">
+    <row r="434" spans="7:8">
       <c r="G434" s="2"/>
       <c r="H434" s="2"/>
     </row>
-    <row r="435" spans="7:8" ht="12.5">
+    <row r="435" spans="7:8">
       <c r="G435" s="2"/>
       <c r="H435" s="2"/>
     </row>
-    <row r="436" spans="7:8" ht="12.5">
+    <row r="436" spans="7:8">
       <c r="G436" s="2"/>
       <c r="H436" s="2"/>
     </row>
-    <row r="437" spans="7:8" ht="12.5">
+    <row r="437" spans="7:8">
       <c r="G437" s="2"/>
       <c r="H437" s="2"/>
     </row>
-    <row r="438" spans="7:8" ht="12.5">
+    <row r="438" spans="7:8">
       <c r="G438" s="2"/>
       <c r="H438" s="2"/>
     </row>
-    <row r="439" spans="7:8" ht="12.5">
+    <row r="439" spans="7:8">
       <c r="G439" s="2"/>
       <c r="H439" s="2"/>
     </row>
-    <row r="440" spans="7:8" ht="12.5">
+    <row r="440" spans="7:8">
       <c r="G440" s="2"/>
       <c r="H440" s="2"/>
     </row>
-    <row r="441" spans="7:8" ht="12.5">
+    <row r="441" spans="7:8">
       <c r="G441" s="2"/>
       <c r="H441" s="2"/>
     </row>
-    <row r="442" spans="7:8" ht="12.5">
+    <row r="442" spans="7:8">
       <c r="G442" s="2"/>
       <c r="H442" s="2"/>
     </row>
-    <row r="443" spans="7:8" ht="12.5">
+    <row r="443" spans="7:8">
       <c r="G443" s="2"/>
       <c r="H443" s="2"/>
     </row>
-    <row r="444" spans="7:8" ht="12.5">
+    <row r="444" spans="7:8">
       <c r="G444" s="2"/>
       <c r="H444" s="2"/>
     </row>
-    <row r="445" spans="7:8" ht="12.5">
+    <row r="445" spans="7:8">
       <c r="G445" s="2"/>
       <c r="H445" s="2"/>
     </row>
-    <row r="446" spans="7:8" ht="12.5">
+    <row r="446" spans="7:8">
       <c r="G446" s="2"/>
       <c r="H446" s="2"/>
     </row>
-    <row r="447" spans="7:8" ht="12.5">
+    <row r="447" spans="7:8">
       <c r="G447" s="2"/>
       <c r="H447" s="2"/>
     </row>
-    <row r="448" spans="7:8" ht="12.5">
+    <row r="448" spans="7:8">
       <c r="G448" s="2"/>
       <c r="H448" s="2"/>
     </row>
-    <row r="449" spans="7:8" ht="12.5">
+    <row r="449" spans="7:8">
       <c r="G449" s="2"/>
       <c r="H449" s="2"/>
     </row>
-    <row r="450" spans="7:8" ht="12.5">
+    <row r="450" spans="7:8">
       <c r="G450" s="2"/>
       <c r="H450" s="2"/>
     </row>
-    <row r="451" spans="7:8" ht="12.5">
+    <row r="451" spans="7:8">
       <c r="G451" s="2"/>
       <c r="H451" s="2"/>
     </row>
-    <row r="452" spans="7:8" ht="12.5">
+    <row r="452" spans="7:8">
       <c r="G452" s="2"/>
       <c r="H452" s="2"/>
     </row>
-    <row r="453" spans="7:8" ht="12.5">
+    <row r="453" spans="7:8">
       <c r="G453" s="2"/>
       <c r="H453" s="2"/>
     </row>
-    <row r="454" spans="7:8" ht="12.5">
+    <row r="454" spans="7:8">
       <c r="G454" s="2"/>
       <c r="H454" s="2"/>
     </row>
-    <row r="455" spans="7:8" ht="12.5">
+    <row r="455" spans="7:8">
       <c r="G455" s="2"/>
       <c r="H455" s="2"/>
     </row>
-    <row r="456" spans="7:8" ht="12.5">
+    <row r="456" spans="7:8">
       <c r="G456" s="2"/>
       <c r="H456" s="2"/>
     </row>
-    <row r="457" spans="7:8" ht="12.5">
+    <row r="457" spans="7:8">
       <c r="G457" s="2"/>
       <c r="H457" s="2"/>
     </row>
-    <row r="458" spans="7:8" ht="12.5">
+    <row r="458" spans="7:8">
       <c r="G458" s="2"/>
       <c r="H458" s="2"/>
     </row>
-    <row r="459" spans="7:8" ht="12.5">
+    <row r="459" spans="7:8">
       <c r="G459" s="2"/>
       <c r="H459" s="2"/>
     </row>
-    <row r="460" spans="7:8" ht="12.5">
+    <row r="460" spans="7:8">
       <c r="G460" s="2"/>
       <c r="H460" s="2"/>
     </row>
-    <row r="461" spans="7:8" ht="12.5">
+    <row r="461" spans="7:8">
       <c r="G461" s="2"/>
       <c r="H461" s="2"/>
     </row>
-    <row r="462" spans="7:8" ht="12.5">
+    <row r="462" spans="7:8">
       <c r="G462" s="2"/>
       <c r="H462" s="2"/>
     </row>
-    <row r="463" spans="7:8" ht="12.5">
+    <row r="463" spans="7:8">
       <c r="G463" s="2"/>
       <c r="H463" s="2"/>
     </row>
-    <row r="464" spans="7:8" ht="12.5">
+    <row r="464" spans="7:8">
       <c r="G464" s="2"/>
       <c r="H464" s="2"/>
     </row>
-    <row r="465" spans="7:8" ht="12.5">
+    <row r="465" spans="7:8">
       <c r="G465" s="2"/>
       <c r="H465" s="2"/>
     </row>
-    <row r="466" spans="7:8" ht="12.5">
+    <row r="466" spans="7:8">
       <c r="G466" s="2"/>
       <c r="H466" s="2"/>
     </row>
-    <row r="467" spans="7:8" ht="12.5">
+    <row r="467" spans="7:8">
       <c r="G467" s="2"/>
       <c r="H467" s="2"/>
     </row>
-    <row r="468" spans="7:8" ht="12.5">
+    <row r="468" spans="7:8">
       <c r="G468" s="2"/>
       <c r="H468" s="2"/>
     </row>
-    <row r="469" spans="7:8" ht="12.5">
+    <row r="469" spans="7:8">
       <c r="G469" s="2"/>
       <c r="H469" s="2"/>
     </row>
-    <row r="470" spans="7:8" ht="12.5">
+    <row r="470" spans="7:8">
       <c r="G470" s="2"/>
       <c r="H470" s="2"/>
     </row>
-    <row r="471" spans="7:8" ht="12.5">
+    <row r="471" spans="7:8">
       <c r="G471" s="2"/>
       <c r="H471" s="2"/>
     </row>
-    <row r="472" spans="7:8" ht="12.5">
+    <row r="472" spans="7:8">
       <c r="G472" s="2"/>
       <c r="H472" s="2"/>
     </row>
-    <row r="473" spans="7:8" ht="12.5">
+    <row r="473" spans="7:8">
       <c r="G473" s="2"/>
       <c r="H473" s="2"/>
     </row>
-    <row r="474" spans="7:8" ht="12.5">
+    <row r="474" spans="7:8">
       <c r="G474" s="2"/>
       <c r="H474" s="2"/>
     </row>
-    <row r="475" spans="7:8" ht="12.5">
+    <row r="475" spans="7:8">
       <c r="G475" s="2"/>
       <c r="H475" s="2"/>
     </row>
-    <row r="476" spans="7:8" ht="12.5">
+    <row r="476" spans="7:8">
       <c r="G476" s="2"/>
       <c r="H476" s="2"/>
     </row>
-    <row r="477" spans="7:8" ht="12.5">
+    <row r="477" spans="7:8">
       <c r="G477" s="2"/>
       <c r="H477" s="2"/>
     </row>
-    <row r="478" spans="7:8" ht="12.5">
+    <row r="478" spans="7:8">
       <c r="G478" s="2"/>
       <c r="H478" s="2"/>
     </row>
-    <row r="479" spans="7:8" ht="12.5">
+    <row r="479" spans="7:8">
       <c r="G479" s="2"/>
       <c r="H479" s="2"/>
     </row>
-    <row r="480" spans="7:8" ht="12.5">
+    <row r="480" spans="7:8">
       <c r="G480" s="2"/>
       <c r="H480" s="2"/>
     </row>
-    <row r="481" spans="7:8" ht="12.5">
+    <row r="481" spans="7:8">
       <c r="G481" s="2"/>
       <c r="H481" s="2"/>
     </row>
-    <row r="482" spans="7:8" ht="12.5">
+    <row r="482" spans="7:8">
       <c r="G482" s="2"/>
       <c r="H482" s="2"/>
     </row>
-    <row r="483" spans="7:8" ht="12.5">
+    <row r="483" spans="7:8">
       <c r="G483" s="2"/>
       <c r="H483" s="2"/>
     </row>
-    <row r="484" spans="7:8" ht="12.5">
+    <row r="484" spans="7:8">
       <c r="G484" s="2"/>
       <c r="H484" s="2"/>
     </row>
-    <row r="485" spans="7:8" ht="12.5">
+    <row r="485" spans="7:8">
       <c r="G485" s="2"/>
       <c r="H485" s="2"/>
     </row>
-    <row r="486" spans="7:8" ht="12.5">
+    <row r="486" spans="7:8">
       <c r="G486" s="2"/>
       <c r="H486" s="2"/>
     </row>
-    <row r="487" spans="7:8" ht="12.5">
+    <row r="487" spans="7:8">
       <c r="G487" s="2"/>
       <c r="H487" s="2"/>
     </row>
-    <row r="488" spans="7:8" ht="12.5">
+    <row r="488" spans="7:8">
       <c r="G488" s="2"/>
       <c r="H488" s="2"/>
     </row>
-    <row r="489" spans="7:8" ht="12.5">
+    <row r="489" spans="7:8">
       <c r="G489" s="2"/>
       <c r="H489" s="2"/>
     </row>
-    <row r="490" spans="7:8" ht="12.5">
+    <row r="490" spans="7:8">
       <c r="G490" s="2"/>
       <c r="H490" s="2"/>
     </row>
-    <row r="491" spans="7:8" ht="12.5">
+    <row r="491" spans="7:8">
       <c r="G491" s="2"/>
       <c r="H491" s="2"/>
     </row>
-    <row r="492" spans="7:8" ht="12.5">
+    <row r="492" spans="7:8">
       <c r="G492" s="2"/>
       <c r="H492" s="2"/>
     </row>
-    <row r="493" spans="7:8" ht="12.5">
+    <row r="493" spans="7:8">
       <c r="G493" s="2"/>
       <c r="H493" s="2"/>
     </row>
-    <row r="494" spans="7:8" ht="12.5">
+    <row r="494" spans="7:8">
       <c r="G494" s="2"/>
       <c r="H494" s="2"/>
     </row>
-    <row r="495" spans="7:8" ht="12.5">
+    <row r="495" spans="7:8">
       <c r="G495" s="2"/>
       <c r="H495" s="2"/>
     </row>
-    <row r="496" spans="7:8" ht="12.5">
+    <row r="496" spans="7:8">
       <c r="G496" s="2"/>
       <c r="H496" s="2"/>
     </row>
-    <row r="497" spans="7:8" ht="12.5">
+    <row r="497" spans="7:8">
       <c r="G497" s="2"/>
       <c r="H497" s="2"/>
     </row>
-    <row r="498" spans="7:8" ht="12.5">
+    <row r="498" spans="7:8">
       <c r="G498" s="2"/>
       <c r="H498" s="2"/>
     </row>
-    <row r="499" spans="7:8" ht="12.5">
+    <row r="499" spans="7:8">
       <c r="G499" s="2"/>
       <c r="H499" s="2"/>
     </row>
-    <row r="500" spans="7:8" ht="12.5">
+    <row r="500" spans="7:8">
       <c r="G500" s="2"/>
       <c r="H500" s="2"/>
     </row>
-    <row r="501" spans="7:8" ht="12.5">
+    <row r="501" spans="7:8">
       <c r="G501" s="2"/>
       <c r="H501" s="2"/>
     </row>
-    <row r="502" spans="7:8" ht="12.5">
+    <row r="502" spans="7:8">
       <c r="G502" s="2"/>
       <c r="H502" s="2"/>
     </row>
-    <row r="503" spans="7:8" ht="12.5">
+    <row r="503" spans="7:8">
       <c r="G503" s="2"/>
       <c r="H503" s="2"/>
     </row>
-    <row r="504" spans="7:8" ht="12.5">
+    <row r="504" spans="7:8">
       <c r="G504" s="2"/>
       <c r="H504" s="2"/>
     </row>
-    <row r="505" spans="7:8" ht="12.5">
+    <row r="505" spans="7:8">
       <c r="G505" s="2"/>
       <c r="H505" s="2"/>
     </row>
-    <row r="506" spans="7:8" ht="12.5">
+    <row r="506" spans="7:8">
       <c r="G506" s="2"/>
       <c r="H506" s="2"/>
     </row>
-    <row r="507" spans="7:8" ht="12.5">
+    <row r="507" spans="7:8">
       <c r="G507" s="2"/>
       <c r="H507" s="2"/>
     </row>
-    <row r="508" spans="7:8" ht="12.5">
+    <row r="508" spans="7:8">
       <c r="G508" s="2"/>
       <c r="H508" s="2"/>
     </row>
-    <row r="509" spans="7:8" ht="12.5">
+    <row r="509" spans="7:8">
       <c r="G509" s="2"/>
       <c r="H509" s="2"/>
     </row>
-    <row r="510" spans="7:8" ht="12.5">
+    <row r="510" spans="7:8">
       <c r="G510" s="2"/>
       <c r="H510" s="2"/>
     </row>
-    <row r="511" spans="7:8" ht="12.5">
+    <row r="511" spans="7:8">
       <c r="G511" s="2"/>
       <c r="H511" s="2"/>
     </row>
-    <row r="512" spans="7:8" ht="12.5">
+    <row r="512" spans="7:8">
       <c r="G512" s="2"/>
       <c r="H512" s="2"/>
     </row>
-    <row r="513" spans="7:8" ht="12.5">
+    <row r="513" spans="7:8">
       <c r="G513" s="2"/>
       <c r="H513" s="2"/>
     </row>
-    <row r="514" spans="7:8" ht="12.5">
+    <row r="514" spans="7:8">
       <c r="G514" s="2"/>
       <c r="H514" s="2"/>
     </row>
-    <row r="515" spans="7:8" ht="12.5">
+    <row r="515" spans="7:8">
       <c r="G515" s="2"/>
       <c r="H515" s="2"/>
     </row>
-    <row r="516" spans="7:8" ht="12.5">
+    <row r="516" spans="7:8">
       <c r="G516" s="2"/>
       <c r="H516" s="2"/>
     </row>
-    <row r="517" spans="7:8" ht="12.5">
+    <row r="517" spans="7:8">
       <c r="G517" s="2"/>
       <c r="H517" s="2"/>
     </row>
-    <row r="518" spans="7:8" ht="12.5">
+    <row r="518" spans="7:8">
       <c r="G518" s="2"/>
       <c r="H518" s="2"/>
     </row>
-    <row r="519" spans="7:8" ht="12.5">
+    <row r="519" spans="7:8">
       <c r="G519" s="2"/>
       <c r="H519" s="2"/>
     </row>
-    <row r="520" spans="7:8" ht="12.5">
+    <row r="520" spans="7:8">
       <c r="G520" s="2"/>
       <c r="H520" s="2"/>
     </row>
-    <row r="521" spans="7:8" ht="12.5">
+    <row r="521" spans="7:8">
       <c r="G521" s="2"/>
       <c r="H521" s="2"/>
     </row>
-    <row r="522" spans="7:8" ht="12.5">
+    <row r="522" spans="7:8">
       <c r="G522" s="2"/>
       <c r="H522" s="2"/>
     </row>
-    <row r="523" spans="7:8" ht="12.5">
+    <row r="523" spans="7:8">
       <c r="G523" s="2"/>
       <c r="H523" s="2"/>
     </row>
-    <row r="524" spans="7:8" ht="12.5">
+    <row r="524" spans="7:8">
       <c r="G524" s="2"/>
       <c r="H524" s="2"/>
     </row>
-    <row r="525" spans="7:8" ht="12.5">
+    <row r="525" spans="7:8">
       <c r="G525" s="2"/>
       <c r="H525" s="2"/>
     </row>
-    <row r="526" spans="7:8" ht="12.5">
+    <row r="526" spans="7:8">
       <c r="G526" s="2"/>
       <c r="H526" s="2"/>
     </row>
-    <row r="527" spans="7:8" ht="12.5">
+    <row r="527" spans="7:8">
       <c r="G527" s="2"/>
       <c r="H527" s="2"/>
     </row>
-    <row r="528" spans="7:8" ht="12.5">
+    <row r="528" spans="7:8">
       <c r="G528" s="2"/>
       <c r="H528" s="2"/>
     </row>
-    <row r="529" spans="7:8" ht="12.5">
+    <row r="529" spans="7:8">
       <c r="G529" s="2"/>
       <c r="H529" s="2"/>
     </row>
-    <row r="530" spans="7:8" ht="12.5">
+    <row r="530" spans="7:8">
       <c r="G530" s="2"/>
       <c r="H530" s="2"/>
     </row>
-    <row r="531" spans="7:8" ht="12.5">
+    <row r="531" spans="7:8">
       <c r="G531" s="2"/>
       <c r="H531" s="2"/>
     </row>
-    <row r="532" spans="7:8" ht="12.5">
+    <row r="532" spans="7:8">
       <c r="G532" s="2"/>
       <c r="H532" s="2"/>
     </row>
-    <row r="533" spans="7:8" ht="12.5">
+    <row r="533" spans="7:8">
       <c r="G533" s="2"/>
       <c r="H533" s="2"/>
     </row>
-    <row r="534" spans="7:8" ht="12.5">
+    <row r="534" spans="7:8">
       <c r="G534" s="2"/>
       <c r="H534" s="2"/>
     </row>
-    <row r="535" spans="7:8" ht="12.5">
+    <row r="535" spans="7:8">
       <c r="G535" s="2"/>
       <c r="H535" s="2"/>
     </row>
-    <row r="536" spans="7:8" ht="12.5">
+    <row r="536" spans="7:8">
       <c r="G536" s="2"/>
       <c r="H536" s="2"/>
     </row>
-    <row r="537" spans="7:8" ht="12.5">
+    <row r="537" spans="7:8">
       <c r="G537" s="2"/>
       <c r="H537" s="2"/>
     </row>
-    <row r="538" spans="7:8" ht="12.5">
+    <row r="538" spans="7:8">
       <c r="G538" s="2"/>
       <c r="H538" s="2"/>
     </row>
-    <row r="539" spans="7:8" ht="12.5">
+    <row r="539" spans="7:8">
       <c r="G539" s="2"/>
       <c r="H539" s="2"/>
     </row>
-    <row r="540" spans="7:8" ht="12.5">
+    <row r="540" spans="7:8">
       <c r="G540" s="2"/>
       <c r="H540" s="2"/>
     </row>
-    <row r="541" spans="7:8" ht="12.5">
+    <row r="541" spans="7:8">
       <c r="G541" s="2"/>
       <c r="H541" s="2"/>
     </row>
-    <row r="542" spans="7:8" ht="12.5">
+    <row r="542" spans="7:8">
       <c r="G542" s="2"/>
       <c r="H542" s="2"/>
     </row>
-    <row r="543" spans="7:8" ht="12.5">
+    <row r="543" spans="7:8">
       <c r="G543" s="2"/>
       <c r="H543" s="2"/>
     </row>
-    <row r="544" spans="7:8" ht="12.5">
+    <row r="544" spans="7:8">
       <c r="G544" s="2"/>
       <c r="H544" s="2"/>
     </row>
-    <row r="545" spans="7:8" ht="12.5">
+    <row r="545" spans="7:8">
       <c r="G545" s="2"/>
       <c r="H545" s="2"/>
     </row>
-    <row r="546" spans="7:8" ht="12.5">
+    <row r="546" spans="7:8">
       <c r="G546" s="2"/>
       <c r="H546" s="2"/>
     </row>
-    <row r="547" spans="7:8" ht="12.5">
+    <row r="547" spans="7:8">
       <c r="G547" s="2"/>
       <c r="H547" s="2"/>
     </row>
-    <row r="548" spans="7:8" ht="12.5">
+    <row r="548" spans="7:8">
       <c r="G548" s="2"/>
       <c r="H548" s="2"/>
     </row>
-    <row r="549" spans="7:8" ht="12.5">
+    <row r="549" spans="7:8">
       <c r="G549" s="2"/>
       <c r="H549" s="2"/>
     </row>
-    <row r="550" spans="7:8" ht="12.5">
+    <row r="550" spans="7:8">
       <c r="G550" s="2"/>
       <c r="H550" s="2"/>
     </row>
-    <row r="551" spans="7:8" ht="12.5">
+    <row r="551" spans="7:8">
       <c r="G551" s="2"/>
       <c r="H551" s="2"/>
     </row>
-    <row r="552" spans="7:8" ht="12.5">
+    <row r="552" spans="7:8">
       <c r="G552" s="2"/>
       <c r="H552" s="2"/>
     </row>
-    <row r="553" spans="7:8" ht="12.5">
+    <row r="553" spans="7:8">
       <c r="G553" s="2"/>
       <c r="H553" s="2"/>
     </row>
-    <row r="554" spans="7:8" ht="12.5">
+    <row r="554" spans="7:8">
       <c r="G554" s="2"/>
       <c r="H554" s="2"/>
     </row>
-    <row r="555" spans="7:8" ht="12.5">
+    <row r="555" spans="7:8">
       <c r="G555" s="2"/>
       <c r="H555" s="2"/>
     </row>
-    <row r="556" spans="7:8" ht="12.5">
+    <row r="556" spans="7:8">
       <c r="G556" s="2"/>
       <c r="H556" s="2"/>
     </row>
-    <row r="557" spans="7:8" ht="12.5">
+    <row r="557" spans="7:8">
       <c r="G557" s="2"/>
       <c r="H557" s="2"/>
     </row>
-    <row r="558" spans="7:8" ht="12.5">
+    <row r="558" spans="7:8">
       <c r="G558" s="2"/>
       <c r="H558" s="2"/>
     </row>
-    <row r="559" spans="7:8" ht="12.5">
+    <row r="559" spans="7:8">
       <c r="G559" s="2"/>
       <c r="H559" s="2"/>
     </row>
-    <row r="560" spans="7:8" ht="12.5">
+    <row r="560" spans="7:8">
       <c r="G560" s="2"/>
       <c r="H560" s="2"/>
     </row>
-    <row r="561" spans="7:8" ht="12.5">
+    <row r="561" spans="7:8">
       <c r="G561" s="2"/>
       <c r="H561" s="2"/>
     </row>
-    <row r="562" spans="7:8" ht="12.5">
+    <row r="562" spans="7:8">
       <c r="G562" s="2"/>
       <c r="H562" s="2"/>
     </row>
-    <row r="563" spans="7:8" ht="12.5">
+    <row r="563" spans="7:8">
       <c r="G563" s="2"/>
       <c r="H563" s="2"/>
     </row>
-    <row r="564" spans="7:8" ht="12.5">
+    <row r="564" spans="7:8">
       <c r="G564" s="2"/>
       <c r="H564" s="2"/>
     </row>
-    <row r="565" spans="7:8" ht="12.5">
+    <row r="565" spans="7:8">
       <c r="G565" s="2"/>
       <c r="H565" s="2"/>
     </row>
-    <row r="566" spans="7:8" ht="12.5">
+    <row r="566" spans="7:8">
       <c r="G566" s="2"/>
       <c r="H566" s="2"/>
     </row>
-    <row r="567" spans="7:8" ht="12.5">
+    <row r="567" spans="7:8">
       <c r="G567" s="2"/>
       <c r="H567" s="2"/>
     </row>
-    <row r="568" spans="7:8" ht="12.5">
+    <row r="568" spans="7:8">
       <c r="G568" s="2"/>
       <c r="H568" s="2"/>
     </row>
-    <row r="569" spans="7:8" ht="12.5">
+    <row r="569" spans="7:8">
       <c r="G569" s="2"/>
       <c r="H569" s="2"/>
     </row>
-    <row r="570" spans="7:8" ht="12.5">
+    <row r="570" spans="7:8">
       <c r="G570" s="2"/>
       <c r="H570" s="2"/>
     </row>
-    <row r="571" spans="7:8" ht="12.5">
+    <row r="571" spans="7:8">
       <c r="G571" s="2"/>
       <c r="H571" s="2"/>
     </row>
-    <row r="572" spans="7:8" ht="12.5">
+    <row r="572" spans="7:8">
       <c r="G572" s="2"/>
       <c r="H572" s="2"/>
     </row>
-    <row r="573" spans="7:8" ht="12.5">
+    <row r="573" spans="7:8">
       <c r="G573" s="2"/>
       <c r="H573" s="2"/>
     </row>
-    <row r="574" spans="7:8" ht="12.5">
+    <row r="574" spans="7:8">
       <c r="G574" s="2"/>
       <c r="H574" s="2"/>
     </row>
-    <row r="575" spans="7:8" ht="12.5">
+    <row r="575" spans="7:8">
       <c r="G575" s="2"/>
       <c r="H575" s="2"/>
     </row>
-    <row r="576" spans="7:8" ht="12.5">
+    <row r="576" spans="7:8">
       <c r="G576" s="2"/>
       <c r="H576" s="2"/>
     </row>
-    <row r="577" spans="7:8" ht="12.5">
+    <row r="577" spans="7:8">
       <c r="G577" s="2"/>
       <c r="H577" s="2"/>
     </row>
-    <row r="578" spans="7:8" ht="12.5">
+    <row r="578" spans="7:8">
       <c r="G578" s="2"/>
       <c r="H578" s="2"/>
     </row>
-    <row r="579" spans="7:8" ht="12.5">
+    <row r="579" spans="7:8">
       <c r="G579" s="2"/>
       <c r="H579" s="2"/>
     </row>
-    <row r="580" spans="7:8" ht="12.5">
+    <row r="580" spans="7:8">
       <c r="G580" s="2"/>
       <c r="H580" s="2"/>
     </row>
-    <row r="581" spans="7:8" ht="12.5">
+    <row r="581" spans="7:8">
       <c r="G581" s="2"/>
       <c r="H581" s="2"/>
     </row>
-    <row r="582" spans="7:8" ht="12.5">
+    <row r="582" spans="7:8">
       <c r="G582" s="2"/>
       <c r="H582" s="2"/>
     </row>
-    <row r="583" spans="7:8" ht="12.5">
+    <row r="583" spans="7:8">
       <c r="G583" s="2"/>
       <c r="H583" s="2"/>
     </row>
-    <row r="584" spans="7:8" ht="12.5">
+    <row r="584" spans="7:8">
       <c r="G584" s="2"/>
       <c r="H584" s="2"/>
     </row>
-    <row r="585" spans="7:8" ht="12.5">
+    <row r="585" spans="7:8">
       <c r="G585" s="2"/>
       <c r="H585" s="2"/>
     </row>
-    <row r="586" spans="7:8" ht="12.5">
+    <row r="586" spans="7:8">
       <c r="G586" s="2"/>
       <c r="H586" s="2"/>
     </row>
-    <row r="587" spans="7:8" ht="12.5">
+    <row r="587" spans="7:8">
       <c r="G587" s="2"/>
       <c r="H587" s="2"/>
     </row>
-    <row r="588" spans="7:8" ht="12.5">
+    <row r="588" spans="7:8">
       <c r="G588" s="2"/>
       <c r="H588" s="2"/>
     </row>
-    <row r="589" spans="7:8" ht="12.5">
+    <row r="589" spans="7:8">
       <c r="G589" s="2"/>
       <c r="H589" s="2"/>
     </row>
-    <row r="590" spans="7:8" ht="12.5">
+    <row r="590" spans="7:8">
       <c r="G590" s="2"/>
       <c r="H590" s="2"/>
     </row>
-    <row r="591" spans="7:8" ht="12.5">
+    <row r="591" spans="7:8">
       <c r="G591" s="2"/>
       <c r="H591" s="2"/>
     </row>
-    <row r="592" spans="7:8" ht="12.5">
+    <row r="592" spans="7:8">
       <c r="G592" s="2"/>
       <c r="H592" s="2"/>
     </row>
-    <row r="593" spans="7:8" ht="12.5">
+    <row r="593" spans="7:8">
       <c r="G593" s="2"/>
       <c r="H593" s="2"/>
     </row>
-    <row r="594" spans="7:8" ht="12.5">
+    <row r="594" spans="7:8">
       <c r="G594" s="2"/>
       <c r="H594" s="2"/>
     </row>
-    <row r="595" spans="7:8" ht="12.5">
+    <row r="595" spans="7:8">
       <c r="G595" s="2"/>
       <c r="H595" s="2"/>
     </row>
-    <row r="596" spans="7:8" ht="12.5">
+    <row r="596" spans="7:8">
       <c r="G596" s="2"/>
       <c r="H596" s="2"/>
     </row>
-    <row r="597" spans="7:8" ht="12.5">
+    <row r="597" spans="7:8">
       <c r="G597" s="2"/>
       <c r="H597" s="2"/>
     </row>
-    <row r="598" spans="7:8" ht="12.5">
+    <row r="598" spans="7:8">
       <c r="G598" s="2"/>
       <c r="H598" s="2"/>
     </row>
-    <row r="599" spans="7:8" ht="12.5">
+    <row r="599" spans="7:8">
       <c r="G599" s="2"/>
       <c r="H599" s="2"/>
     </row>
-    <row r="600" spans="7:8" ht="12.5">
+    <row r="600" spans="7:8">
       <c r="G600" s="2"/>
       <c r="H600" s="2"/>
     </row>
-    <row r="601" spans="7:8" ht="12.5">
+    <row r="601" spans="7:8">
       <c r="G601" s="2"/>
       <c r="H601" s="2"/>
     </row>
-    <row r="602" spans="7:8" ht="12.5">
+    <row r="602" spans="7:8">
       <c r="G602" s="2"/>
       <c r="H602" s="2"/>
     </row>
-    <row r="603" spans="7:8" ht="12.5">
+    <row r="603" spans="7:8">
       <c r="G603" s="2"/>
       <c r="H603" s="2"/>
     </row>
-    <row r="604" spans="7:8" ht="12.5">
+    <row r="604" spans="7:8">
       <c r="G604" s="2"/>
       <c r="H604" s="2"/>
     </row>
-    <row r="605" spans="7:8" ht="12.5">
+    <row r="605" spans="7:8">
       <c r="G605" s="2"/>
       <c r="H605" s="2"/>
     </row>
-    <row r="606" spans="7:8" ht="12.5">
+    <row r="606" spans="7:8">
       <c r="G606" s="2"/>
       <c r="H606" s="2"/>
     </row>
-    <row r="607" spans="7:8" ht="12.5">
+    <row r="607" spans="7:8">
       <c r="G607" s="2"/>
       <c r="H607" s="2"/>
     </row>
-    <row r="608" spans="7:8" ht="12.5">
+    <row r="608" spans="7:8">
       <c r="G608" s="2"/>
       <c r="H608" s="2"/>
     </row>
-    <row r="609" spans="7:8" ht="12.5">
+    <row r="609" spans="7:8">
       <c r="G609" s="2"/>
       <c r="H609" s="2"/>
     </row>
-    <row r="610" spans="7:8" ht="12.5">
+    <row r="610" spans="7:8">
       <c r="G610" s="2"/>
       <c r="H610" s="2"/>
     </row>
-    <row r="611" spans="7:8" ht="12.5">
+    <row r="611" spans="7:8">
       <c r="G611" s="2"/>
       <c r="H611" s="2"/>
     </row>
-    <row r="612" spans="7:8" ht="12.5">
+    <row r="612" spans="7:8">
       <c r="G612" s="2"/>
       <c r="H612" s="2"/>
     </row>
-    <row r="613" spans="7:8" ht="12.5">
+    <row r="613" spans="7:8">
       <c r="G613" s="2"/>
       <c r="H613" s="2"/>
     </row>
-    <row r="614" spans="7:8" ht="12.5">
+    <row r="614" spans="7:8">
       <c r="G614" s="2"/>
       <c r="H614" s="2"/>
     </row>
-    <row r="615" spans="7:8" ht="12.5">
+    <row r="615" spans="7:8">
       <c r="G615" s="2"/>
       <c r="H615" s="2"/>
     </row>
-    <row r="616" spans="7:8" ht="12.5">
+    <row r="616" spans="7:8">
       <c r="G616" s="2"/>
       <c r="H616" s="2"/>
     </row>
-    <row r="617" spans="7:8" ht="12.5">
+    <row r="617" spans="7:8">
       <c r="G617" s="2"/>
       <c r="H617" s="2"/>
     </row>
-    <row r="618" spans="7:8" ht="12.5">
+    <row r="618" spans="7:8">
       <c r="G618" s="2"/>
       <c r="H618" s="2"/>
     </row>
-    <row r="619" spans="7:8" ht="12.5">
+    <row r="619" spans="7:8">
       <c r="G619" s="2"/>
       <c r="H619" s="2"/>
     </row>
-    <row r="620" spans="7:8" ht="12.5">
+    <row r="620" spans="7:8">
       <c r="G620" s="2"/>
       <c r="H620" s="2"/>
     </row>
-    <row r="621" spans="7:8" ht="12.5">
+    <row r="621" spans="7:8">
       <c r="G621" s="2"/>
       <c r="H621" s="2"/>
     </row>
-    <row r="622" spans="7:8" ht="12.5">
+    <row r="622" spans="7:8">
       <c r="G622" s="2"/>
       <c r="H622" s="2"/>
     </row>
-    <row r="623" spans="7:8" ht="12.5">
+    <row r="623" spans="7:8">
       <c r="G623" s="2"/>
       <c r="H623" s="2"/>
     </row>
-    <row r="624" spans="7:8" ht="12.5">
+    <row r="624" spans="7:8">
       <c r="G624" s="2"/>
       <c r="H624" s="2"/>
     </row>
-    <row r="625" spans="7:8" ht="12.5">
+    <row r="625" spans="7:8">
       <c r="G625" s="2"/>
       <c r="H625" s="2"/>
     </row>
-    <row r="626" spans="7:8" ht="12.5">
+    <row r="626" spans="7:8">
       <c r="G626" s="2"/>
       <c r="H626" s="2"/>
     </row>
-    <row r="627" spans="7:8" ht="12.5">
+    <row r="627" spans="7:8">
       <c r="G627" s="2"/>
       <c r="H627" s="2"/>
     </row>
-    <row r="628" spans="7:8" ht="12.5">
+    <row r="628" spans="7:8">
       <c r="G628" s="2"/>
       <c r="H628" s="2"/>
     </row>
-    <row r="629" spans="7:8" ht="12.5">
+    <row r="629" spans="7:8">
       <c r="G629" s="2"/>
       <c r="H629" s="2"/>
     </row>
-    <row r="630" spans="7:8" ht="12.5">
+    <row r="630" spans="7:8">
       <c r="G630" s="2"/>
       <c r="H630" s="2"/>
     </row>
-    <row r="631" spans="7:8" ht="12.5">
+    <row r="631" spans="7:8">
       <c r="G631" s="2"/>
       <c r="H631" s="2"/>
     </row>
-    <row r="632" spans="7:8" ht="12.5">
+    <row r="632" spans="7:8">
       <c r="G632" s="2"/>
       <c r="H632" s="2"/>
     </row>
-    <row r="633" spans="7:8" ht="12.5">
+    <row r="633" spans="7:8">
       <c r="G633" s="2"/>
       <c r="H633" s="2"/>
     </row>
-    <row r="634" spans="7:8" ht="12.5">
+    <row r="634" spans="7:8">
       <c r="G634" s="2"/>
       <c r="H634" s="2"/>
     </row>
-    <row r="635" spans="7:8" ht="12.5">
+    <row r="635" spans="7:8">
       <c r="G635" s="2"/>
       <c r="H635" s="2"/>
     </row>
-    <row r="636" spans="7:8" ht="12.5">
+    <row r="636" spans="7:8">
       <c r="G636" s="2"/>
       <c r="H636" s="2"/>
     </row>
-    <row r="637" spans="7:8" ht="12.5">
+    <row r="637" spans="7:8">
       <c r="G637" s="2"/>
       <c r="H637" s="2"/>
     </row>
-    <row r="638" spans="7:8" ht="12.5">
+    <row r="638" spans="7:8">
       <c r="G638" s="2"/>
       <c r="H638" s="2"/>
     </row>
-    <row r="639" spans="7:8" ht="12.5">
+    <row r="639" spans="7:8">
       <c r="G639" s="2"/>
       <c r="H639" s="2"/>
     </row>
-    <row r="640" spans="7:8" ht="12.5">
+    <row r="640" spans="7:8">
       <c r="G640" s="2"/>
       <c r="H640" s="2"/>
     </row>
-    <row r="641" spans="7:8" ht="12.5">
+    <row r="641" spans="7:8">
       <c r="G641" s="2"/>
       <c r="H641" s="2"/>
     </row>
-    <row r="642" spans="7:8" ht="12.5">
+    <row r="642" spans="7:8">
       <c r="G642" s="2"/>
       <c r="H642" s="2"/>
     </row>
-    <row r="643" spans="7:8" ht="12.5">
+    <row r="643" spans="7:8">
       <c r="G643" s="2"/>
       <c r="H643" s="2"/>
     </row>
-    <row r="644" spans="7:8" ht="12.5">
+    <row r="644" spans="7:8">
       <c r="G644" s="2"/>
       <c r="H644" s="2"/>
     </row>
-    <row r="645" spans="7:8" ht="12.5">
+    <row r="645" spans="7:8">
       <c r="G645" s="2"/>
       <c r="H645" s="2"/>
     </row>
-    <row r="646" spans="7:8" ht="12.5">
+    <row r="646" spans="7:8">
       <c r="G646" s="2"/>
       <c r="H646" s="2"/>
     </row>
-    <row r="647" spans="7:8" ht="12.5">
+    <row r="647" spans="7:8">
       <c r="G647" s="2"/>
       <c r="H647" s="2"/>
     </row>
-    <row r="648" spans="7:8" ht="12.5">
+    <row r="648" spans="7:8">
       <c r="G648" s="2"/>
       <c r="H648" s="2"/>
     </row>
-    <row r="649" spans="7:8" ht="12.5">
+    <row r="649" spans="7:8">
       <c r="G649" s="2"/>
       <c r="H649" s="2"/>
     </row>
-    <row r="650" spans="7:8" ht="12.5">
+    <row r="650" spans="7:8">
       <c r="G650" s="2"/>
       <c r="H650" s="2"/>
     </row>
-    <row r="651" spans="7:8" ht="12.5">
+    <row r="651" spans="7:8">
       <c r="G651" s="2"/>
       <c r="H651" s="2"/>
     </row>
-    <row r="652" spans="7:8" ht="12.5">
+    <row r="652" spans="7:8">
       <c r="G652" s="2"/>
       <c r="H652" s="2"/>
     </row>
-    <row r="653" spans="7:8" ht="12.5">
+    <row r="653" spans="7:8">
       <c r="G653" s="2"/>
       <c r="H653" s="2"/>
     </row>
-    <row r="654" spans="7:8" ht="12.5">
+    <row r="654" spans="7:8">
       <c r="G654" s="2"/>
       <c r="H654" s="2"/>
     </row>
-    <row r="655" spans="7:8" ht="12.5">
+    <row r="655" spans="7:8">
       <c r="G655" s="2"/>
       <c r="H655" s="2"/>
     </row>
-    <row r="656" spans="7:8" ht="12.5">
+    <row r="656" spans="7:8">
       <c r="G656" s="2"/>
       <c r="H656" s="2"/>
     </row>
-    <row r="657" spans="7:8" ht="12.5">
+    <row r="657" spans="7:8">
       <c r="G657" s="2"/>
       <c r="H657" s="2"/>
     </row>
-    <row r="658" spans="7:8" ht="12.5">
+    <row r="658" spans="7:8">
       <c r="G658" s="2"/>
       <c r="H658" s="2"/>
     </row>
-    <row r="659" spans="7:8" ht="12.5">
+    <row r="659" spans="7:8">
       <c r="G659" s="2"/>
       <c r="H659" s="2"/>
     </row>
-    <row r="660" spans="7:8" ht="12.5">
+    <row r="660" spans="7:8">
       <c r="G660" s="2"/>
       <c r="H660" s="2"/>
     </row>
-    <row r="661" spans="7:8" ht="12.5">
+    <row r="661" spans="7:8">
       <c r="G661" s="2"/>
       <c r="H661" s="2"/>
     </row>
-    <row r="662" spans="7:8" ht="12.5">
+    <row r="662" spans="7:8">
       <c r="G662" s="2"/>
       <c r="H662" s="2"/>
     </row>
-    <row r="663" spans="7:8" ht="12.5">
+    <row r="663" spans="7:8">
       <c r="G663" s="2"/>
       <c r="H663" s="2"/>
     </row>
-    <row r="664" spans="7:8" ht="12.5">
+    <row r="664" spans="7:8">
       <c r="G664" s="2"/>
       <c r="H664" s="2"/>
     </row>
-    <row r="665" spans="7:8" ht="12.5">
+    <row r="665" spans="7:8">
       <c r="G665" s="2"/>
       <c r="H665" s="2"/>
     </row>
-    <row r="666" spans="7:8" ht="12.5">
+    <row r="666" spans="7:8">
       <c r="G666" s="2"/>
       <c r="H666" s="2"/>
     </row>
-    <row r="667" spans="7:8" ht="12.5">
+    <row r="667" spans="7:8">
       <c r="G667" s="2"/>
       <c r="H667" s="2"/>
     </row>
-    <row r="668" spans="7:8" ht="12.5">
+    <row r="668" spans="7:8">
       <c r="G668" s="2"/>
       <c r="H668" s="2"/>
     </row>
-    <row r="669" spans="7:8" ht="12.5">
+    <row r="669" spans="7:8">
       <c r="G669" s="2"/>
       <c r="H669" s="2"/>
     </row>
-    <row r="670" spans="7:8" ht="12.5">
+    <row r="670" spans="7:8">
       <c r="G670" s="2"/>
       <c r="H670" s="2"/>
     </row>
-    <row r="671" spans="7:8" ht="12.5">
+    <row r="671" spans="7:8">
       <c r="G671" s="2"/>
       <c r="H671" s="2"/>
     </row>
-    <row r="672" spans="7:8" ht="12.5">
+    <row r="672" spans="7:8">
       <c r="G672" s="2"/>
       <c r="H672" s="2"/>
     </row>
-    <row r="673" spans="7:8" ht="12.5">
+    <row r="673" spans="7:8">
       <c r="G673" s="2"/>
       <c r="H673" s="2"/>
     </row>
-    <row r="674" spans="7:8" ht="12.5">
+    <row r="674" spans="7:8">
       <c r="G674" s="2"/>
       <c r="H674" s="2"/>
     </row>
-    <row r="675" spans="7:8" ht="12.5">
+    <row r="675" spans="7:8">
       <c r="G675" s="2"/>
       <c r="H675" s="2"/>
     </row>
-    <row r="676" spans="7:8" ht="12.5">
+    <row r="676" spans="7:8">
       <c r="G676" s="2"/>
       <c r="H676" s="2"/>
     </row>
-    <row r="677" spans="7:8" ht="12.5">
+    <row r="677" spans="7:8">
       <c r="G677" s="2"/>
       <c r="H677" s="2"/>
     </row>
-    <row r="678" spans="7:8" ht="12.5">
+    <row r="678" spans="7:8">
       <c r="G678" s="2"/>
       <c r="H678" s="2"/>
     </row>
-    <row r="679" spans="7:8" ht="12.5">
+    <row r="679" spans="7:8">
       <c r="G679" s="2"/>
       <c r="H679" s="2"/>
     </row>
-    <row r="680" spans="7:8" ht="12.5">
+    <row r="680" spans="7:8">
       <c r="G680" s="2"/>
       <c r="H680" s="2"/>
     </row>
-    <row r="681" spans="7:8" ht="12.5">
+    <row r="681" spans="7:8">
       <c r="G681" s="2"/>
       <c r="H681" s="2"/>
     </row>
-    <row r="682" spans="7:8" ht="12.5">
+    <row r="682" spans="7:8">
       <c r="G682" s="2"/>
       <c r="H682" s="2"/>
     </row>
-    <row r="683" spans="7:8" ht="12.5">
+    <row r="683" spans="7:8">
       <c r="G683" s="2"/>
       <c r="H683" s="2"/>
     </row>
-    <row r="684" spans="7:8" ht="12.5">
+    <row r="684" spans="7:8">
       <c r="G684" s="2"/>
       <c r="H684" s="2"/>
     </row>
-    <row r="685" spans="7:8" ht="12.5">
+    <row r="685" spans="7:8">
       <c r="G685" s="2"/>
       <c r="H685" s="2"/>
     </row>
-    <row r="686" spans="7:8" ht="12.5">
+    <row r="686" spans="7:8">
       <c r="G686" s="2"/>
       <c r="H686" s="2"/>
     </row>
-    <row r="687" spans="7:8" ht="12.5">
+    <row r="687" spans="7:8">
       <c r="G687" s="2"/>
       <c r="H687" s="2"/>
     </row>
-    <row r="688" spans="7:8" ht="12.5">
+    <row r="688" spans="7:8">
       <c r="G688" s="2"/>
       <c r="H688" s="2"/>
     </row>
-    <row r="689" spans="7:8" ht="12.5">
+    <row r="689" spans="7:8">
       <c r="G689" s="2"/>
       <c r="H689" s="2"/>
     </row>
-    <row r="690" spans="7:8" ht="12.5">
+    <row r="690" spans="7:8">
       <c r="G690" s="2"/>
       <c r="H690" s="2"/>
     </row>
-    <row r="691" spans="7:8" ht="12.5">
+    <row r="691" spans="7:8">
       <c r="G691" s="2"/>
       <c r="H691" s="2"/>
     </row>
-    <row r="692" spans="7:8" ht="12.5">
+    <row r="692" spans="7:8">
       <c r="G692" s="2"/>
       <c r="H692" s="2"/>
     </row>
-    <row r="693" spans="7:8" ht="12.5">
+    <row r="693" spans="7:8">
       <c r="G693" s="2"/>
       <c r="H693" s="2"/>
     </row>
-    <row r="694" spans="7:8" ht="12.5">
+    <row r="694" spans="7:8">
       <c r="G694" s="2"/>
       <c r="H694" s="2"/>
     </row>
-    <row r="695" spans="7:8" ht="12.5">
+    <row r="695" spans="7:8">
       <c r="G695" s="2"/>
       <c r="H695" s="2"/>
     </row>
-    <row r="696" spans="7:8" ht="12.5">
+    <row r="696" spans="7:8">
       <c r="G696" s="2"/>
       <c r="H696" s="2"/>
     </row>
-    <row r="697" spans="7:8" ht="12.5">
+    <row r="697" spans="7:8">
       <c r="G697" s="2"/>
       <c r="H697" s="2"/>
     </row>
-    <row r="698" spans="7:8" ht="12.5">
+    <row r="698" spans="7:8">
       <c r="G698" s="2"/>
       <c r="H698" s="2"/>
     </row>
-    <row r="699" spans="7:8" ht="12.5">
+    <row r="699" spans="7:8">
       <c r="G699" s="2"/>
       <c r="H699" s="2"/>
     </row>
-    <row r="700" spans="7:8" ht="12.5">
+    <row r="700" spans="7:8">
       <c r="G700" s="2"/>
       <c r="H700" s="2"/>
     </row>
-    <row r="701" spans="7:8" ht="12.5">
+    <row r="701" spans="7:8">
       <c r="G701" s="2"/>
       <c r="H701" s="2"/>
     </row>
-    <row r="702" spans="7:8" ht="12.5">
+    <row r="702" spans="7:8">
       <c r="G702" s="2"/>
       <c r="H702" s="2"/>
     </row>
-    <row r="703" spans="7:8" ht="12.5">
+    <row r="703" spans="7:8">
       <c r="G703" s="2"/>
       <c r="H703" s="2"/>
     </row>
-    <row r="704" spans="7:8" ht="12.5">
+    <row r="704" spans="7:8">
       <c r="G704" s="2"/>
       <c r="H704" s="2"/>
     </row>
-    <row r="705" spans="7:8" ht="12.5">
+    <row r="705" spans="7:8">
       <c r="G705" s="2"/>
       <c r="H705" s="2"/>
     </row>
-    <row r="706" spans="7:8" ht="12.5">
+    <row r="706" spans="7:8">
       <c r="G706" s="2"/>
       <c r="H706" s="2"/>
     </row>
-    <row r="707" spans="7:8" ht="12.5">
+    <row r="707" spans="7:8">
       <c r="G707" s="2"/>
       <c r="H707" s="2"/>
     </row>
-    <row r="708" spans="7:8" ht="12.5">
+    <row r="708" spans="7:8">
       <c r="G708" s="2"/>
       <c r="H708" s="2"/>
     </row>
-    <row r="709" spans="7:8" ht="12.5">
+    <row r="709" spans="7:8">
       <c r="G709" s="2"/>
       <c r="H709" s="2"/>
     </row>
-    <row r="710" spans="7:8" ht="12.5">
+    <row r="710" spans="7:8">
       <c r="G710" s="2"/>
       <c r="H710" s="2"/>
     </row>
-    <row r="711" spans="7:8" ht="12.5">
+    <row r="711" spans="7:8">
       <c r="G711" s="2"/>
       <c r="H711" s="2"/>
     </row>
-    <row r="712" spans="7:8" ht="12.5">
+    <row r="712" spans="7:8">
       <c r="G712" s="2"/>
       <c r="H712" s="2"/>
     </row>
-    <row r="713" spans="7:8" ht="12.5">
+    <row r="713" spans="7:8">
       <c r="G713" s="2"/>
       <c r="H713" s="2"/>
     </row>
-    <row r="714" spans="7:8" ht="12.5">
+    <row r="714" spans="7:8">
       <c r="G714" s="2"/>
       <c r="H714" s="2"/>
     </row>
-    <row r="715" spans="7:8" ht="12.5">
+    <row r="715" spans="7:8">
       <c r="G715" s="2"/>
       <c r="H715" s="2"/>
     </row>
-    <row r="716" spans="7:8" ht="12.5">
+    <row r="716" spans="7:8">
       <c r="G716" s="2"/>
       <c r="H716" s="2"/>
     </row>
-    <row r="717" spans="7:8" ht="12.5">
+    <row r="717" spans="7:8">
       <c r="G717" s="2"/>
       <c r="H717" s="2"/>
     </row>
-    <row r="718" spans="7:8" ht="12.5">
+    <row r="718" spans="7:8">
       <c r="G718" s="2"/>
       <c r="H718" s="2"/>
     </row>
-    <row r="719" spans="7:8" ht="12.5">
+    <row r="719" spans="7:8">
       <c r="G719" s="2"/>
       <c r="H719" s="2"/>
     </row>
-    <row r="720" spans="7:8" ht="12.5">
+    <row r="720" spans="7:8">
       <c r="G720" s="2"/>
       <c r="H720" s="2"/>
     </row>
-    <row r="721" spans="7:8" ht="12.5">
+    <row r="721" spans="7:8">
       <c r="G721" s="2"/>
       <c r="H721" s="2"/>
     </row>
-    <row r="722" spans="7:8" ht="12.5">
+    <row r="722" spans="7:8">
       <c r="G722" s="2"/>
       <c r="H722" s="2"/>
     </row>
-    <row r="723" spans="7:8" ht="12.5">
+    <row r="723" spans="7:8">
       <c r="G723" s="2"/>
       <c r="H723" s="2"/>
     </row>
-    <row r="724" spans="7:8" ht="12.5">
+    <row r="724" spans="7:8">
       <c r="G724" s="2"/>
       <c r="H724" s="2"/>
     </row>
-    <row r="725" spans="7:8" ht="12.5">
+    <row r="725" spans="7:8">
       <c r="G725" s="2"/>
       <c r="H725" s="2"/>
     </row>
-    <row r="726" spans="7:8" ht="12.5">
+    <row r="726" spans="7:8">
       <c r="G726" s="2"/>
       <c r="H726" s="2"/>
     </row>
-    <row r="727" spans="7:8" ht="12.5">
+    <row r="727" spans="7:8">
       <c r="G727" s="2"/>
       <c r="H727" s="2"/>
     </row>
-    <row r="728" spans="7:8" ht="12.5">
+    <row r="728" spans="7:8">
       <c r="G728" s="2"/>
       <c r="H728" s="2"/>
     </row>
-    <row r="729" spans="7:8" ht="12.5">
+    <row r="729" spans="7:8">
       <c r="G729" s="2"/>
       <c r="H729" s="2"/>
     </row>
-    <row r="730" spans="7:8" ht="12.5">
+    <row r="730" spans="7:8">
       <c r="G730" s="2"/>
       <c r="H730" s="2"/>
     </row>
-    <row r="731" spans="7:8" ht="12.5">
+    <row r="731" spans="7:8">
       <c r="G731" s="2"/>
       <c r="H731" s="2"/>
     </row>
-    <row r="732" spans="7:8" ht="12.5">
+    <row r="732" spans="7:8">
       <c r="G732" s="2"/>
       <c r="H732" s="2"/>
     </row>
-    <row r="733" spans="7:8" ht="12.5">
+    <row r="733" spans="7:8">
       <c r="G733" s="2"/>
       <c r="H733" s="2"/>
     </row>
-    <row r="734" spans="7:8" ht="12.5">
+    <row r="734" spans="7:8">
       <c r="G734" s="2"/>
       <c r="H734" s="2"/>
     </row>
-    <row r="735" spans="7:8" ht="12.5">
+    <row r="735" spans="7:8">
       <c r="G735" s="2"/>
       <c r="H735" s="2"/>
     </row>
-    <row r="736" spans="7:8" ht="12.5">
+    <row r="736" spans="7:8">
       <c r="G736" s="2"/>
       <c r="H736" s="2"/>
     </row>
-    <row r="737" spans="7:8" ht="12.5">
+    <row r="737" spans="7:8">
       <c r="G737" s="2"/>
       <c r="H737" s="2"/>
     </row>
-    <row r="738" spans="7:8" ht="12.5">
+    <row r="738" spans="7:8">
       <c r="G738" s="2"/>
       <c r="H738" s="2"/>
     </row>
-    <row r="739" spans="7:8" ht="12.5">
+    <row r="739" spans="7:8">
       <c r="G739" s="2"/>
       <c r="H739" s="2"/>
     </row>
-    <row r="740" spans="7:8" ht="12.5">
+    <row r="740" spans="7:8">
       <c r="G740" s="2"/>
       <c r="H740" s="2"/>
     </row>
-    <row r="741" spans="7:8" ht="12.5">
+    <row r="741" spans="7:8">
       <c r="G741" s="2"/>
       <c r="H741" s="2"/>
     </row>
-    <row r="742" spans="7:8" ht="12.5">
+    <row r="742" spans="7:8">
       <c r="G742" s="2"/>
       <c r="H742" s="2"/>
     </row>
-    <row r="743" spans="7:8" ht="12.5">
+    <row r="743" spans="7:8">
       <c r="G743" s="2"/>
       <c r="H743" s="2"/>
     </row>
-    <row r="744" spans="7:8" ht="12.5">
+    <row r="744" spans="7:8">
       <c r="G744" s="2"/>
       <c r="H744" s="2"/>
     </row>
-    <row r="745" spans="7:8" ht="12.5">
+    <row r="745" spans="7:8">
       <c r="G745" s="2"/>
       <c r="H745" s="2"/>
     </row>
-    <row r="746" spans="7:8" ht="12.5">
+    <row r="746" spans="7:8">
       <c r="G746" s="2"/>
       <c r="H746" s="2"/>
     </row>
-    <row r="747" spans="7:8" ht="12.5">
+    <row r="747" spans="7:8">
       <c r="G747" s="2"/>
       <c r="H747" s="2"/>
     </row>
-    <row r="748" spans="7:8" ht="12.5">
+    <row r="748" spans="7:8">
       <c r="G748" s="2"/>
       <c r="H748" s="2"/>
     </row>
-    <row r="749" spans="7:8" ht="12.5">
+    <row r="749" spans="7:8">
       <c r="G749" s="2"/>
       <c r="H749" s="2"/>
     </row>
-    <row r="750" spans="7:8" ht="12.5">
+    <row r="750" spans="7:8">
       <c r="G750" s="2"/>
       <c r="H750" s="2"/>
     </row>
-    <row r="751" spans="7:8" ht="12.5">
+    <row r="751" spans="7:8">
       <c r="G751" s="2"/>
       <c r="H751" s="2"/>
     </row>
-    <row r="752" spans="7:8" ht="12.5">
+    <row r="752" spans="7:8">
       <c r="G752" s="2"/>
       <c r="H752" s="2"/>
     </row>
-    <row r="753" spans="7:8" ht="12.5">
+    <row r="753" spans="7:8">
       <c r="G753" s="2"/>
       <c r="H753" s="2"/>
     </row>
-    <row r="754" spans="7:8" ht="12.5">
+    <row r="754" spans="7:8">
       <c r="G754" s="2"/>
       <c r="H754" s="2"/>
     </row>
-    <row r="755" spans="7:8" ht="12.5">
+    <row r="755" spans="7:8">
       <c r="G755" s="2"/>
       <c r="H755" s="2"/>
     </row>
-    <row r="756" spans="7:8" ht="12.5">
+    <row r="756" spans="7:8">
       <c r="G756" s="2"/>
       <c r="H756" s="2"/>
     </row>
-    <row r="757" spans="7:8" ht="12.5">
+    <row r="757" spans="7:8">
       <c r="G757" s="2"/>
       <c r="H757" s="2"/>
     </row>
-    <row r="758" spans="7:8" ht="12.5">
+    <row r="758" spans="7:8">
       <c r="G758" s="2"/>
       <c r="H758" s="2"/>
     </row>
-    <row r="759" spans="7:8" ht="12.5">
+    <row r="759" spans="7:8">
       <c r="G759" s="2"/>
       <c r="H759" s="2"/>
     </row>
-    <row r="760" spans="7:8" ht="12.5">
+    <row r="760" spans="7:8">
       <c r="G760" s="2"/>
       <c r="H760" s="2"/>
     </row>
-    <row r="761" spans="7:8" ht="12.5">
+    <row r="761" spans="7:8">
       <c r="G761" s="2"/>
       <c r="H761" s="2"/>
     </row>
-    <row r="762" spans="7:8" ht="12.5">
+    <row r="762" spans="7:8">
       <c r="G762" s="2"/>
       <c r="H762" s="2"/>
     </row>
-    <row r="763" spans="7:8" ht="12.5">
+    <row r="763" spans="7:8">
       <c r="G763" s="2"/>
       <c r="H763" s="2"/>
     </row>
-    <row r="764" spans="7:8" ht="12.5">
+    <row r="764" spans="7:8">
       <c r="G764" s="2"/>
       <c r="H764" s="2"/>
     </row>
-    <row r="765" spans="7:8" ht="12.5">
+    <row r="765" spans="7:8">
       <c r="G765" s="2"/>
       <c r="H765" s="2"/>
     </row>
-    <row r="766" spans="7:8" ht="12.5">
+    <row r="766" spans="7:8">
       <c r="G766" s="2"/>
       <c r="H766" s="2"/>
     </row>
-    <row r="767" spans="7:8" ht="12.5">
+    <row r="767" spans="7:8">
       <c r="G767" s="2"/>
       <c r="H767" s="2"/>
     </row>
-    <row r="768" spans="7:8" ht="12.5">
+    <row r="768" spans="7:8">
       <c r="G768" s="2"/>
       <c r="H768" s="2"/>
     </row>
-    <row r="769" spans="7:8" ht="12.5">
+    <row r="769" spans="7:8">
       <c r="G769" s="2"/>
       <c r="H769" s="2"/>
     </row>
-    <row r="770" spans="7:8" ht="12.5">
+    <row r="770" spans="7:8">
       <c r="G770" s="2"/>
       <c r="H770" s="2"/>
     </row>
-    <row r="771" spans="7:8" ht="12.5">
+    <row r="771" spans="7:8">
       <c r="G771" s="2"/>
       <c r="H771" s="2"/>
     </row>
-    <row r="772" spans="7:8" ht="12.5">
+    <row r="772" spans="7:8">
       <c r="G772" s="2"/>
       <c r="H772" s="2"/>
     </row>
-    <row r="773" spans="7:8" ht="12.5">
+    <row r="773" spans="7:8">
       <c r="G773" s="2"/>
       <c r="H773" s="2"/>
     </row>
-    <row r="774" spans="7:8" ht="12.5">
+    <row r="774" spans="7:8">
       <c r="G774" s="2"/>
       <c r="H774" s="2"/>
     </row>
-    <row r="775" spans="7:8" ht="12.5">
+    <row r="775" spans="7:8">
       <c r="G775" s="2"/>
       <c r="H775" s="2"/>
     </row>
-    <row r="776" spans="7:8" ht="12.5">
+    <row r="776" spans="7:8">
       <c r="G776" s="2"/>
       <c r="H776" s="2"/>
     </row>
-    <row r="777" spans="7:8" ht="12.5">
+    <row r="777" spans="7:8">
       <c r="G777" s="2"/>
       <c r="H777" s="2"/>
     </row>
-    <row r="778" spans="7:8" ht="12.5">
+    <row r="778" spans="7:8">
       <c r="G778" s="2"/>
       <c r="H778" s="2"/>
     </row>
-    <row r="779" spans="7:8" ht="12.5">
+    <row r="779" spans="7:8">
       <c r="G779" s="2"/>
       <c r="H779" s="2"/>
     </row>
-    <row r="780" spans="7:8" ht="12.5">
+    <row r="780" spans="7:8">
       <c r="G780" s="2"/>
       <c r="H780" s="2"/>
     </row>
-    <row r="781" spans="7:8" ht="12.5">
+    <row r="781" spans="7:8">
       <c r="G781" s="2"/>
       <c r="H781" s="2"/>
     </row>
-    <row r="782" spans="7:8" ht="12.5">
+    <row r="782" spans="7:8">
       <c r="G782" s="2"/>
       <c r="H782" s="2"/>
     </row>
-    <row r="783" spans="7:8" ht="12.5">
+    <row r="783" spans="7:8">
       <c r="G783" s="2"/>
       <c r="H783" s="2"/>
     </row>
-    <row r="784" spans="7:8" ht="12.5">
+    <row r="784" spans="7:8">
       <c r="G784" s="2"/>
       <c r="H784" s="2"/>
     </row>
-    <row r="785" spans="7:8" ht="12.5">
+    <row r="785" spans="7:8">
       <c r="G785" s="2"/>
       <c r="H785" s="2"/>
     </row>
-    <row r="786" spans="7:8" ht="12.5">
+    <row r="786" spans="7:8">
       <c r="G786" s="2"/>
       <c r="H786" s="2"/>
     </row>
-    <row r="787" spans="7:8" ht="12.5">
+    <row r="787" spans="7:8">
       <c r="G787" s="2"/>
       <c r="H787" s="2"/>
     </row>
-    <row r="788" spans="7:8" ht="12.5">
+    <row r="788" spans="7:8">
       <c r="G788" s="2"/>
       <c r="H788" s="2"/>
     </row>
-    <row r="789" spans="7:8" ht="12.5">
+    <row r="789" spans="7:8">
       <c r="G789" s="2"/>
       <c r="H789" s="2"/>
     </row>
-    <row r="790" spans="7:8" ht="12.5">
+    <row r="790" spans="7:8">
       <c r="G790" s="2"/>
       <c r="H790" s="2"/>
     </row>
-    <row r="791" spans="7:8" ht="12.5">
+    <row r="791" spans="7:8">
       <c r="G791" s="2"/>
       <c r="H791" s="2"/>
     </row>
-    <row r="792" spans="7:8" ht="12.5">
+    <row r="792" spans="7:8">
       <c r="G792" s="2"/>
       <c r="H792" s="2"/>
     </row>
-    <row r="793" spans="7:8" ht="12.5">
+    <row r="793" spans="7:8">
       <c r="G793" s="2"/>
       <c r="H793" s="2"/>
     </row>
-    <row r="794" spans="7:8" ht="12.5">
+    <row r="794" spans="7:8">
       <c r="G794" s="2"/>
       <c r="H794" s="2"/>
     </row>
-    <row r="795" spans="7:8" ht="12.5">
+    <row r="795" spans="7:8">
       <c r="G795" s="2"/>
       <c r="H795" s="2"/>
     </row>
-    <row r="796" spans="7:8" ht="12.5">
+    <row r="796" spans="7:8">
       <c r="G796" s="2"/>
       <c r="H796" s="2"/>
     </row>
-    <row r="797" spans="7:8" ht="12.5">
+    <row r="797" spans="7:8">
       <c r="G797" s="2"/>
       <c r="H797" s="2"/>
     </row>
-    <row r="798" spans="7:8" ht="12.5">
+    <row r="798" spans="7:8">
       <c r="G798" s="2"/>
       <c r="H798" s="2"/>
     </row>
-    <row r="799" spans="7:8" ht="12.5">
+    <row r="799" spans="7:8">
       <c r="G799" s="2"/>
       <c r="H799" s="2"/>
     </row>
-    <row r="800" spans="7:8" ht="12.5">
+    <row r="800" spans="7:8">
       <c r="G800" s="2"/>
       <c r="H800" s="2"/>
     </row>
-    <row r="801" spans="7:8" ht="12.5">
+    <row r="801" spans="7:8">
       <c r="G801" s="2"/>
       <c r="H801" s="2"/>
     </row>
-    <row r="802" spans="7:8" ht="12.5">
+    <row r="802" spans="7:8">
       <c r="G802" s="2"/>
       <c r="H802" s="2"/>
     </row>
-    <row r="803" spans="7:8" ht="12.5">
+    <row r="803" spans="7:8">
       <c r="G803" s="2"/>
       <c r="H803" s="2"/>
     </row>
-    <row r="804" spans="7:8" ht="12.5">
+    <row r="804" spans="7:8">
       <c r="G804" s="2"/>
       <c r="H804" s="2"/>
     </row>
-    <row r="805" spans="7:8" ht="12.5">
+    <row r="805" spans="7:8">
       <c r="G805" s="2"/>
       <c r="H805" s="2"/>
     </row>
-    <row r="806" spans="7:8" ht="12.5">
+    <row r="806" spans="7:8">
       <c r="G806" s="2"/>
       <c r="H806" s="2"/>
     </row>
-    <row r="807" spans="7:8" ht="12.5">
+    <row r="807" spans="7:8">
       <c r="G807" s="2"/>
       <c r="H807" s="2"/>
     </row>
-    <row r="808" spans="7:8" ht="12.5">
+    <row r="808" spans="7:8">
       <c r="G808" s="2"/>
       <c r="H808" s="2"/>
     </row>
-    <row r="809" spans="7:8" ht="12.5">
+    <row r="809" spans="7:8">
       <c r="G809" s="2"/>
       <c r="H809" s="2"/>
     </row>
-    <row r="810" spans="7:8" ht="12.5">
+    <row r="810" spans="7:8">
       <c r="G810" s="2"/>
       <c r="H810" s="2"/>
     </row>
-    <row r="811" spans="7:8" ht="12.5">
+    <row r="811" spans="7:8">
       <c r="G811" s="2"/>
       <c r="H811" s="2"/>
     </row>
-    <row r="812" spans="7:8" ht="12.5">
+    <row r="812" spans="7:8">
       <c r="G812" s="2"/>
       <c r="H812" s="2"/>
     </row>
-    <row r="813" spans="7:8" ht="12.5">
+    <row r="813" spans="7:8">
       <c r="G813" s="2"/>
       <c r="H813" s="2"/>
     </row>
-    <row r="814" spans="7:8" ht="12.5">
+    <row r="814" spans="7:8">
       <c r="G814" s="2"/>
       <c r="H814" s="2"/>
     </row>
-    <row r="815" spans="7:8" ht="12.5">
+    <row r="815" spans="7:8">
       <c r="G815" s="2"/>
       <c r="H815" s="2"/>
     </row>
-    <row r="816" spans="7:8" ht="12.5">
+    <row r="816" spans="7:8">
       <c r="G816" s="2"/>
       <c r="H816" s="2"/>
     </row>
-    <row r="817" spans="7:8" ht="12.5">
+    <row r="817" spans="7:8">
       <c r="G817" s="2"/>
       <c r="H817" s="2"/>
     </row>
-    <row r="818" spans="7:8" ht="12.5">
+    <row r="818" spans="7:8">
       <c r="G818" s="2"/>
       <c r="H818" s="2"/>
     </row>
-    <row r="819" spans="7:8" ht="12.5">
+    <row r="819" spans="7:8">
       <c r="G819" s="2"/>
       <c r="H819" s="2"/>
     </row>
-    <row r="820" spans="7:8" ht="12.5">
+    <row r="820" spans="7:8">
       <c r="G820" s="2"/>
       <c r="H820" s="2"/>
     </row>
-    <row r="821" spans="7:8" ht="12.5">
+    <row r="821" spans="7:8">
       <c r="G821" s="2"/>
       <c r="H821" s="2"/>
     </row>
-    <row r="822" spans="7:8" ht="12.5">
+    <row r="822" spans="7:8">
       <c r="G822" s="2"/>
       <c r="H822" s="2"/>
     </row>
-    <row r="823" spans="7:8" ht="12.5">
+    <row r="823" spans="7:8">
       <c r="G823" s="2"/>
       <c r="H823" s="2"/>
     </row>
-    <row r="824" spans="7:8" ht="12.5">
+    <row r="824" spans="7:8">
       <c r="G824" s="2"/>
       <c r="H824" s="2"/>
     </row>
-    <row r="825" spans="7:8" ht="12.5">
+    <row r="825" spans="7:8">
       <c r="G825" s="2"/>
       <c r="H825" s="2"/>
     </row>
-    <row r="826" spans="7:8" ht="12.5">
+    <row r="826" spans="7:8">
       <c r="G826" s="2"/>
       <c r="H826" s="2"/>
     </row>
-    <row r="827" spans="7:8" ht="12.5">
+    <row r="827" spans="7:8">
       <c r="G827" s="2"/>
       <c r="H827" s="2"/>
     </row>
-    <row r="828" spans="7:8" ht="12.5">
+    <row r="828" spans="7:8">
       <c r="G828" s="2"/>
       <c r="H828" s="2"/>
     </row>
-    <row r="829" spans="7:8" ht="12.5">
+    <row r="829" spans="7:8">
       <c r="G829" s="2"/>
       <c r="H829" s="2"/>
     </row>
-    <row r="830" spans="7:8" ht="12.5">
+    <row r="830" spans="7:8">
       <c r="G830" s="2"/>
       <c r="H830" s="2"/>
     </row>
-    <row r="831" spans="7:8" ht="12.5">
+    <row r="831" spans="7:8">
       <c r="G831" s="2"/>
       <c r="H831" s="2"/>
     </row>
-    <row r="832" spans="7:8" ht="12.5">
+    <row r="832" spans="7:8">
       <c r="G832" s="2"/>
       <c r="H832" s="2"/>
     </row>
-    <row r="833" spans="7:8" ht="12.5">
+    <row r="833" spans="7:8">
       <c r="G833" s="2"/>
       <c r="H833" s="2"/>
     </row>
-    <row r="834" spans="7:8" ht="12.5">
+    <row r="834" spans="7:8">
       <c r="G834" s="2"/>
       <c r="H834" s="2"/>
     </row>
-    <row r="835" spans="7:8" ht="12.5">
+    <row r="835" spans="7:8">
       <c r="G835" s="2"/>
       <c r="H835" s="2"/>
     </row>
-    <row r="836" spans="7:8" ht="12.5">
+    <row r="836" spans="7:8">
       <c r="G836" s="2"/>
       <c r="H836" s="2"/>
     </row>
-    <row r="837" spans="7:8" ht="12.5">
+    <row r="837" spans="7:8">
       <c r="G837" s="2"/>
       <c r="H837" s="2"/>
     </row>
-    <row r="838" spans="7:8" ht="12.5">
+    <row r="838" spans="7:8">
       <c r="G838" s="2"/>
       <c r="H838" s="2"/>
     </row>
-    <row r="839" spans="7:8" ht="12.5">
+    <row r="839" spans="7:8">
       <c r="G839" s="2"/>
       <c r="H839" s="2"/>
     </row>
-    <row r="840" spans="7:8" ht="12.5">
+    <row r="840" spans="7:8">
       <c r="G840" s="2"/>
       <c r="H840" s="2"/>
     </row>
-    <row r="841" spans="7:8" ht="12.5">
+    <row r="841" spans="7:8">
       <c r="G841" s="2"/>
       <c r="H841" s="2"/>
     </row>
-    <row r="842" spans="7:8" ht="12.5">
+    <row r="842" spans="7:8">
       <c r="G842" s="2"/>
       <c r="H842" s="2"/>
     </row>
-    <row r="843" spans="7:8" ht="12.5">
+    <row r="843" spans="7:8">
       <c r="G843" s="2"/>
       <c r="H843" s="2"/>
     </row>
-    <row r="844" spans="7:8" ht="12.5">
+    <row r="844" spans="7:8">
       <c r="G844" s="2"/>
       <c r="H844" s="2"/>
     </row>
-    <row r="845" spans="7:8" ht="12.5">
+    <row r="845" spans="7:8">
       <c r="G845" s="2"/>
       <c r="H845" s="2"/>
     </row>
-    <row r="846" spans="7:8" ht="12.5">
+    <row r="846" spans="7:8">
       <c r="G846" s="2"/>
       <c r="H846" s="2"/>
     </row>
-    <row r="847" spans="7:8" ht="12.5">
+    <row r="847" spans="7:8">
       <c r="G847" s="2"/>
       <c r="H847" s="2"/>
     </row>
-    <row r="848" spans="7:8" ht="12.5">
+    <row r="848" spans="7:8">
       <c r="G848" s="2"/>
       <c r="H848" s="2"/>
     </row>
-    <row r="849" spans="7:8" ht="12.5">
+    <row r="849" spans="7:8">
       <c r="G849" s="2"/>
       <c r="H849" s="2"/>
     </row>
-    <row r="850" spans="7:8" ht="12.5">
+    <row r="850" spans="7:8">
       <c r="G850" s="2"/>
       <c r="H850" s="2"/>
     </row>
-    <row r="851" spans="7:8" ht="12.5">
+    <row r="851" spans="7:8">
       <c r="G851" s="2"/>
       <c r="H851" s="2"/>
     </row>
-    <row r="852" spans="7:8" ht="12.5">
+    <row r="852" spans="7:8">
       <c r="G852" s="2"/>
       <c r="H852" s="2"/>
     </row>
-    <row r="853" spans="7:8" ht="12.5">
+    <row r="853" spans="7:8">
       <c r="G853" s="2"/>
       <c r="H853" s="2"/>
     </row>
-    <row r="854" spans="7:8" ht="12.5">
+    <row r="854" spans="7:8">
       <c r="G854" s="2"/>
       <c r="H854" s="2"/>
     </row>
-    <row r="855" spans="7:8" ht="12.5">
+    <row r="855" spans="7:8">
       <c r="G855" s="2"/>
       <c r="H855" s="2"/>
     </row>
-    <row r="856" spans="7:8" ht="12.5">
+    <row r="856" spans="7:8">
       <c r="G856" s="2"/>
       <c r="H856" s="2"/>
     </row>
-    <row r="857" spans="7:8" ht="12.5">
+    <row r="857" spans="7:8">
       <c r="G857" s="2"/>
       <c r="H857" s="2"/>
     </row>
-    <row r="858" spans="7:8" ht="12.5">
+    <row r="858" spans="7:8">
       <c r="G858" s="2"/>
       <c r="H858" s="2"/>
     </row>
-    <row r="859" spans="7:8" ht="12.5">
+    <row r="859" spans="7:8">
       <c r="G859" s="2"/>
       <c r="H859" s="2"/>
     </row>
-    <row r="860" spans="7:8" ht="12.5">
+    <row r="860" spans="7:8">
       <c r="G860" s="2"/>
       <c r="H860" s="2"/>
     </row>
-    <row r="861" spans="7:8" ht="12.5">
+    <row r="861" spans="7:8">
       <c r="G861" s="2"/>
       <c r="H861" s="2"/>
     </row>
-    <row r="862" spans="7:8" ht="12.5">
+    <row r="862" spans="7:8">
       <c r="G862" s="2"/>
       <c r="H862" s="2"/>
     </row>
-    <row r="863" spans="7:8" ht="12.5">
+    <row r="863" spans="7:8">
       <c r="G863" s="2"/>
       <c r="H863" s="2"/>
     </row>
-    <row r="864" spans="7:8" ht="12.5">
+    <row r="864" spans="7:8">
       <c r="G864" s="2"/>
       <c r="H864" s="2"/>
     </row>
-    <row r="865" spans="7:8" ht="12.5">
+    <row r="865" spans="7:8">
       <c r="G865" s="2"/>
       <c r="H865" s="2"/>
     </row>
-    <row r="866" spans="7:8" ht="12.5">
+    <row r="866" spans="7:8">
       <c r="G866" s="2"/>
       <c r="H866" s="2"/>
     </row>
-    <row r="867" spans="7:8" ht="12.5">
+    <row r="867" spans="7:8">
       <c r="G867" s="2"/>
       <c r="H867" s="2"/>
     </row>
-    <row r="868" spans="7:8" ht="12.5">
+    <row r="868" spans="7:8">
       <c r="G868" s="2"/>
       <c r="H868" s="2"/>
     </row>
-    <row r="869" spans="7:8" ht="12.5">
+    <row r="869" spans="7:8">
       <c r="G869" s="2"/>
       <c r="H869" s="2"/>
     </row>
-    <row r="870" spans="7:8" ht="12.5">
+    <row r="870" spans="7:8">
       <c r="G870" s="2"/>
       <c r="H870" s="2"/>
     </row>
-    <row r="871" spans="7:8" ht="12.5">
+    <row r="871" spans="7:8">
       <c r="G871" s="2"/>
       <c r="H871" s="2"/>
     </row>
-    <row r="872" spans="7:8" ht="12.5">
+    <row r="872" spans="7:8">
       <c r="G872" s="2"/>
       <c r="H872" s="2"/>
     </row>
-    <row r="873" spans="7:8" ht="12.5">
+    <row r="873" spans="7:8">
       <c r="G873" s="2"/>
       <c r="H873" s="2"/>
     </row>
-    <row r="874" spans="7:8" ht="12.5">
+    <row r="874" spans="7:8">
       <c r="G874" s="2"/>
       <c r="H874" s="2"/>
     </row>
-    <row r="875" spans="7:8" ht="12.5">
+    <row r="875" spans="7:8">
       <c r="G875" s="2"/>
       <c r="H875" s="2"/>
     </row>
-    <row r="876" spans="7:8" ht="12.5">
+    <row r="876" spans="7:8">
       <c r="G876" s="2"/>
       <c r="H876" s="2"/>
     </row>
-    <row r="877" spans="7:8" ht="12.5">
+    <row r="877" spans="7:8">
       <c r="G877" s="2"/>
       <c r="H877" s="2"/>
     </row>
-    <row r="878" spans="7:8" ht="12.5">
+    <row r="878" spans="7:8">
       <c r="G878" s="2"/>
       <c r="H878" s="2"/>
     </row>
-    <row r="879" spans="7:8" ht="12.5">
+    <row r="879" spans="7:8">
       <c r="G879" s="2"/>
       <c r="H879" s="2"/>
     </row>
-    <row r="880" spans="7:8" ht="12.5">
+    <row r="880" spans="7:8">
       <c r="G880" s="2"/>
       <c r="H880" s="2"/>
     </row>
-    <row r="881" spans="7:8" ht="12.5">
+    <row r="881" spans="7:8">
       <c r="G881" s="2"/>
       <c r="H881" s="2"/>
     </row>
-    <row r="882" spans="7:8" ht="12.5">
+    <row r="882" spans="7:8">
       <c r="G882" s="2"/>
       <c r="H882" s="2"/>
     </row>
-    <row r="883" spans="7:8" ht="12.5">
+    <row r="883" spans="7:8">
       <c r="G883" s="2"/>
       <c r="H883" s="2"/>
     </row>
-    <row r="884" spans="7:8" ht="12.5">
+    <row r="884" spans="7:8">
       <c r="G884" s="2"/>
       <c r="H884" s="2"/>
     </row>
-    <row r="885" spans="7:8" ht="12.5">
+    <row r="885" spans="7:8">
       <c r="G885" s="2"/>
       <c r="H885" s="2"/>
     </row>
-    <row r="886" spans="7:8" ht="12.5">
+    <row r="886" spans="7:8">
       <c r="G886" s="2"/>
       <c r="H886" s="2"/>
     </row>
-    <row r="887" spans="7:8" ht="12.5">
+    <row r="887" spans="7:8">
       <c r="G887" s="2"/>
       <c r="H887" s="2"/>
     </row>
-    <row r="888" spans="7:8" ht="12.5">
+    <row r="888" spans="7:8">
       <c r="G888" s="2"/>
       <c r="H888" s="2"/>
     </row>
-    <row r="889" spans="7:8" ht="12.5">
+    <row r="889" spans="7:8">
       <c r="G889" s="2"/>
       <c r="H889" s="2"/>
     </row>
-    <row r="890" spans="7:8" ht="12.5">
+    <row r="890" spans="7:8">
       <c r="G890" s="2"/>
       <c r="H890" s="2"/>
     </row>
-    <row r="891" spans="7:8" ht="12.5">
+    <row r="891" spans="7:8">
       <c r="G891" s="2"/>
       <c r="H891" s="2"/>
     </row>
-    <row r="892" spans="7:8" ht="12.5">
+    <row r="892" spans="7:8">
       <c r="G892" s="2"/>
       <c r="H892" s="2"/>
     </row>
-    <row r="893" spans="7:8" ht="12.5">
+    <row r="893" spans="7:8">
       <c r="G893" s="2"/>
       <c r="H893" s="2"/>
     </row>
-    <row r="894" spans="7:8" ht="12.5">
+    <row r="894" spans="7:8">
       <c r="G894" s="2"/>
       <c r="H894" s="2"/>
     </row>
-    <row r="895" spans="7:8" ht="12.5">
+    <row r="895" spans="7:8">
       <c r="G895" s="2"/>
       <c r="H895" s="2"/>
     </row>
-    <row r="896" spans="7:8" ht="12.5">
+    <row r="896" spans="7:8">
       <c r="G896" s="2"/>
       <c r="H896" s="2"/>
     </row>
-    <row r="897" spans="7:8" ht="12.5">
+    <row r="897" spans="7:8">
       <c r="G897" s="2"/>
       <c r="H897" s="2"/>
     </row>
-    <row r="898" spans="7:8" ht="12.5">
+    <row r="898" spans="7:8">
       <c r="G898" s="2"/>
       <c r="H898" s="2"/>
     </row>
-    <row r="899" spans="7:8" ht="12.5">
+    <row r="899" spans="7:8">
       <c r="G899" s="2"/>
       <c r="H899" s="2"/>
     </row>
-    <row r="900" spans="7:8" ht="12.5">
+    <row r="900" spans="7:8">
       <c r="G900" s="2"/>
       <c r="H900" s="2"/>
     </row>
-    <row r="901" spans="7:8" ht="12.5">
+    <row r="901" spans="7:8">
       <c r="G901" s="2"/>
       <c r="H901" s="2"/>
     </row>
-    <row r="902" spans="7:8" ht="12.5">
+    <row r="902" spans="7:8">
       <c r="G902" s="2"/>
       <c r="H902" s="2"/>
     </row>
-    <row r="903" spans="7:8" ht="12.5">
+    <row r="903" spans="7:8">
       <c r="G903" s="2"/>
       <c r="H903" s="2"/>
     </row>
-    <row r="904" spans="7:8" ht="12.5">
+    <row r="904" spans="7:8">
       <c r="G904" s="2"/>
       <c r="H904" s="2"/>
     </row>
-    <row r="905" spans="7:8" ht="12.5">
+    <row r="905" spans="7:8">
       <c r="G905" s="2"/>
       <c r="H905" s="2"/>
     </row>
-    <row r="906" spans="7:8" ht="12.5">
+    <row r="906" spans="7:8">
       <c r="G906" s="2"/>
       <c r="H906" s="2"/>
     </row>
-    <row r="907" spans="7:8" ht="12.5">
+    <row r="907" spans="7:8">
       <c r="G907" s="2"/>
       <c r="H907" s="2"/>
     </row>
-    <row r="908" spans="7:8" ht="12.5">
+    <row r="908" spans="7:8">
       <c r="G908" s="2"/>
       <c r="H908" s="2"/>
     </row>
-    <row r="909" spans="7:8" ht="12.5">
+    <row r="909" spans="7:8">
       <c r="G909" s="2"/>
       <c r="H909" s="2"/>
     </row>
-    <row r="910" spans="7:8" ht="12.5">
+    <row r="910" spans="7:8">
       <c r="G910" s="2"/>
       <c r="H910" s="2"/>
     </row>
-    <row r="911" spans="7:8" ht="12.5">
+    <row r="911" spans="7:8">
       <c r="G911" s="2"/>
       <c r="H911" s="2"/>
     </row>
-    <row r="912" spans="7:8" ht="12.5">
+    <row r="912" spans="7:8">
       <c r="G912" s="2"/>
       <c r="H912" s="2"/>
     </row>
-    <row r="913" spans="7:8" ht="12.5">
+    <row r="913" spans="7:8">
       <c r="G913" s="2"/>
       <c r="H913" s="2"/>
     </row>
-    <row r="914" spans="7:8" ht="12.5">
+    <row r="914" spans="7:8">
       <c r="G914" s="2"/>
       <c r="H914" s="2"/>
     </row>
-    <row r="915" spans="7:8" ht="12.5">
+    <row r="915" spans="7:8">
       <c r="G915" s="2"/>
       <c r="H915" s="2"/>
     </row>
-    <row r="916" spans="7:8" ht="12.5">
+    <row r="916" spans="7:8">
       <c r="G916" s="2"/>
       <c r="H916" s="2"/>
     </row>
-    <row r="917" spans="7:8" ht="12.5">
+    <row r="917" spans="7:8">
       <c r="G917" s="2"/>
       <c r="H917" s="2"/>
     </row>
-    <row r="918" spans="7:8" ht="12.5">
+    <row r="918" spans="7:8">
       <c r="G918" s="2"/>
       <c r="H918" s="2"/>
     </row>
-    <row r="919" spans="7:8" ht="12.5">
+    <row r="919" spans="7:8">
       <c r="G919" s="2"/>
       <c r="H919" s="2"/>
     </row>
-    <row r="920" spans="7:8" ht="12.5">
+    <row r="920" spans="7:8">
       <c r="G920" s="2"/>
       <c r="H920" s="2"/>
     </row>
-    <row r="921" spans="7:8" ht="12.5">
+    <row r="921" spans="7:8">
       <c r="G921" s="2"/>
       <c r="H921" s="2"/>
     </row>
-    <row r="922" spans="7:8" ht="12.5">
+    <row r="922" spans="7:8">
       <c r="G922" s="2"/>
       <c r="H922" s="2"/>
     </row>
-    <row r="923" spans="7:8" ht="12.5">
+    <row r="923" spans="7:8">
       <c r="G923" s="2"/>
       <c r="H923" s="2"/>
     </row>
-    <row r="924" spans="7:8" ht="12.5">
+    <row r="924" spans="7:8">
       <c r="G924" s="2"/>
       <c r="H924" s="2"/>
     </row>
-    <row r="925" spans="7:8" ht="12.5">
+    <row r="925" spans="7:8">
       <c r="G925" s="2"/>
       <c r="H925" s="2"/>
     </row>
-    <row r="926" spans="7:8" ht="12.5">
+    <row r="926" spans="7:8">
       <c r="G926" s="2"/>
       <c r="H926" s="2"/>
     </row>
-    <row r="927" spans="7:8" ht="12.5">
+    <row r="927" spans="7:8">
       <c r="G927" s="2"/>
       <c r="H927" s="2"/>
     </row>
-    <row r="928" spans="7:8" ht="12.5">
+    <row r="928" spans="7:8">
       <c r="G928" s="2"/>
       <c r="H928" s="2"/>
     </row>
-    <row r="929" spans="7:8" ht="12.5">
+    <row r="929" spans="7:8">
       <c r="G929" s="2"/>
       <c r="H929" s="2"/>
     </row>
-    <row r="930" spans="7:8" ht="12.5">
+    <row r="930" spans="7:8">
       <c r="G930" s="2"/>
       <c r="H930" s="2"/>
     </row>
-    <row r="931" spans="7:8" ht="12.5">
+    <row r="931" spans="7:8">
       <c r="G931" s="2"/>
       <c r="H931" s="2"/>
     </row>
-    <row r="932" spans="7:8" ht="12.5">
+    <row r="932" spans="7:8">
       <c r="G932" s="2"/>
       <c r="H932" s="2"/>
     </row>
-    <row r="933" spans="7:8" ht="12.5">
+    <row r="933" spans="7:8">
       <c r="G933" s="2"/>
       <c r="H933" s="2"/>
     </row>
-    <row r="934" spans="7:8" ht="12.5">
+    <row r="934" spans="7:8">
       <c r="G934" s="2"/>
       <c r="H934" s="2"/>
     </row>
-    <row r="935" spans="7:8" ht="12.5">
+    <row r="935" spans="7:8">
       <c r="G935" s="2"/>
       <c r="H935" s="2"/>
     </row>
-    <row r="936" spans="7:8" ht="12.5">
+    <row r="936" spans="7:8">
       <c r="G936" s="2"/>
       <c r="H936" s="2"/>
     </row>
-    <row r="937" spans="7:8" ht="12.5">
+    <row r="937" spans="7:8">
       <c r="G937" s="2"/>
       <c r="H937" s="2"/>
     </row>
-    <row r="938" spans="7:8" ht="12.5">
+    <row r="938" spans="7:8">
       <c r="G938" s="2"/>
       <c r="H938" s="2"/>
     </row>
-    <row r="939" spans="7:8" ht="12.5">
+    <row r="939" spans="7:8">
       <c r="G939" s="2"/>
       <c r="H939" s="2"/>
     </row>
-    <row r="940" spans="7:8" ht="12.5">
+    <row r="940" spans="7:8">
       <c r="G940" s="2"/>
       <c r="H940" s="2"/>
     </row>
-    <row r="941" spans="7:8" ht="12.5">
+    <row r="941" spans="7:8">
       <c r="G941" s="2"/>
       <c r="H941" s="2"/>
     </row>
-    <row r="942" spans="7:8" ht="12.5">
+    <row r="942" spans="7:8">
       <c r="G942" s="2"/>
       <c r="H942" s="2"/>
     </row>
-    <row r="943" spans="7:8" ht="12.5">
+    <row r="943" spans="7:8">
       <c r="G943" s="2"/>
       <c r="H943" s="2"/>
     </row>
-    <row r="944" spans="7:8" ht="12.5">
+    <row r="944" spans="7:8">
       <c r="G944" s="2"/>
       <c r="H944" s="2"/>
     </row>
-    <row r="945" spans="7:8" ht="12.5">
+    <row r="945" spans="7:8">
       <c r="G945" s="2"/>
       <c r="H945" s="2"/>
     </row>
-    <row r="946" spans="7:8" ht="12.5">
+    <row r="946" spans="7:8">
       <c r="G946" s="2"/>
       <c r="H946" s="2"/>
     </row>
-    <row r="947" spans="7:8" ht="12.5">
+    <row r="947" spans="7:8">
       <c r="G947" s="2"/>
       <c r="H947" s="2"/>
     </row>
-    <row r="948" spans="7:8" ht="12.5">
+    <row r="948" spans="7:8">
       <c r="G948" s="2"/>
       <c r="H948" s="2"/>
     </row>
-    <row r="949" spans="7:8" ht="12.5">
+    <row r="949" spans="7:8">
       <c r="G949" s="2"/>
       <c r="H949" s="2"/>
     </row>
-    <row r="950" spans="7:8" ht="12.5">
+    <row r="950" spans="7:8">
       <c r="G950" s="2"/>
       <c r="H950" s="2"/>
     </row>
-    <row r="951" spans="7:8" ht="12.5">
+    <row r="951" spans="7:8">
       <c r="G951" s="2"/>
       <c r="H951" s="2"/>
     </row>
-    <row r="952" spans="7:8" ht="12.5">
+    <row r="952" spans="7:8">
       <c r="G952" s="2"/>
       <c r="H952" s="2"/>
     </row>
-    <row r="953" spans="7:8" ht="12.5">
+    <row r="953" spans="7:8">
       <c r="G953" s="2"/>
       <c r="H953" s="2"/>
     </row>
-    <row r="954" spans="7:8" ht="12.5">
+    <row r="954" spans="7:8">
       <c r="G954" s="2"/>
       <c r="H954" s="2"/>
     </row>
-    <row r="955" spans="7:8" ht="12.5">
+    <row r="955" spans="7:8">
       <c r="G955" s="2"/>
       <c r="H955" s="2"/>
     </row>
-    <row r="956" spans="7:8" ht="12.5">
+    <row r="956" spans="7:8">
       <c r="G956" s="2"/>
       <c r="H956" s="2"/>
     </row>
-    <row r="957" spans="7:8" ht="12.5">
+    <row r="957" spans="7:8">
       <c r="G957" s="2"/>
       <c r="H957" s="2"/>
     </row>
-    <row r="958" spans="7:8" ht="12.5">
+    <row r="958" spans="7:8">
       <c r="G958" s="2"/>
       <c r="H958" s="2"/>
     </row>
-    <row r="959" spans="7:8" ht="12.5">
+    <row r="959" spans="7:8">
       <c r="G959" s="2"/>
       <c r="H959" s="2"/>
     </row>
-    <row r="960" spans="7:8" ht="12.5">
+    <row r="960" spans="7:8">
       <c r="G960" s="2"/>
       <c r="H960" s="2"/>
     </row>
-    <row r="961" spans="7:8" ht="12.5">
+    <row r="961" spans="7:8">
       <c r="G961" s="2"/>
       <c r="H961" s="2"/>
     </row>
-    <row r="962" spans="7:8" ht="12.5">
+    <row r="962" spans="7:8">
       <c r="G962" s="2"/>
       <c r="H962" s="2"/>
     </row>
-    <row r="963" spans="7:8" ht="12.5">
+    <row r="963" spans="7:8">
       <c r="G963" s="2"/>
       <c r="H963" s="2"/>
     </row>
-    <row r="964" spans="7:8" ht="12.5">
+    <row r="964" spans="7:8">
       <c r="G964" s="2"/>
       <c r="H964" s="2"/>
     </row>
-    <row r="965" spans="7:8" ht="12.5">
+    <row r="965" spans="7:8">
       <c r="G965" s="2"/>
       <c r="H965" s="2"/>
     </row>
-    <row r="966" spans="7:8" ht="12.5">
+    <row r="966" spans="7:8">
       <c r="G966" s="2"/>
       <c r="H966" s="2"/>
     </row>
-    <row r="967" spans="7:8" ht="12.5">
+    <row r="967" spans="7:8">
       <c r="G967" s="2"/>
       <c r="H967" s="2"/>
     </row>
-    <row r="968" spans="7:8" ht="12.5">
+    <row r="968" spans="7:8">
       <c r="G968" s="2"/>
       <c r="H968" s="2"/>
     </row>
-    <row r="969" spans="7:8" ht="12.5">
+    <row r="969" spans="7:8">
       <c r="G969" s="2"/>
       <c r="H969" s="2"/>
     </row>
-    <row r="970" spans="7:8" ht="12.5">
+    <row r="970" spans="7:8">
       <c r="G970" s="2"/>
       <c r="H970" s="2"/>
     </row>
-    <row r="971" spans="7:8" ht="12.5">
+    <row r="971" spans="7:8">
       <c r="G971" s="2"/>
       <c r="H971" s="2"/>
     </row>
-    <row r="972" spans="7:8" ht="12.5">
+    <row r="972" spans="7:8">
       <c r="G972" s="2"/>
       <c r="H972" s="2"/>
     </row>
-    <row r="973" spans="7:8" ht="12.5">
+    <row r="973" spans="7:8">
       <c r="G973" s="2"/>
       <c r="H973" s="2"/>
     </row>
-    <row r="974" spans="7:8" ht="12.5">
+    <row r="974" spans="7:8">
       <c r="G974" s="2"/>
       <c r="H974" s="2"/>
     </row>
-    <row r="975" spans="7:8" ht="12.5">
+    <row r="975" spans="7:8">
       <c r="G975" s="2"/>
       <c r="H975" s="2"/>
     </row>
-    <row r="976" spans="7:8" ht="12.5">
+    <row r="976" spans="7:8">
       <c r="G976" s="2"/>
       <c r="H976" s="2"/>
     </row>
-    <row r="977" spans="7:8" ht="12.5">
+    <row r="977" spans="7:8">
       <c r="G977" s="2"/>
       <c r="H977" s="2"/>
     </row>
-    <row r="978" spans="7:8" ht="12.5">
+    <row r="978" spans="7:8">
       <c r="G978" s="2"/>
       <c r="H978" s="2"/>
     </row>
-    <row r="979" spans="7:8" ht="12.5">
+    <row r="979" spans="7:8">
       <c r="G979" s="2"/>
       <c r="H979" s="2"/>
     </row>
-    <row r="980" spans="7:8" ht="12.5">
+    <row r="980" spans="7:8">
       <c r="G980" s="2"/>
       <c r="H980" s="2"/>
     </row>
-    <row r="981" spans="7:8" ht="12.5">
+    <row r="981" spans="7:8">
       <c r="G981" s="2"/>
       <c r="H981" s="2"/>
     </row>
-    <row r="982" spans="7:8" ht="12.5">
+    <row r="982" spans="7:8">
       <c r="G982" s="2"/>
       <c r="H982" s="2"/>
     </row>
-    <row r="983" spans="7:8" ht="12.5">
+    <row r="983" spans="7:8">
       <c r="G983" s="2"/>
       <c r="H983" s="2"/>
     </row>
-    <row r="984" spans="7:8" ht="12.5">
+    <row r="984" spans="7:8">
       <c r="G984" s="2"/>
       <c r="H984" s="2"/>
     </row>
-    <row r="985" spans="7:8" ht="12.5">
+    <row r="985" spans="7:8">
       <c r="G985" s="2"/>
       <c r="H985" s="2"/>
     </row>
-    <row r="986" spans="7:8" ht="12.5">
+    <row r="986" spans="7:8">
       <c r="G986" s="2"/>
       <c r="H986" s="2"/>
     </row>
-    <row r="987" spans="7:8" ht="12.5">
+    <row r="987" spans="7:8">
       <c r="G987" s="2"/>
       <c r="H987" s="2"/>
     </row>
-    <row r="988" spans="7:8" ht="12.5">
+    <row r="988" spans="7:8">
       <c r="G988" s="2"/>
       <c r="H988" s="2"/>
     </row>
-    <row r="989" spans="7:8" ht="12.5">
+    <row r="989" spans="7:8">
       <c r="G989" s="2"/>
       <c r="H989" s="2"/>
     </row>
-    <row r="990" spans="7:8" ht="12.5">
+    <row r="990" spans="7:8">
       <c r="G990" s="2"/>
       <c r="H990" s="2"/>
     </row>
-    <row r="991" spans="7:8" ht="12.5">
+    <row r="991" spans="7:8">
       <c r="G991" s="2"/>
       <c r="H991" s="2"/>
     </row>
-    <row r="992" spans="7:8" ht="12.5">
+    <row r="992" spans="7:8">
       <c r="G992" s="2"/>
       <c r="H992" s="2"/>
     </row>
-    <row r="993" spans="7:8" ht="12.5">
+    <row r="993" spans="7:8">
       <c r="G993" s="2"/>
       <c r="H993" s="2"/>
     </row>
-    <row r="994" spans="7:8" ht="12.5">
+    <row r="994" spans="7:8">
       <c r="G994" s="2"/>
       <c r="H994" s="2"/>
     </row>
-    <row r="995" spans="7:8" ht="12.5">
+    <row r="995" spans="7:8">
       <c r="G995" s="2"/>
       <c r="H995" s="2"/>
     </row>
-    <row r="996" spans="7:8" ht="12.5">
+    <row r="996" spans="7:8">
       <c r="G996" s="2"/>
       <c r="H996" s="2"/>
     </row>
-    <row r="997" spans="7:8" ht="12.5">
+    <row r="997" spans="7:8">
       <c r="G997" s="2"/>
       <c r="H997" s="2"/>
     </row>
-    <row r="998" spans="7:8" ht="12.5">
+    <row r="998" spans="7:8">
       <c r="G998" s="2"/>
       <c r="H998" s="2"/>
     </row>
-    <row r="999" spans="7:8" ht="12.5">
+    <row r="999" spans="7:8">
       <c r="G999" s="2"/>
       <c r="H999" s="2"/>
     </row>
-    <row r="1000" spans="7:8" ht="12.5">
+    <row r="1000" spans="7:8">
       <c r="G1000" s="2"/>
       <c r="H1000" s="2"/>
     </row>

--- a/doc/bug-report.xlsx
+++ b/doc/bug-report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asher\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0939DFFC-33A1-47D0-9C3A-03D6DF902872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F902230-EA98-4A86-8B89-BF7D87897223}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27675" yWindow="-1170" windowWidth="24075" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Tracker" sheetId="2" r:id="rId1"/>
@@ -44,18 +44,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="119">
   <si>
     <t>Matt</t>
   </si>
   <si>
+    <t>Patrick</t>
+  </si>
+  <si>
+    <t>Arshvir</t>
+  </si>
+  <si>
     <t>Asher</t>
-  </si>
-  <si>
-    <t>Patrick</t>
-  </si>
-  <si>
-    <t>Arshvir</t>
   </si>
   <si>
     <t>Title</t>
@@ -402,6 +402,92 @@
   </si>
   <si>
     <t>item should be scrapped and disspear</t>
+  </si>
+  <si>
+    <t>Game crashing on final boss kill</t>
+  </si>
+  <si>
+    <t>1) launch game
+2) Get to final boss
+3) Kill final boss
+4) Observe game crashes</t>
+  </si>
+  <si>
+    <t>Player should get win screen and game shouldn't crash</t>
+  </si>
+  <si>
+    <t>Game crashing on boss 1 exit dooe</t>
+  </si>
+  <si>
+    <t>1) launch game
+2) Get to boss 1
+3) Kill boss 1
+4) Go to exit door
+5) Observe game crashes</t>
+  </si>
+  <si>
+    <t>Player should be sent to the second stage</t>
+  </si>
+  <si>
+    <t>Scraping item crashes game</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Launch game
+2) Scrap item
+3) Observe game crashes </t>
+  </si>
+  <si>
+    <t>Scrap should be added to player and game shouldn't crash</t>
+  </si>
+  <si>
+    <t>All items in UI are rerendered every time an item is picked up</t>
+  </si>
+  <si>
+    <t>1) Launch game
+2) Collect item
+3) Collect another item
+4) Observe first item is rendered twice on top of eachother</t>
+  </si>
+  <si>
+    <t>Items should only be rendered once in the inventory</t>
+  </si>
+  <si>
+    <t>Save as item floats up after being picked up</t>
+  </si>
+  <si>
+    <t>1) Launch game
+2) Collect item
+3) Save game as it floats up
+4) Reload
+5) Observe item can be picked up again</t>
+  </si>
+  <si>
+    <t>Items should only be able to be picked up once</t>
+  </si>
+  <si>
+    <t>Still shooting after death</t>
+  </si>
+  <si>
+    <t>1) launch game
+2) Hold down shoot
+3) Die
+4) Observe player still shooting</t>
+  </si>
+  <si>
+    <t>Player should stop shootin</t>
+  </si>
+  <si>
+    <t>Save and main menu overlapping in pause screen</t>
+  </si>
+  <si>
+    <t>1) launch game
+2) pause in no combat
+3) enter combat and pause
+4) leave combat and pause
+5) observe save and main menu overlap</t>
+  </si>
+  <si>
+    <t>pause button should not overlap</t>
   </si>
 </sst>
 </file>
@@ -724,12 +810,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:L1000"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="19.85546875" customWidth="1"/>
+    <col min="1" max="1" width="19.90625" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" customWidth="1"/>
-    <col min="8" max="8" width="15.140625" customWidth="1"/>
+    <col min="3" max="3" width="26.90625" customWidth="1"/>
+    <col min="8" max="8" width="15.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
@@ -790,16 +876,16 @@
         <v>20</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>22</v>
       </c>
@@ -819,16 +905,16 @@
         <v>20</v>
       </c>
       <c r="G3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>25</v>
       </c>
@@ -848,16 +934,16 @@
         <v>28</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" ht="15.75" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -877,16 +963,16 @@
         <v>28</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>1</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" ht="15.75" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>32</v>
       </c>
@@ -915,7 +1001,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>36</v>
       </c>
@@ -935,16 +1021,16 @@
         <v>28</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>40</v>
       </c>
@@ -964,7 +1050,7 @@
         <v>28</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>0</v>
@@ -973,7 +1059,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>43</v>
       </c>
@@ -1002,7 +1088,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>47</v>
       </c>
@@ -1022,7 +1108,7 @@
         <v>28</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>46</v>
@@ -1031,7 +1117,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>50</v>
       </c>
@@ -1060,7 +1146,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>53</v>
       </c>
@@ -1080,16 +1166,16 @@
         <v>28</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>56</v>
       </c>
@@ -1109,10 +1195,10 @@
         <v>59</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>21</v>
@@ -1121,7 +1207,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>61</v>
       </c>
@@ -1141,16 +1227,16 @@
         <v>28</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" ht="15.75" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>64</v>
       </c>
@@ -1179,7 +1265,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>67</v>
       </c>
@@ -1202,13 +1288,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:11" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>71</v>
       </c>
@@ -1228,16 +1314,16 @@
         <v>28</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:11" ht="15.75" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>74</v>
       </c>
@@ -1257,16 +1343,16 @@
         <v>28</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:11" ht="15.75" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>77</v>
       </c>
@@ -1286,16 +1372,16 @@
         <v>28</v>
       </c>
       <c r="G19" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>1</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>2</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:11" ht="15.75" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>80</v>
       </c>
@@ -1318,13 +1404,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:11" ht="37.5">
       <c r="A21" s="1" t="s">
         <v>83</v>
       </c>
@@ -1347,13 +1433,13 @@
         <v>46</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:11" ht="12.5">
       <c r="A22" s="1" t="s">
         <v>86</v>
       </c>
@@ -1376,13 +1462,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K22" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:11" ht="25">
       <c r="A23" s="1" t="s">
         <v>89</v>
       </c>
@@ -1402,16 +1488,16 @@
         <v>28</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:11" ht="100">
       <c r="A24" s="1" t="s">
         <v>92</v>
       </c>
@@ -1431,16 +1517,16 @@
         <v>28</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:11" ht="12.5">
       <c r="A25" s="1" t="s">
         <v>95</v>
       </c>
@@ -1463,4253 +1549,4421 @@
         <v>46</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
-      <c r="A26" s="1"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" s="1"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="1"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="1"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="1"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="1"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="1"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-    </row>
-    <row r="33" spans="1:8">
+    <row r="26" spans="1:11" ht="25">
+      <c r="A26" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D26" s="9">
+        <v>45628</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="25">
+      <c r="A27" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D27" s="9">
+        <v>45628</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="25">
+      <c r="A28" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" s="9">
+        <v>45628</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="37.5">
+      <c r="A29" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" s="9">
+        <v>45628</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="25">
+      <c r="A30" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D30" s="9">
+        <v>45628</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="25">
+      <c r="A31" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D31" s="9">
+        <v>45628</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" ht="37.5">
+      <c r="A32" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D32" s="9">
+        <v>45628</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="12.5">
       <c r="A33" s="1"/>
       <c r="G33" s="2"/>
       <c r="H33" s="2"/>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" ht="12.5">
       <c r="A34" s="1"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" ht="12.5">
       <c r="A35" s="1"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" ht="12.5">
       <c r="A36" s="1"/>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" ht="12.5">
       <c r="A37" s="1"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" ht="12.5">
       <c r="A38" s="1"/>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" ht="12.5">
       <c r="A39" s="1"/>
       <c r="G39" s="2"/>
       <c r="H39" s="2"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" ht="12.5">
       <c r="A40" s="1"/>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" ht="12.5">
       <c r="A41" s="1"/>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" ht="12.5">
       <c r="A42" s="1"/>
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" ht="12.5">
       <c r="A43" s="1"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" ht="12.5">
       <c r="A44" s="1"/>
       <c r="G44" s="2"/>
       <c r="H44" s="2"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" ht="12.5">
       <c r="A45" s="1"/>
       <c r="G45" s="2"/>
       <c r="H45" s="2"/>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" ht="12.5">
       <c r="A46" s="1"/>
       <c r="G46" s="2"/>
       <c r="H46" s="2"/>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" ht="12.5">
       <c r="A47" s="1"/>
       <c r="G47" s="2"/>
       <c r="H47" s="2"/>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" ht="12.5">
       <c r="A48" s="1"/>
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" ht="12.5">
       <c r="A49" s="1"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" ht="12.5">
       <c r="A50" s="1"/>
       <c r="G50" s="2"/>
       <c r="H50" s="2"/>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" ht="12.5">
       <c r="A51" s="1"/>
       <c r="G51" s="2"/>
       <c r="H51" s="2"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" ht="12.5">
       <c r="A52" s="1"/>
       <c r="G52" s="2"/>
       <c r="H52" s="2"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" ht="12.5">
       <c r="A53" s="1"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" ht="12.5">
       <c r="A54" s="1"/>
       <c r="G54" s="2"/>
       <c r="H54" s="2"/>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" ht="12.5">
       <c r="A55" s="1"/>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" ht="12.5">
       <c r="A56" s="1"/>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" ht="12.5">
       <c r="A57" s="1"/>
       <c r="G57" s="2"/>
       <c r="H57" s="2"/>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" ht="12.5">
       <c r="A58" s="1"/>
       <c r="G58" s="2"/>
       <c r="H58" s="2"/>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" ht="12.5">
       <c r="A59" s="1"/>
       <c r="G59" s="2"/>
       <c r="H59" s="2"/>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" ht="12.5">
       <c r="A60" s="1"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" ht="12.5">
       <c r="A61" s="1"/>
       <c r="G61" s="2"/>
       <c r="H61" s="2"/>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" ht="12.5">
       <c r="A62" s="1"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" ht="12.5">
       <c r="A63" s="1"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" ht="12.5">
       <c r="A64" s="1"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" ht="12.5">
       <c r="A65" s="1"/>
       <c r="G65" s="2"/>
       <c r="H65" s="2"/>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" ht="12.5">
       <c r="A66" s="1"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" ht="12.5">
       <c r="A67" s="1"/>
       <c r="G67" s="2"/>
       <c r="H67" s="2"/>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" ht="12.5">
       <c r="A68" s="1"/>
       <c r="G68" s="2"/>
       <c r="H68" s="2"/>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" ht="12.5">
       <c r="A69" s="1"/>
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" ht="12.5">
       <c r="A70" s="1"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" ht="12.5">
       <c r="A71" s="1"/>
       <c r="G71" s="2"/>
       <c r="H71" s="2"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" ht="12.5">
       <c r="A72" s="1"/>
       <c r="G72" s="2"/>
       <c r="H72" s="2"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" ht="12.5">
       <c r="A73" s="1"/>
       <c r="G73" s="2"/>
       <c r="H73" s="2"/>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" ht="12.5">
       <c r="A74" s="1"/>
       <c r="G74" s="2"/>
       <c r="H74" s="2"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" ht="12.5">
       <c r="A75" s="1"/>
       <c r="G75" s="2"/>
       <c r="H75" s="2"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" ht="12.5">
       <c r="A76" s="1"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" ht="12.5">
       <c r="A77" s="1"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" ht="12.5">
       <c r="A78" s="1"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" ht="12.5">
       <c r="A79" s="1"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" ht="12.5">
       <c r="A80" s="1"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" ht="12.5">
       <c r="A81" s="1"/>
       <c r="G81" s="2"/>
       <c r="H81" s="2"/>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" ht="12.5">
       <c r="A82" s="1"/>
       <c r="G82" s="2"/>
       <c r="H82" s="2"/>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" ht="12.5">
       <c r="A83" s="1"/>
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" ht="12.5">
       <c r="A84" s="1"/>
       <c r="G84" s="2"/>
       <c r="H84" s="2"/>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" ht="12.5">
       <c r="A85" s="1"/>
       <c r="G85" s="2"/>
       <c r="H85" s="2"/>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" ht="12.5">
       <c r="A86" s="1"/>
       <c r="G86" s="2"/>
       <c r="H86" s="2"/>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" ht="12.5">
       <c r="A87" s="1"/>
       <c r="G87" s="2"/>
       <c r="H87" s="2"/>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" ht="12.5">
       <c r="A88" s="1"/>
       <c r="G88" s="2"/>
       <c r="H88" s="2"/>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" ht="12.5">
       <c r="A89" s="1"/>
       <c r="G89" s="2"/>
       <c r="H89" s="2"/>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" ht="12.5">
       <c r="A90" s="1"/>
       <c r="G90" s="2"/>
       <c r="H90" s="2"/>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" ht="12.5">
       <c r="A91" s="1"/>
       <c r="G91" s="2"/>
       <c r="H91" s="2"/>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" ht="12.5">
       <c r="A92" s="1"/>
       <c r="G92" s="2"/>
       <c r="H92" s="2"/>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" ht="12.5">
       <c r="A93" s="1"/>
       <c r="G93" s="2"/>
       <c r="H93" s="2"/>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" ht="12.5">
       <c r="A94" s="1"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" ht="12.5">
       <c r="A95" s="1"/>
       <c r="G95" s="2"/>
       <c r="H95" s="2"/>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" ht="12.5">
       <c r="A96" s="1"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" ht="12.5">
       <c r="A97" s="1"/>
       <c r="G97" s="2"/>
       <c r="H97" s="2"/>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" ht="12.5">
       <c r="A98" s="1"/>
       <c r="G98" s="2"/>
       <c r="H98" s="2"/>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" ht="12.5">
       <c r="A99" s="1"/>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" ht="12.5">
       <c r="A100" s="1"/>
       <c r="G100" s="2"/>
       <c r="H100" s="2"/>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" ht="12.5">
       <c r="A101" s="1"/>
       <c r="G101" s="2"/>
       <c r="H101" s="2"/>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" ht="12.5">
       <c r="A102" s="1"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" ht="12.5">
       <c r="A103" s="1"/>
       <c r="G103" s="2"/>
       <c r="H103" s="2"/>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" ht="12.5">
       <c r="A104" s="1"/>
       <c r="G104" s="2"/>
       <c r="H104" s="2"/>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" ht="12.5">
       <c r="A105" s="1"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" ht="12.5">
       <c r="A106" s="1"/>
       <c r="G106" s="2"/>
       <c r="H106" s="2"/>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" ht="12.5">
       <c r="A107" s="1"/>
       <c r="G107" s="2"/>
       <c r="H107" s="2"/>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" ht="12.5">
       <c r="A108" s="1"/>
       <c r="G108" s="2"/>
       <c r="H108" s="2"/>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" ht="12.5">
       <c r="A109" s="1"/>
       <c r="G109" s="2"/>
       <c r="H109" s="2"/>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" ht="12.5">
       <c r="A110" s="1"/>
       <c r="G110" s="2"/>
       <c r="H110" s="2"/>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:8" ht="12.5">
       <c r="A111" s="1"/>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" ht="12.5">
       <c r="A112" s="1"/>
       <c r="G112" s="2"/>
       <c r="H112" s="2"/>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" ht="12.5">
       <c r="A113" s="1"/>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" ht="12.5">
       <c r="A114" s="1"/>
       <c r="G114" s="2"/>
       <c r="H114" s="2"/>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" ht="12.5">
       <c r="A115" s="1"/>
       <c r="G115" s="2"/>
       <c r="H115" s="2"/>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" ht="12.5">
       <c r="A116" s="1"/>
       <c r="G116" s="2"/>
       <c r="H116" s="2"/>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" ht="12.5">
       <c r="A117" s="1"/>
       <c r="G117" s="2"/>
       <c r="H117" s="2"/>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" ht="12.5">
       <c r="A118" s="1"/>
       <c r="G118" s="2"/>
       <c r="H118" s="2"/>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" ht="12.5">
       <c r="A119" s="1"/>
       <c r="G119" s="2"/>
       <c r="H119" s="2"/>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" ht="12.5">
       <c r="A120" s="1"/>
       <c r="G120" s="2"/>
       <c r="H120" s="2"/>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" ht="12.5">
       <c r="A121" s="1"/>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" ht="12.5">
       <c r="A122" s="1"/>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" ht="12.5">
       <c r="A123" s="1"/>
       <c r="G123" s="2"/>
       <c r="H123" s="2"/>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" ht="12.5">
       <c r="A124" s="1"/>
       <c r="G124" s="2"/>
       <c r="H124" s="2"/>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:8" ht="12.5">
       <c r="A125" s="1"/>
       <c r="G125" s="2"/>
       <c r="H125" s="2"/>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:8" ht="12.5">
       <c r="A126" s="1"/>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" ht="12.5">
       <c r="A127" s="1"/>
       <c r="G127" s="2"/>
       <c r="H127" s="2"/>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" ht="12.5">
       <c r="A128" s="1"/>
       <c r="G128" s="2"/>
       <c r="H128" s="2"/>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:8" ht="12.5">
       <c r="A129" s="1"/>
       <c r="G129" s="2"/>
       <c r="H129" s="2"/>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:8" ht="12.5">
       <c r="A130" s="1"/>
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:8" ht="12.5">
       <c r="A131" s="1"/>
       <c r="G131" s="2"/>
       <c r="H131" s="2"/>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:8" ht="12.5">
       <c r="A132" s="1"/>
       <c r="G132" s="2"/>
       <c r="H132" s="2"/>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:8" ht="12.5">
       <c r="A133" s="1"/>
       <c r="G133" s="2"/>
       <c r="H133" s="2"/>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:8" ht="12.5">
       <c r="A134" s="1"/>
       <c r="G134" s="2"/>
       <c r="H134" s="2"/>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:8" ht="12.5">
       <c r="A135" s="1"/>
       <c r="G135" s="2"/>
       <c r="H135" s="2"/>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:8" ht="12.5">
       <c r="A136" s="1"/>
       <c r="G136" s="2"/>
       <c r="H136" s="2"/>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:8" ht="12.5">
       <c r="A137" s="1"/>
       <c r="G137" s="2"/>
       <c r="H137" s="2"/>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" spans="1:8" ht="12.5">
       <c r="A138" s="1"/>
       <c r="G138" s="2"/>
       <c r="H138" s="2"/>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:8" ht="12.5">
       <c r="A139" s="1"/>
       <c r="G139" s="2"/>
       <c r="H139" s="2"/>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:8" ht="12.5">
       <c r="A140" s="1"/>
       <c r="G140" s="2"/>
       <c r="H140" s="2"/>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:8" ht="12.5">
       <c r="A141" s="1"/>
       <c r="G141" s="2"/>
       <c r="H141" s="2"/>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:8" ht="12.5">
       <c r="A142" s="1"/>
       <c r="G142" s="2"/>
       <c r="H142" s="2"/>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:8" ht="12.5">
       <c r="A143" s="1"/>
       <c r="G143" s="2"/>
       <c r="H143" s="2"/>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:8" ht="12.5">
       <c r="A144" s="1"/>
       <c r="G144" s="2"/>
       <c r="H144" s="2"/>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:8" ht="12.5">
       <c r="A145" s="1"/>
       <c r="G145" s="2"/>
       <c r="H145" s="2"/>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:8" ht="12.5">
       <c r="A146" s="1"/>
       <c r="G146" s="2"/>
       <c r="H146" s="2"/>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" ht="12.5">
       <c r="A147" s="1"/>
       <c r="G147" s="2"/>
       <c r="H147" s="2"/>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:8" ht="12.5">
       <c r="A148" s="1"/>
       <c r="G148" s="2"/>
       <c r="H148" s="2"/>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" ht="12.5">
       <c r="A149" s="1"/>
       <c r="G149" s="2"/>
       <c r="H149" s="2"/>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:8" ht="12.5">
       <c r="A150" s="1"/>
       <c r="G150" s="2"/>
       <c r="H150" s="2"/>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:8" ht="12.5">
       <c r="A151" s="1"/>
       <c r="G151" s="2"/>
       <c r="H151" s="2"/>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:8" ht="12.5">
       <c r="A152" s="1"/>
       <c r="G152" s="2"/>
       <c r="H152" s="2"/>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" ht="12.5">
       <c r="A153" s="1"/>
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:8" ht="12.5">
       <c r="A154" s="1"/>
       <c r="G154" s="2"/>
       <c r="H154" s="2"/>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:8" ht="12.5">
       <c r="A155" s="1"/>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:8" ht="12.5">
       <c r="A156" s="1"/>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" ht="12.5">
       <c r="A157" s="1"/>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:8" ht="12.5">
       <c r="A158" s="1"/>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:8" ht="12.5">
       <c r="A159" s="1"/>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:8" ht="12.5">
       <c r="A160" s="1"/>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" spans="1:8" ht="12.5">
       <c r="A161" s="1"/>
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:8" ht="12.5">
       <c r="A162" s="1"/>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" spans="1:8" ht="12.5">
       <c r="A163" s="1"/>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" spans="1:8" ht="12.5">
       <c r="A164" s="1"/>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
     </row>
-    <row r="165" spans="1:8">
+    <row r="165" spans="1:8" ht="12.5">
       <c r="A165" s="1"/>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:8" ht="12.5">
       <c r="A166" s="1"/>
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:8" ht="12.5">
       <c r="A167" s="1"/>
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" spans="1:8" ht="12.5">
       <c r="A168" s="1"/>
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" spans="1:8" ht="12.5">
       <c r="A169" s="1"/>
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:8" ht="12.5">
       <c r="A170" s="1"/>
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" spans="1:8" ht="12.5">
       <c r="A171" s="1"/>
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:8" ht="12.5">
       <c r="A172" s="1"/>
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:8" ht="12.5">
       <c r="A173" s="1"/>
       <c r="G173" s="2"/>
       <c r="H173" s="2"/>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" spans="1:8" ht="12.5">
       <c r="A174" s="1"/>
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:8" ht="12.5">
       <c r="A175" s="1"/>
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" spans="1:8" ht="12.5">
       <c r="A176" s="1"/>
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:8" ht="12.5">
       <c r="A177" s="1"/>
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:8" ht="12.5">
       <c r="A178" s="1"/>
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:8" ht="12.5">
       <c r="A179" s="1"/>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" spans="1:8" ht="12.5">
       <c r="A180" s="1"/>
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" spans="1:8" ht="12.5">
       <c r="A181" s="1"/>
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" spans="1:8" ht="12.5">
       <c r="A182" s="1"/>
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:8" ht="12.5">
       <c r="A183" s="1"/>
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" spans="1:8" ht="12.5">
       <c r="A184" s="1"/>
       <c r="G184" s="2"/>
       <c r="H184" s="2"/>
     </row>
-    <row r="185" spans="1:8">
+    <row r="185" spans="1:8" ht="12.5">
       <c r="A185" s="1"/>
       <c r="G185" s="2"/>
       <c r="H185" s="2"/>
     </row>
-    <row r="186" spans="1:8">
+    <row r="186" spans="1:8" ht="12.5">
       <c r="A186" s="1"/>
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
     </row>
-    <row r="187" spans="1:8">
+    <row r="187" spans="1:8" ht="12.5">
       <c r="A187" s="1"/>
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
     </row>
-    <row r="188" spans="1:8">
+    <row r="188" spans="1:8" ht="12.5">
       <c r="A188" s="1"/>
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
     </row>
-    <row r="189" spans="1:8">
+    <row r="189" spans="1:8" ht="12.5">
       <c r="A189" s="1"/>
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
     </row>
-    <row r="190" spans="1:8">
+    <row r="190" spans="1:8" ht="12.5">
       <c r="A190" s="1"/>
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
     </row>
-    <row r="191" spans="1:8">
+    <row r="191" spans="1:8" ht="12.5">
       <c r="A191" s="1"/>
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
     </row>
-    <row r="192" spans="1:8">
+    <row r="192" spans="1:8" ht="12.5">
       <c r="A192" s="1"/>
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" spans="1:8" ht="12.5">
       <c r="A193" s="1"/>
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
     </row>
-    <row r="194" spans="1:8">
+    <row r="194" spans="1:8" ht="12.5">
       <c r="A194" s="1"/>
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
     </row>
-    <row r="195" spans="1:8">
+    <row r="195" spans="1:8" ht="12.5">
       <c r="A195" s="1"/>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" spans="1:8" ht="12.5">
       <c r="A196" s="1"/>
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:8" ht="12.5">
       <c r="A197" s="1"/>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:8" ht="12.5">
       <c r="A198" s="1"/>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:8" ht="12.5">
       <c r="A199" s="1"/>
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:8" ht="12.5">
       <c r="A200" s="1"/>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:8" ht="12.5">
       <c r="A201" s="1"/>
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:8" ht="12.5">
       <c r="A202" s="1"/>
       <c r="G202" s="2"/>
       <c r="H202" s="2"/>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" spans="1:8" ht="12.5">
       <c r="A203" s="1"/>
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
     </row>
-    <row r="204" spans="1:8">
+    <row r="204" spans="1:8" ht="12.5">
       <c r="A204" s="1"/>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
     </row>
-    <row r="205" spans="1:8">
+    <row r="205" spans="1:8" ht="12.5">
       <c r="A205" s="1"/>
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
     </row>
-    <row r="206" spans="1:8">
+    <row r="206" spans="1:8" ht="12.5">
       <c r="A206" s="1"/>
       <c r="G206" s="2"/>
       <c r="H206" s="2"/>
     </row>
-    <row r="207" spans="1:8">
+    <row r="207" spans="1:8" ht="12.5">
       <c r="A207" s="1"/>
       <c r="G207" s="2"/>
       <c r="H207" s="2"/>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" spans="1:8" ht="12.5">
       <c r="A208" s="1"/>
       <c r="G208" s="2"/>
       <c r="H208" s="2"/>
     </row>
-    <row r="209" spans="1:8">
+    <row r="209" spans="1:8" ht="12.5">
       <c r="A209" s="1"/>
       <c r="G209" s="2"/>
       <c r="H209" s="2"/>
     </row>
-    <row r="210" spans="1:8">
+    <row r="210" spans="1:8" ht="12.5">
       <c r="A210" s="1"/>
       <c r="G210" s="2"/>
       <c r="H210" s="2"/>
     </row>
-    <row r="211" spans="1:8">
+    <row r="211" spans="1:8" ht="12.5">
       <c r="A211" s="1"/>
       <c r="G211" s="2"/>
       <c r="H211" s="2"/>
     </row>
-    <row r="212" spans="1:8">
+    <row r="212" spans="1:8" ht="12.5">
       <c r="A212" s="1"/>
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
     </row>
-    <row r="213" spans="1:8">
+    <row r="213" spans="1:8" ht="12.5">
       <c r="A213" s="1"/>
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
     </row>
-    <row r="214" spans="1:8">
+    <row r="214" spans="1:8" ht="12.5">
       <c r="A214" s="1"/>
       <c r="G214" s="2"/>
       <c r="H214" s="2"/>
     </row>
-    <row r="215" spans="1:8">
+    <row r="215" spans="1:8" ht="12.5">
       <c r="A215" s="1"/>
       <c r="G215" s="2"/>
       <c r="H215" s="2"/>
     </row>
-    <row r="216" spans="1:8">
+    <row r="216" spans="1:8" ht="12.5">
       <c r="A216" s="1"/>
       <c r="G216" s="2"/>
       <c r="H216" s="2"/>
     </row>
-    <row r="217" spans="1:8">
+    <row r="217" spans="1:8" ht="12.5">
       <c r="A217" s="1"/>
       <c r="G217" s="2"/>
       <c r="H217" s="2"/>
     </row>
-    <row r="218" spans="1:8">
+    <row r="218" spans="1:8" ht="12.5">
       <c r="A218" s="1"/>
       <c r="G218" s="2"/>
       <c r="H218" s="2"/>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:8" ht="12.5">
       <c r="A219" s="1"/>
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" spans="1:8" ht="12.5">
       <c r="A220" s="1"/>
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
     </row>
-    <row r="221" spans="1:8">
+    <row r="221" spans="1:8" ht="12.5">
       <c r="A221" s="1"/>
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
     </row>
-    <row r="222" spans="1:8">
+    <row r="222" spans="1:8" ht="12.5">
       <c r="A222" s="1"/>
       <c r="G222" s="2"/>
       <c r="H222" s="2"/>
     </row>
-    <row r="223" spans="1:8">
+    <row r="223" spans="1:8" ht="12.5">
       <c r="A223" s="1"/>
       <c r="G223" s="2"/>
       <c r="H223" s="2"/>
     </row>
-    <row r="224" spans="1:8">
+    <row r="224" spans="1:8" ht="12.5">
       <c r="A224" s="1"/>
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
     </row>
-    <row r="225" spans="1:8">
+    <row r="225" spans="1:8" ht="12.5">
       <c r="A225" s="1"/>
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
     </row>
-    <row r="226" spans="1:8">
+    <row r="226" spans="1:8" ht="12.5">
       <c r="A226" s="1"/>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
     </row>
-    <row r="227" spans="1:8">
+    <row r="227" spans="1:8" ht="12.5">
       <c r="A227" s="1"/>
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
     </row>
-    <row r="228" spans="1:8">
+    <row r="228" spans="1:8" ht="12.5">
       <c r="A228" s="1"/>
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
     </row>
-    <row r="229" spans="1:8">
+    <row r="229" spans="1:8" ht="12.5">
       <c r="A229" s="1"/>
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
     </row>
-    <row r="230" spans="1:8">
+    <row r="230" spans="1:8" ht="12.5">
       <c r="A230" s="1"/>
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
     </row>
-    <row r="231" spans="1:8">
+    <row r="231" spans="1:8" ht="12.5">
       <c r="A231" s="1"/>
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
     </row>
-    <row r="232" spans="1:8">
+    <row r="232" spans="1:8" ht="12.5">
       <c r="A232" s="1"/>
       <c r="G232" s="2"/>
       <c r="H232" s="2"/>
     </row>
-    <row r="233" spans="1:8">
+    <row r="233" spans="1:8" ht="12.5">
       <c r="A233" s="1"/>
       <c r="G233" s="2"/>
       <c r="H233" s="2"/>
     </row>
-    <row r="234" spans="1:8">
+    <row r="234" spans="1:8" ht="12.5">
       <c r="A234" s="1"/>
       <c r="G234" s="2"/>
       <c r="H234" s="2"/>
     </row>
-    <row r="235" spans="1:8">
+    <row r="235" spans="1:8" ht="12.5">
       <c r="A235" s="1"/>
       <c r="G235" s="2"/>
       <c r="H235" s="2"/>
     </row>
-    <row r="236" spans="1:8">
+    <row r="236" spans="1:8" ht="12.5">
       <c r="A236" s="1"/>
       <c r="G236" s="2"/>
       <c r="H236" s="2"/>
     </row>
-    <row r="237" spans="1:8">
+    <row r="237" spans="1:8" ht="12.5">
       <c r="A237" s="1"/>
       <c r="G237" s="2"/>
       <c r="H237" s="2"/>
     </row>
-    <row r="238" spans="1:8">
+    <row r="238" spans="1:8" ht="12.5">
       <c r="A238" s="1"/>
       <c r="G238" s="2"/>
       <c r="H238" s="2"/>
     </row>
-    <row r="239" spans="1:8">
+    <row r="239" spans="1:8" ht="12.5">
       <c r="A239" s="1"/>
       <c r="G239" s="2"/>
       <c r="H239" s="2"/>
     </row>
-    <row r="240" spans="1:8">
+    <row r="240" spans="1:8" ht="12.5">
       <c r="A240" s="1"/>
       <c r="G240" s="2"/>
       <c r="H240" s="2"/>
     </row>
-    <row r="241" spans="1:8">
+    <row r="241" spans="1:8" ht="12.5">
       <c r="A241" s="1"/>
       <c r="G241" s="2"/>
       <c r="H241" s="2"/>
     </row>
-    <row r="242" spans="1:8">
+    <row r="242" spans="1:8" ht="12.5">
       <c r="A242" s="1"/>
       <c r="G242" s="2"/>
       <c r="H242" s="2"/>
     </row>
-    <row r="243" spans="1:8">
+    <row r="243" spans="1:8" ht="12.5">
       <c r="A243" s="1"/>
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
     </row>
-    <row r="244" spans="1:8">
+    <row r="244" spans="1:8" ht="12.5">
       <c r="A244" s="1"/>
       <c r="G244" s="2"/>
       <c r="H244" s="2"/>
     </row>
-    <row r="245" spans="1:8">
+    <row r="245" spans="1:8" ht="12.5">
       <c r="A245" s="1"/>
       <c r="G245" s="2"/>
       <c r="H245" s="2"/>
     </row>
-    <row r="246" spans="1:8">
+    <row r="246" spans="1:8" ht="12.5">
       <c r="A246" s="1"/>
       <c r="G246" s="2"/>
       <c r="H246" s="2"/>
     </row>
-    <row r="247" spans="1:8">
+    <row r="247" spans="1:8" ht="12.5">
       <c r="A247" s="1"/>
       <c r="G247" s="2"/>
       <c r="H247" s="2"/>
     </row>
-    <row r="248" spans="1:8">
+    <row r="248" spans="1:8" ht="12.5">
       <c r="A248" s="1"/>
       <c r="G248" s="2"/>
       <c r="H248" s="2"/>
     </row>
-    <row r="249" spans="1:8">
+    <row r="249" spans="1:8" ht="12.5">
       <c r="A249" s="1"/>
       <c r="G249" s="2"/>
       <c r="H249" s="2"/>
     </row>
-    <row r="250" spans="1:8">
+    <row r="250" spans="1:8" ht="12.5">
       <c r="A250" s="1"/>
       <c r="G250" s="2"/>
       <c r="H250" s="2"/>
     </row>
-    <row r="251" spans="1:8">
+    <row r="251" spans="1:8" ht="12.5">
       <c r="A251" s="1"/>
       <c r="G251" s="2"/>
       <c r="H251" s="2"/>
     </row>
-    <row r="252" spans="1:8">
+    <row r="252" spans="1:8" ht="12.5">
       <c r="A252" s="1"/>
       <c r="G252" s="2"/>
       <c r="H252" s="2"/>
     </row>
-    <row r="253" spans="1:8">
+    <row r="253" spans="1:8" ht="12.5">
       <c r="A253" s="1"/>
       <c r="G253" s="2"/>
       <c r="H253" s="2"/>
     </row>
-    <row r="254" spans="1:8">
+    <row r="254" spans="1:8" ht="12.5">
       <c r="A254" s="1"/>
       <c r="G254" s="2"/>
       <c r="H254" s="2"/>
     </row>
-    <row r="255" spans="1:8">
+    <row r="255" spans="1:8" ht="12.5">
       <c r="A255" s="1"/>
       <c r="G255" s="2"/>
       <c r="H255" s="2"/>
     </row>
-    <row r="256" spans="1:8">
+    <row r="256" spans="1:8" ht="12.5">
       <c r="A256" s="1"/>
       <c r="G256" s="2"/>
       <c r="H256" s="2"/>
     </row>
-    <row r="257" spans="1:8">
+    <row r="257" spans="1:8" ht="12.5">
       <c r="A257" s="1"/>
       <c r="G257" s="2"/>
       <c r="H257" s="2"/>
     </row>
-    <row r="258" spans="1:8">
+    <row r="258" spans="1:8" ht="12.5">
       <c r="A258" s="1"/>
       <c r="G258" s="2"/>
       <c r="H258" s="2"/>
     </row>
-    <row r="259" spans="1:8">
+    <row r="259" spans="1:8" ht="12.5">
       <c r="A259" s="1"/>
       <c r="G259" s="2"/>
       <c r="H259" s="2"/>
     </row>
-    <row r="260" spans="1:8">
+    <row r="260" spans="1:8" ht="12.5">
       <c r="A260" s="1"/>
       <c r="G260" s="2"/>
       <c r="H260" s="2"/>
     </row>
-    <row r="261" spans="1:8">
+    <row r="261" spans="1:8" ht="12.5">
       <c r="A261" s="1"/>
       <c r="G261" s="2"/>
       <c r="H261" s="2"/>
     </row>
-    <row r="262" spans="1:8">
+    <row r="262" spans="1:8" ht="12.5">
       <c r="A262" s="1"/>
       <c r="G262" s="2"/>
       <c r="H262" s="2"/>
     </row>
-    <row r="263" spans="1:8">
+    <row r="263" spans="1:8" ht="12.5">
       <c r="A263" s="1"/>
       <c r="G263" s="2"/>
       <c r="H263" s="2"/>
     </row>
-    <row r="264" spans="1:8">
+    <row r="264" spans="1:8" ht="12.5">
       <c r="A264" s="1"/>
       <c r="G264" s="2"/>
       <c r="H264" s="2"/>
     </row>
-    <row r="265" spans="1:8">
+    <row r="265" spans="1:8" ht="12.5">
       <c r="A265" s="1"/>
       <c r="G265" s="2"/>
       <c r="H265" s="2"/>
     </row>
-    <row r="266" spans="1:8">
+    <row r="266" spans="1:8" ht="12.5">
       <c r="A266" s="1"/>
       <c r="G266" s="2"/>
       <c r="H266" s="2"/>
     </row>
-    <row r="267" spans="1:8">
+    <row r="267" spans="1:8" ht="12.5">
       <c r="A267" s="1"/>
       <c r="G267" s="2"/>
       <c r="H267" s="2"/>
     </row>
-    <row r="268" spans="1:8">
+    <row r="268" spans="1:8" ht="12.5">
       <c r="A268" s="1"/>
       <c r="G268" s="2"/>
       <c r="H268" s="2"/>
     </row>
-    <row r="269" spans="1:8">
+    <row r="269" spans="1:8" ht="12.5">
       <c r="A269" s="1"/>
       <c r="G269" s="2"/>
       <c r="H269" s="2"/>
     </row>
-    <row r="270" spans="1:8">
+    <row r="270" spans="1:8" ht="12.5">
       <c r="A270" s="1"/>
       <c r="G270" s="2"/>
       <c r="H270" s="2"/>
     </row>
-    <row r="271" spans="1:8">
+    <row r="271" spans="1:8" ht="12.5">
       <c r="A271" s="1"/>
       <c r="G271" s="2"/>
       <c r="H271" s="2"/>
     </row>
-    <row r="272" spans="1:8">
+    <row r="272" spans="1:8" ht="12.5">
       <c r="A272" s="1"/>
       <c r="G272" s="2"/>
       <c r="H272" s="2"/>
     </row>
-    <row r="273" spans="1:8">
+    <row r="273" spans="1:8" ht="12.5">
       <c r="A273" s="1"/>
       <c r="G273" s="2"/>
       <c r="H273" s="2"/>
     </row>
-    <row r="274" spans="1:8">
+    <row r="274" spans="1:8" ht="12.5">
       <c r="A274" s="1"/>
       <c r="G274" s="2"/>
       <c r="H274" s="2"/>
     </row>
-    <row r="275" spans="1:8">
+    <row r="275" spans="1:8" ht="12.5">
       <c r="A275" s="1"/>
       <c r="G275" s="2"/>
       <c r="H275" s="2"/>
     </row>
-    <row r="276" spans="1:8">
+    <row r="276" spans="1:8" ht="12.5">
       <c r="A276" s="1"/>
       <c r="G276" s="2"/>
       <c r="H276" s="2"/>
     </row>
-    <row r="277" spans="1:8">
+    <row r="277" spans="1:8" ht="12.5">
       <c r="A277" s="1"/>
       <c r="G277" s="2"/>
       <c r="H277" s="2"/>
     </row>
-    <row r="278" spans="1:8">
+    <row r="278" spans="1:8" ht="12.5">
       <c r="A278" s="1"/>
       <c r="G278" s="2"/>
       <c r="H278" s="2"/>
     </row>
-    <row r="279" spans="1:8">
+    <row r="279" spans="1:8" ht="12.5">
       <c r="A279" s="1"/>
       <c r="G279" s="2"/>
       <c r="H279" s="2"/>
     </row>
-    <row r="280" spans="1:8">
+    <row r="280" spans="1:8" ht="12.5">
       <c r="A280" s="1"/>
       <c r="G280" s="2"/>
       <c r="H280" s="2"/>
     </row>
-    <row r="281" spans="1:8">
+    <row r="281" spans="1:8" ht="12.5">
       <c r="A281" s="1"/>
       <c r="G281" s="2"/>
       <c r="H281" s="2"/>
     </row>
-    <row r="282" spans="1:8">
+    <row r="282" spans="1:8" ht="12.5">
       <c r="A282" s="1"/>
       <c r="G282" s="2"/>
       <c r="H282" s="2"/>
     </row>
-    <row r="283" spans="1:8">
+    <row r="283" spans="1:8" ht="12.5">
       <c r="A283" s="1"/>
       <c r="G283" s="2"/>
       <c r="H283" s="2"/>
     </row>
-    <row r="284" spans="1:8">
+    <row r="284" spans="1:8" ht="12.5">
       <c r="A284" s="1"/>
       <c r="G284" s="2"/>
       <c r="H284" s="2"/>
     </row>
-    <row r="285" spans="1:8">
+    <row r="285" spans="1:8" ht="12.5">
       <c r="A285" s="1"/>
       <c r="G285" s="2"/>
       <c r="H285" s="2"/>
     </row>
-    <row r="286" spans="1:8">
+    <row r="286" spans="1:8" ht="12.5">
       <c r="A286" s="1"/>
       <c r="G286" s="2"/>
       <c r="H286" s="2"/>
     </row>
-    <row r="287" spans="1:8">
+    <row r="287" spans="1:8" ht="12.5">
       <c r="A287" s="1"/>
       <c r="G287" s="2"/>
       <c r="H287" s="2"/>
     </row>
-    <row r="288" spans="1:8">
+    <row r="288" spans="1:8" ht="12.5">
       <c r="A288" s="1"/>
       <c r="G288" s="2"/>
       <c r="H288" s="2"/>
     </row>
-    <row r="289" spans="1:8">
+    <row r="289" spans="1:8" ht="12.5">
       <c r="A289" s="1"/>
       <c r="G289" s="2"/>
       <c r="H289" s="2"/>
     </row>
-    <row r="290" spans="1:8">
+    <row r="290" spans="1:8" ht="12.5">
       <c r="A290" s="1"/>
       <c r="G290" s="2"/>
       <c r="H290" s="2"/>
     </row>
-    <row r="291" spans="1:8">
+    <row r="291" spans="1:8" ht="12.5">
       <c r="A291" s="1"/>
       <c r="G291" s="2"/>
       <c r="H291" s="2"/>
     </row>
-    <row r="292" spans="1:8">
+    <row r="292" spans="1:8" ht="12.5">
       <c r="A292" s="1"/>
       <c r="G292" s="2"/>
       <c r="H292" s="2"/>
     </row>
-    <row r="293" spans="1:8">
+    <row r="293" spans="1:8" ht="12.5">
       <c r="A293" s="1"/>
       <c r="G293" s="2"/>
       <c r="H293" s="2"/>
     </row>
-    <row r="294" spans="1:8">
+    <row r="294" spans="1:8" ht="12.5">
       <c r="A294" s="1"/>
       <c r="G294" s="2"/>
       <c r="H294" s="2"/>
     </row>
-    <row r="295" spans="1:8">
+    <row r="295" spans="1:8" ht="12.5">
       <c r="A295" s="1"/>
       <c r="G295" s="2"/>
       <c r="H295" s="2"/>
     </row>
-    <row r="296" spans="1:8">
+    <row r="296" spans="1:8" ht="12.5">
       <c r="A296" s="1"/>
       <c r="G296" s="2"/>
       <c r="H296" s="2"/>
     </row>
-    <row r="297" spans="1:8">
+    <row r="297" spans="1:8" ht="12.5">
       <c r="A297" s="1"/>
       <c r="G297" s="2"/>
       <c r="H297" s="2"/>
     </row>
-    <row r="298" spans="1:8">
+    <row r="298" spans="1:8" ht="12.5">
       <c r="A298" s="1"/>
       <c r="G298" s="2"/>
       <c r="H298" s="2"/>
     </row>
-    <row r="299" spans="1:8">
+    <row r="299" spans="1:8" ht="12.5">
       <c r="A299" s="1"/>
       <c r="G299" s="2"/>
       <c r="H299" s="2"/>
     </row>
-    <row r="300" spans="1:8">
+    <row r="300" spans="1:8" ht="12.5">
       <c r="A300" s="1"/>
       <c r="G300" s="2"/>
       <c r="H300" s="2"/>
     </row>
-    <row r="301" spans="1:8">
+    <row r="301" spans="1:8" ht="12.5">
       <c r="A301" s="1"/>
       <c r="G301" s="2"/>
       <c r="H301" s="2"/>
     </row>
-    <row r="302" spans="1:8">
+    <row r="302" spans="1:8" ht="12.5">
       <c r="A302" s="1"/>
       <c r="G302" s="2"/>
       <c r="H302" s="2"/>
     </row>
-    <row r="303" spans="1:8">
+    <row r="303" spans="1:8" ht="12.5">
       <c r="A303" s="1"/>
       <c r="G303" s="2"/>
       <c r="H303" s="2"/>
     </row>
-    <row r="304" spans="1:8">
+    <row r="304" spans="1:8" ht="12.5">
       <c r="A304" s="1"/>
       <c r="G304" s="2"/>
       <c r="H304" s="2"/>
     </row>
-    <row r="305" spans="1:8">
+    <row r="305" spans="1:8" ht="12.5">
       <c r="A305" s="1"/>
       <c r="G305" s="2"/>
       <c r="H305" s="2"/>
     </row>
-    <row r="306" spans="1:8">
+    <row r="306" spans="1:8" ht="12.5">
       <c r="A306" s="1"/>
       <c r="G306" s="2"/>
       <c r="H306" s="2"/>
     </row>
-    <row r="307" spans="1:8">
+    <row r="307" spans="1:8" ht="12.5">
       <c r="A307" s="1"/>
       <c r="G307" s="2"/>
       <c r="H307" s="2"/>
     </row>
-    <row r="308" spans="1:8">
+    <row r="308" spans="1:8" ht="12.5">
       <c r="A308" s="1"/>
       <c r="G308" s="2"/>
       <c r="H308" s="2"/>
     </row>
-    <row r="309" spans="1:8">
+    <row r="309" spans="1:8" ht="12.5">
       <c r="A309" s="1"/>
       <c r="G309" s="2"/>
       <c r="H309" s="2"/>
     </row>
-    <row r="310" spans="1:8">
+    <row r="310" spans="1:8" ht="12.5">
       <c r="A310" s="1"/>
       <c r="G310" s="2"/>
       <c r="H310" s="2"/>
     </row>
-    <row r="311" spans="1:8">
+    <row r="311" spans="1:8" ht="12.5">
       <c r="A311" s="1"/>
       <c r="G311" s="2"/>
       <c r="H311" s="2"/>
     </row>
-    <row r="312" spans="1:8">
+    <row r="312" spans="1:8" ht="12.5">
       <c r="A312" s="1"/>
       <c r="G312" s="2"/>
       <c r="H312" s="2"/>
     </row>
-    <row r="313" spans="1:8">
+    <row r="313" spans="1:8" ht="12.5">
       <c r="A313" s="1"/>
       <c r="G313" s="2"/>
       <c r="H313" s="2"/>
     </row>
-    <row r="314" spans="1:8">
+    <row r="314" spans="1:8" ht="12.5">
       <c r="A314" s="1"/>
       <c r="G314" s="2"/>
       <c r="H314" s="2"/>
     </row>
-    <row r="315" spans="1:8">
+    <row r="315" spans="1:8" ht="12.5">
       <c r="A315" s="1"/>
       <c r="G315" s="2"/>
       <c r="H315" s="2"/>
     </row>
-    <row r="316" spans="1:8">
+    <row r="316" spans="1:8" ht="12.5">
       <c r="A316" s="1"/>
       <c r="G316" s="2"/>
       <c r="H316" s="2"/>
     </row>
-    <row r="317" spans="1:8">
+    <row r="317" spans="1:8" ht="12.5">
       <c r="A317" s="1"/>
       <c r="G317" s="2"/>
       <c r="H317" s="2"/>
     </row>
-    <row r="318" spans="1:8">
+    <row r="318" spans="1:8" ht="12.5">
       <c r="A318" s="1"/>
       <c r="G318" s="2"/>
       <c r="H318" s="2"/>
     </row>
-    <row r="319" spans="1:8">
+    <row r="319" spans="1:8" ht="12.5">
       <c r="A319" s="1"/>
       <c r="G319" s="2"/>
       <c r="H319" s="2"/>
     </row>
-    <row r="320" spans="1:8">
+    <row r="320" spans="1:8" ht="12.5">
       <c r="A320" s="1"/>
       <c r="G320" s="2"/>
       <c r="H320" s="2"/>
     </row>
-    <row r="321" spans="1:8">
+    <row r="321" spans="1:8" ht="12.5">
       <c r="A321" s="1"/>
       <c r="G321" s="2"/>
       <c r="H321" s="2"/>
     </row>
-    <row r="322" spans="1:8">
+    <row r="322" spans="1:8" ht="12.5">
       <c r="A322" s="1"/>
       <c r="G322" s="2"/>
       <c r="H322" s="2"/>
     </row>
-    <row r="323" spans="1:8">
+    <row r="323" spans="1:8" ht="12.5">
       <c r="A323" s="1"/>
       <c r="G323" s="2"/>
       <c r="H323" s="2"/>
     </row>
-    <row r="324" spans="1:8">
+    <row r="324" spans="1:8" ht="12.5">
       <c r="A324" s="1"/>
       <c r="G324" s="2"/>
       <c r="H324" s="2"/>
     </row>
-    <row r="325" spans="1:8">
+    <row r="325" spans="1:8" ht="12.5">
       <c r="A325" s="1"/>
       <c r="G325" s="2"/>
       <c r="H325" s="2"/>
     </row>
-    <row r="326" spans="1:8">
+    <row r="326" spans="1:8" ht="12.5">
       <c r="A326" s="1"/>
       <c r="G326" s="2"/>
       <c r="H326" s="2"/>
     </row>
-    <row r="327" spans="1:8">
+    <row r="327" spans="1:8" ht="12.5">
       <c r="A327" s="1"/>
       <c r="G327" s="2"/>
       <c r="H327" s="2"/>
     </row>
-    <row r="328" spans="1:8">
+    <row r="328" spans="1:8" ht="12.5">
       <c r="A328" s="1"/>
       <c r="G328" s="2"/>
       <c r="H328" s="2"/>
     </row>
-    <row r="329" spans="1:8">
+    <row r="329" spans="1:8" ht="12.5">
       <c r="A329" s="1"/>
       <c r="G329" s="2"/>
       <c r="H329" s="2"/>
     </row>
-    <row r="330" spans="1:8">
+    <row r="330" spans="1:8" ht="12.5">
       <c r="A330" s="1"/>
       <c r="G330" s="2"/>
       <c r="H330" s="2"/>
     </row>
-    <row r="331" spans="1:8">
+    <row r="331" spans="1:8" ht="12.5">
       <c r="A331" s="1"/>
       <c r="G331" s="2"/>
       <c r="H331" s="2"/>
     </row>
-    <row r="332" spans="1:8">
+    <row r="332" spans="1:8" ht="12.5">
       <c r="A332" s="1"/>
       <c r="G332" s="2"/>
       <c r="H332" s="2"/>
     </row>
-    <row r="333" spans="1:8">
+    <row r="333" spans="1:8" ht="12.5">
       <c r="A333" s="1"/>
       <c r="G333" s="2"/>
       <c r="H333" s="2"/>
     </row>
-    <row r="334" spans="1:8">
+    <row r="334" spans="1:8" ht="12.5">
       <c r="A334" s="1"/>
       <c r="G334" s="2"/>
       <c r="H334" s="2"/>
     </row>
-    <row r="335" spans="1:8">
+    <row r="335" spans="1:8" ht="12.5">
       <c r="A335" s="1"/>
       <c r="G335" s="2"/>
       <c r="H335" s="2"/>
     </row>
-    <row r="336" spans="1:8">
+    <row r="336" spans="1:8" ht="12.5">
       <c r="A336" s="1"/>
       <c r="G336" s="2"/>
       <c r="H336" s="2"/>
     </row>
-    <row r="337" spans="1:8">
+    <row r="337" spans="1:8" ht="12.5">
       <c r="A337" s="1"/>
       <c r="G337" s="2"/>
       <c r="H337" s="2"/>
     </row>
-    <row r="338" spans="1:8">
+    <row r="338" spans="1:8" ht="12.5">
       <c r="A338" s="1"/>
       <c r="G338" s="2"/>
       <c r="H338" s="2"/>
     </row>
-    <row r="339" spans="1:8">
+    <row r="339" spans="1:8" ht="12.5">
       <c r="A339" s="1"/>
       <c r="G339" s="2"/>
       <c r="H339" s="2"/>
     </row>
-    <row r="340" spans="1:8">
+    <row r="340" spans="1:8" ht="12.5">
       <c r="A340" s="1"/>
       <c r="G340" s="2"/>
       <c r="H340" s="2"/>
     </row>
-    <row r="341" spans="1:8">
+    <row r="341" spans="1:8" ht="12.5">
       <c r="A341" s="1"/>
       <c r="G341" s="2"/>
       <c r="H341" s="2"/>
     </row>
-    <row r="342" spans="1:8">
+    <row r="342" spans="1:8" ht="12.5">
       <c r="A342" s="1"/>
       <c r="G342" s="2"/>
       <c r="H342" s="2"/>
     </row>
-    <row r="343" spans="1:8">
+    <row r="343" spans="1:8" ht="12.5">
       <c r="A343" s="1"/>
       <c r="G343" s="2"/>
       <c r="H343" s="2"/>
     </row>
-    <row r="344" spans="1:8">
+    <row r="344" spans="1:8" ht="12.5">
       <c r="A344" s="1"/>
       <c r="G344" s="2"/>
       <c r="H344" s="2"/>
     </row>
-    <row r="345" spans="1:8">
+    <row r="345" spans="1:8" ht="12.5">
       <c r="A345" s="1"/>
       <c r="G345" s="2"/>
       <c r="H345" s="2"/>
     </row>
-    <row r="346" spans="1:8">
+    <row r="346" spans="1:8" ht="12.5">
       <c r="A346" s="1"/>
       <c r="G346" s="2"/>
       <c r="H346" s="2"/>
     </row>
-    <row r="347" spans="1:8">
+    <row r="347" spans="1:8" ht="12.5">
       <c r="A347" s="1"/>
       <c r="G347" s="2"/>
       <c r="H347" s="2"/>
     </row>
-    <row r="348" spans="1:8">
+    <row r="348" spans="1:8" ht="12.5">
       <c r="A348" s="1"/>
       <c r="G348" s="2"/>
       <c r="H348" s="2"/>
     </row>
-    <row r="349" spans="1:8">
+    <row r="349" spans="1:8" ht="12.5">
       <c r="A349" s="1"/>
       <c r="G349" s="2"/>
       <c r="H349" s="2"/>
     </row>
-    <row r="350" spans="1:8">
+    <row r="350" spans="1:8" ht="12.5">
       <c r="A350" s="1"/>
       <c r="G350" s="2"/>
       <c r="H350" s="2"/>
     </row>
-    <row r="351" spans="1:8">
+    <row r="351" spans="1:8" ht="12.5">
       <c r="A351" s="1"/>
       <c r="G351" s="2"/>
       <c r="H351" s="2"/>
     </row>
-    <row r="352" spans="1:8">
+    <row r="352" spans="1:8" ht="12.5">
       <c r="A352" s="1"/>
       <c r="G352" s="2"/>
       <c r="H352" s="2"/>
     </row>
-    <row r="353" spans="1:8">
+    <row r="353" spans="1:8" ht="12.5">
       <c r="A353" s="1"/>
       <c r="G353" s="2"/>
       <c r="H353" s="2"/>
     </row>
-    <row r="354" spans="1:8">
+    <row r="354" spans="1:8" ht="12.5">
       <c r="A354" s="1"/>
       <c r="G354" s="2"/>
       <c r="H354" s="2"/>
     </row>
-    <row r="355" spans="1:8">
+    <row r="355" spans="1:8" ht="12.5">
       <c r="A355" s="1"/>
       <c r="G355" s="2"/>
       <c r="H355" s="2"/>
     </row>
-    <row r="356" spans="1:8">
+    <row r="356" spans="1:8" ht="12.5">
       <c r="A356" s="1"/>
       <c r="G356" s="2"/>
       <c r="H356" s="2"/>
     </row>
-    <row r="357" spans="1:8">
+    <row r="357" spans="1:8" ht="12.5">
       <c r="A357" s="1"/>
       <c r="G357" s="2"/>
       <c r="H357" s="2"/>
     </row>
-    <row r="358" spans="1:8">
+    <row r="358" spans="1:8" ht="12.5">
       <c r="A358" s="1"/>
       <c r="G358" s="2"/>
       <c r="H358" s="2"/>
     </row>
-    <row r="359" spans="1:8">
+    <row r="359" spans="1:8" ht="12.5">
       <c r="A359" s="1"/>
       <c r="G359" s="2"/>
       <c r="H359" s="2"/>
     </row>
-    <row r="360" spans="1:8">
+    <row r="360" spans="1:8" ht="12.5">
       <c r="A360" s="1"/>
       <c r="G360" s="2"/>
       <c r="H360" s="2"/>
     </row>
-    <row r="361" spans="1:8">
+    <row r="361" spans="1:8" ht="12.5">
       <c r="A361" s="1"/>
       <c r="G361" s="2"/>
       <c r="H361" s="2"/>
     </row>
-    <row r="362" spans="1:8">
+    <row r="362" spans="1:8" ht="12.5">
       <c r="A362" s="1"/>
       <c r="G362" s="2"/>
       <c r="H362" s="2"/>
     </row>
-    <row r="363" spans="1:8">
+    <row r="363" spans="1:8" ht="12.5">
       <c r="A363" s="1"/>
       <c r="G363" s="2"/>
       <c r="H363" s="2"/>
     </row>
-    <row r="364" spans="1:8">
+    <row r="364" spans="1:8" ht="12.5">
       <c r="A364" s="1"/>
       <c r="G364" s="2"/>
       <c r="H364" s="2"/>
     </row>
-    <row r="365" spans="1:8">
+    <row r="365" spans="1:8" ht="12.5">
       <c r="A365" s="1"/>
       <c r="G365" s="2"/>
       <c r="H365" s="2"/>
     </row>
-    <row r="366" spans="1:8">
+    <row r="366" spans="1:8" ht="12.5">
       <c r="A366" s="1"/>
       <c r="G366" s="2"/>
       <c r="H366" s="2"/>
     </row>
-    <row r="367" spans="1:8">
+    <row r="367" spans="1:8" ht="12.5">
       <c r="A367" s="1"/>
       <c r="G367" s="2"/>
       <c r="H367" s="2"/>
     </row>
-    <row r="368" spans="1:8">
+    <row r="368" spans="1:8" ht="12.5">
       <c r="A368" s="1"/>
       <c r="G368" s="2"/>
       <c r="H368" s="2"/>
     </row>
-    <row r="369" spans="1:8">
+    <row r="369" spans="1:8" ht="12.5">
       <c r="A369" s="1"/>
       <c r="G369" s="2"/>
       <c r="H369" s="2"/>
     </row>
-    <row r="370" spans="1:8">
+    <row r="370" spans="1:8" ht="12.5">
       <c r="G370" s="2"/>
       <c r="H370" s="2"/>
     </row>
-    <row r="371" spans="1:8">
+    <row r="371" spans="1:8" ht="12.5">
       <c r="G371" s="2"/>
       <c r="H371" s="2"/>
     </row>
-    <row r="372" spans="1:8">
+    <row r="372" spans="1:8" ht="12.5">
       <c r="G372" s="2"/>
       <c r="H372" s="2"/>
     </row>
-    <row r="373" spans="1:8">
+    <row r="373" spans="1:8" ht="12.5">
       <c r="G373" s="2"/>
       <c r="H373" s="2"/>
     </row>
-    <row r="374" spans="1:8">
+    <row r="374" spans="1:8" ht="12.5">
       <c r="G374" s="2"/>
       <c r="H374" s="2"/>
     </row>
-    <row r="375" spans="1:8">
+    <row r="375" spans="1:8" ht="12.5">
       <c r="G375" s="2"/>
       <c r="H375" s="2"/>
     </row>
-    <row r="376" spans="1:8">
+    <row r="376" spans="1:8" ht="12.5">
       <c r="G376" s="2"/>
       <c r="H376" s="2"/>
     </row>
-    <row r="377" spans="1:8">
+    <row r="377" spans="1:8" ht="12.5">
       <c r="G377" s="2"/>
       <c r="H377" s="2"/>
     </row>
-    <row r="378" spans="1:8">
+    <row r="378" spans="1:8" ht="12.5">
       <c r="G378" s="2"/>
       <c r="H378" s="2"/>
     </row>
-    <row r="379" spans="1:8">
+    <row r="379" spans="1:8" ht="12.5">
       <c r="G379" s="2"/>
       <c r="H379" s="2"/>
     </row>
-    <row r="380" spans="1:8">
+    <row r="380" spans="1:8" ht="12.5">
       <c r="G380" s="2"/>
       <c r="H380" s="2"/>
     </row>
-    <row r="381" spans="1:8">
+    <row r="381" spans="1:8" ht="12.5">
       <c r="G381" s="2"/>
       <c r="H381" s="2"/>
     </row>
-    <row r="382" spans="1:8">
+    <row r="382" spans="1:8" ht="12.5">
       <c r="G382" s="2"/>
       <c r="H382" s="2"/>
     </row>
-    <row r="383" spans="1:8">
+    <row r="383" spans="1:8" ht="12.5">
       <c r="G383" s="2"/>
       <c r="H383" s="2"/>
     </row>
-    <row r="384" spans="1:8">
+    <row r="384" spans="1:8" ht="12.5">
       <c r="G384" s="2"/>
       <c r="H384" s="2"/>
     </row>
-    <row r="385" spans="7:8">
+    <row r="385" spans="7:8" ht="12.5">
       <c r="G385" s="2"/>
       <c r="H385" s="2"/>
     </row>
-    <row r="386" spans="7:8">
+    <row r="386" spans="7:8" ht="12.5">
       <c r="G386" s="2"/>
       <c r="H386" s="2"/>
     </row>
-    <row r="387" spans="7:8">
+    <row r="387" spans="7:8" ht="12.5">
       <c r="G387" s="2"/>
       <c r="H387" s="2"/>
     </row>
-    <row r="388" spans="7:8">
+    <row r="388" spans="7:8" ht="12.5">
       <c r="G388" s="2"/>
       <c r="H388" s="2"/>
     </row>
-    <row r="389" spans="7:8">
+    <row r="389" spans="7:8" ht="12.5">
       <c r="G389" s="2"/>
       <c r="H389" s="2"/>
     </row>
-    <row r="390" spans="7:8">
+    <row r="390" spans="7:8" ht="12.5">
       <c r="G390" s="2"/>
       <c r="H390" s="2"/>
     </row>
-    <row r="391" spans="7:8">
+    <row r="391" spans="7:8" ht="12.5">
       <c r="G391" s="2"/>
       <c r="H391" s="2"/>
     </row>
-    <row r="392" spans="7:8">
+    <row r="392" spans="7:8" ht="12.5">
       <c r="G392" s="2"/>
       <c r="H392" s="2"/>
     </row>
-    <row r="393" spans="7:8">
+    <row r="393" spans="7:8" ht="12.5">
       <c r="G393" s="2"/>
       <c r="H393" s="2"/>
     </row>
-    <row r="394" spans="7:8">
+    <row r="394" spans="7:8" ht="12.5">
       <c r="G394" s="2"/>
       <c r="H394" s="2"/>
     </row>
-    <row r="395" spans="7:8">
+    <row r="395" spans="7:8" ht="12.5">
       <c r="G395" s="2"/>
       <c r="H395" s="2"/>
     </row>
-    <row r="396" spans="7:8">
+    <row r="396" spans="7:8" ht="12.5">
       <c r="G396" s="2"/>
       <c r="H396" s="2"/>
     </row>
-    <row r="397" spans="7:8">
+    <row r="397" spans="7:8" ht="12.5">
       <c r="G397" s="2"/>
       <c r="H397" s="2"/>
     </row>
-    <row r="398" spans="7:8">
+    <row r="398" spans="7:8" ht="12.5">
       <c r="G398" s="2"/>
       <c r="H398" s="2"/>
     </row>
-    <row r="399" spans="7:8">
+    <row r="399" spans="7:8" ht="12.5">
       <c r="G399" s="2"/>
       <c r="H399" s="2"/>
     </row>
-    <row r="400" spans="7:8">
+    <row r="400" spans="7:8" ht="12.5">
       <c r="G400" s="2"/>
       <c r="H400" s="2"/>
     </row>
-    <row r="401" spans="7:8">
+    <row r="401" spans="7:8" ht="12.5">
       <c r="G401" s="2"/>
       <c r="H401" s="2"/>
     </row>
-    <row r="402" spans="7:8">
+    <row r="402" spans="7:8" ht="12.5">
       <c r="G402" s="2"/>
       <c r="H402" s="2"/>
     </row>
-    <row r="403" spans="7:8">
+    <row r="403" spans="7:8" ht="12.5">
       <c r="G403" s="2"/>
       <c r="H403" s="2"/>
     </row>
-    <row r="404" spans="7:8">
+    <row r="404" spans="7:8" ht="12.5">
       <c r="G404" s="2"/>
       <c r="H404" s="2"/>
     </row>
-    <row r="405" spans="7:8">
+    <row r="405" spans="7:8" ht="12.5">
       <c r="G405" s="2"/>
       <c r="H405" s="2"/>
     </row>
-    <row r="406" spans="7:8">
+    <row r="406" spans="7:8" ht="12.5">
       <c r="G406" s="2"/>
       <c r="H406" s="2"/>
     </row>
-    <row r="407" spans="7:8">
+    <row r="407" spans="7:8" ht="12.5">
       <c r="G407" s="2"/>
       <c r="H407" s="2"/>
     </row>
-    <row r="408" spans="7:8">
+    <row r="408" spans="7:8" ht="12.5">
       <c r="G408" s="2"/>
       <c r="H408" s="2"/>
     </row>
-    <row r="409" spans="7:8">
+    <row r="409" spans="7:8" ht="12.5">
       <c r="G409" s="2"/>
       <c r="H409" s="2"/>
     </row>
-    <row r="410" spans="7:8">
+    <row r="410" spans="7:8" ht="12.5">
       <c r="G410" s="2"/>
       <c r="H410" s="2"/>
     </row>
-    <row r="411" spans="7:8">
+    <row r="411" spans="7:8" ht="12.5">
       <c r="G411" s="2"/>
       <c r="H411" s="2"/>
     </row>
-    <row r="412" spans="7:8">
+    <row r="412" spans="7:8" ht="12.5">
       <c r="G412" s="2"/>
       <c r="H412" s="2"/>
     </row>
-    <row r="413" spans="7:8">
+    <row r="413" spans="7:8" ht="12.5">
       <c r="G413" s="2"/>
       <c r="H413" s="2"/>
     </row>
-    <row r="414" spans="7:8">
+    <row r="414" spans="7:8" ht="12.5">
       <c r="G414" s="2"/>
       <c r="H414" s="2"/>
     </row>
-    <row r="415" spans="7:8">
+    <row r="415" spans="7:8" ht="12.5">
       <c r="G415" s="2"/>
       <c r="H415" s="2"/>
     </row>
-    <row r="416" spans="7:8">
+    <row r="416" spans="7:8" ht="12.5">
       <c r="G416" s="2"/>
       <c r="H416" s="2"/>
     </row>
-    <row r="417" spans="7:8">
+    <row r="417" spans="7:8" ht="12.5">
       <c r="G417" s="2"/>
       <c r="H417" s="2"/>
     </row>
-    <row r="418" spans="7:8">
+    <row r="418" spans="7:8" ht="12.5">
       <c r="G418" s="2"/>
       <c r="H418" s="2"/>
     </row>
-    <row r="419" spans="7:8">
+    <row r="419" spans="7:8" ht="12.5">
       <c r="G419" s="2"/>
       <c r="H419" s="2"/>
     </row>
-    <row r="420" spans="7:8">
+    <row r="420" spans="7:8" ht="12.5">
       <c r="G420" s="2"/>
       <c r="H420" s="2"/>
     </row>
-    <row r="421" spans="7:8">
+    <row r="421" spans="7:8" ht="12.5">
       <c r="G421" s="2"/>
       <c r="H421" s="2"/>
     </row>
-    <row r="422" spans="7:8">
+    <row r="422" spans="7:8" ht="12.5">
       <c r="G422" s="2"/>
       <c r="H422" s="2"/>
     </row>
-    <row r="423" spans="7:8">
+    <row r="423" spans="7:8" ht="12.5">
       <c r="G423" s="2"/>
       <c r="H423" s="2"/>
     </row>
-    <row r="424" spans="7:8">
+    <row r="424" spans="7:8" ht="12.5">
       <c r="G424" s="2"/>
       <c r="H424" s="2"/>
     </row>
-    <row r="425" spans="7:8">
+    <row r="425" spans="7:8" ht="12.5">
       <c r="G425" s="2"/>
       <c r="H425" s="2"/>
     </row>
-    <row r="426" spans="7:8">
+    <row r="426" spans="7:8" ht="12.5">
       <c r="G426" s="2"/>
       <c r="H426" s="2"/>
     </row>
-    <row r="427" spans="7:8">
+    <row r="427" spans="7:8" ht="12.5">
       <c r="G427" s="2"/>
       <c r="H427" s="2"/>
     </row>
-    <row r="428" spans="7:8">
+    <row r="428" spans="7:8" ht="12.5">
       <c r="G428" s="2"/>
       <c r="H428" s="2"/>
     </row>
-    <row r="429" spans="7:8">
+    <row r="429" spans="7:8" ht="12.5">
       <c r="G429" s="2"/>
       <c r="H429" s="2"/>
     </row>
-    <row r="430" spans="7:8">
+    <row r="430" spans="7:8" ht="12.5">
       <c r="G430" s="2"/>
       <c r="H430" s="2"/>
     </row>
-    <row r="431" spans="7:8">
+    <row r="431" spans="7:8" ht="12.5">
       <c r="G431" s="2"/>
       <c r="H431" s="2"/>
     </row>
-    <row r="432" spans="7:8">
+    <row r="432" spans="7:8" ht="12.5">
       <c r="G432" s="2"/>
       <c r="H432" s="2"/>
     </row>
-    <row r="433" spans="7:8">
+    <row r="433" spans="7:8" ht="12.5">
       <c r="G433" s="2"/>
       <c r="H433" s="2"/>
     </row>
-    <row r="434" spans="7:8">
+    <row r="434" spans="7:8" ht="12.5">
       <c r="G434" s="2"/>
       <c r="H434" s="2"/>
     </row>
-    <row r="435" spans="7:8">
+    <row r="435" spans="7:8" ht="12.5">
       <c r="G435" s="2"/>
       <c r="H435" s="2"/>
     </row>
-    <row r="436" spans="7:8">
+    <row r="436" spans="7:8" ht="12.5">
       <c r="G436" s="2"/>
       <c r="H436" s="2"/>
     </row>
-    <row r="437" spans="7:8">
+    <row r="437" spans="7:8" ht="12.5">
       <c r="G437" s="2"/>
       <c r="H437" s="2"/>
     </row>
-    <row r="438" spans="7:8">
+    <row r="438" spans="7:8" ht="12.5">
       <c r="G438" s="2"/>
       <c r="H438" s="2"/>
     </row>
-    <row r="439" spans="7:8">
+    <row r="439" spans="7:8" ht="12.5">
       <c r="G439" s="2"/>
       <c r="H439" s="2"/>
     </row>
-    <row r="440" spans="7:8">
+    <row r="440" spans="7:8" ht="12.5">
       <c r="G440" s="2"/>
       <c r="H440" s="2"/>
     </row>
-    <row r="441" spans="7:8">
+    <row r="441" spans="7:8" ht="12.5">
       <c r="G441" s="2"/>
       <c r="H441" s="2"/>
     </row>
-    <row r="442" spans="7:8">
+    <row r="442" spans="7:8" ht="12.5">
       <c r="G442" s="2"/>
       <c r="H442" s="2"/>
     </row>
-    <row r="443" spans="7:8">
+    <row r="443" spans="7:8" ht="12.5">
       <c r="G443" s="2"/>
       <c r="H443" s="2"/>
     </row>
-    <row r="444" spans="7:8">
+    <row r="444" spans="7:8" ht="12.5">
       <c r="G444" s="2"/>
       <c r="H444" s="2"/>
     </row>
-    <row r="445" spans="7:8">
+    <row r="445" spans="7:8" ht="12.5">
       <c r="G445" s="2"/>
       <c r="H445" s="2"/>
     </row>
-    <row r="446" spans="7:8">
+    <row r="446" spans="7:8" ht="12.5">
       <c r="G446" s="2"/>
       <c r="H446" s="2"/>
     </row>
-    <row r="447" spans="7:8">
+    <row r="447" spans="7:8" ht="12.5">
       <c r="G447" s="2"/>
       <c r="H447" s="2"/>
     </row>
-    <row r="448" spans="7:8">
+    <row r="448" spans="7:8" ht="12.5">
       <c r="G448" s="2"/>
       <c r="H448" s="2"/>
     </row>
-    <row r="449" spans="7:8">
+    <row r="449" spans="7:8" ht="12.5">
       <c r="G449" s="2"/>
       <c r="H449" s="2"/>
     </row>
-    <row r="450" spans="7:8">
+    <row r="450" spans="7:8" ht="12.5">
       <c r="G450" s="2"/>
       <c r="H450" s="2"/>
     </row>
-    <row r="451" spans="7:8">
+    <row r="451" spans="7:8" ht="12.5">
       <c r="G451" s="2"/>
       <c r="H451" s="2"/>
     </row>
-    <row r="452" spans="7:8">
+    <row r="452" spans="7:8" ht="12.5">
       <c r="G452" s="2"/>
       <c r="H452" s="2"/>
     </row>
-    <row r="453" spans="7:8">
+    <row r="453" spans="7:8" ht="12.5">
       <c r="G453" s="2"/>
       <c r="H453" s="2"/>
     </row>
-    <row r="454" spans="7:8">
+    <row r="454" spans="7:8" ht="12.5">
       <c r="G454" s="2"/>
       <c r="H454" s="2"/>
     </row>
-    <row r="455" spans="7:8">
+    <row r="455" spans="7:8" ht="12.5">
       <c r="G455" s="2"/>
       <c r="H455" s="2"/>
     </row>
-    <row r="456" spans="7:8">
+    <row r="456" spans="7:8" ht="12.5">
       <c r="G456" s="2"/>
       <c r="H456" s="2"/>
     </row>
-    <row r="457" spans="7:8">
+    <row r="457" spans="7:8" ht="12.5">
       <c r="G457" s="2"/>
       <c r="H457" s="2"/>
     </row>
-    <row r="458" spans="7:8">
+    <row r="458" spans="7:8" ht="12.5">
       <c r="G458" s="2"/>
       <c r="H458" s="2"/>
     </row>
-    <row r="459" spans="7:8">
+    <row r="459" spans="7:8" ht="12.5">
       <c r="G459" s="2"/>
       <c r="H459" s="2"/>
     </row>
-    <row r="460" spans="7:8">
+    <row r="460" spans="7:8" ht="12.5">
       <c r="G460" s="2"/>
       <c r="H460" s="2"/>
     </row>
-    <row r="461" spans="7:8">
+    <row r="461" spans="7:8" ht="12.5">
       <c r="G461" s="2"/>
       <c r="H461" s="2"/>
     </row>
-    <row r="462" spans="7:8">
+    <row r="462" spans="7:8" ht="12.5">
       <c r="G462" s="2"/>
       <c r="H462" s="2"/>
     </row>
-    <row r="463" spans="7:8">
+    <row r="463" spans="7:8" ht="12.5">
       <c r="G463" s="2"/>
       <c r="H463" s="2"/>
     </row>
-    <row r="464" spans="7:8">
+    <row r="464" spans="7:8" ht="12.5">
       <c r="G464" s="2"/>
       <c r="H464" s="2"/>
     </row>
-    <row r="465" spans="7:8">
+    <row r="465" spans="7:8" ht="12.5">
       <c r="G465" s="2"/>
       <c r="H465" s="2"/>
     </row>
-    <row r="466" spans="7:8">
+    <row r="466" spans="7:8" ht="12.5">
       <c r="G466" s="2"/>
       <c r="H466" s="2"/>
     </row>
-    <row r="467" spans="7:8">
+    <row r="467" spans="7:8" ht="12.5">
       <c r="G467" s="2"/>
       <c r="H467" s="2"/>
     </row>
-    <row r="468" spans="7:8">
+    <row r="468" spans="7:8" ht="12.5">
       <c r="G468" s="2"/>
       <c r="H468" s="2"/>
     </row>
-    <row r="469" spans="7:8">
+    <row r="469" spans="7:8" ht="12.5">
       <c r="G469" s="2"/>
       <c r="H469" s="2"/>
     </row>
-    <row r="470" spans="7:8">
+    <row r="470" spans="7:8" ht="12.5">
       <c r="G470" s="2"/>
       <c r="H470" s="2"/>
     </row>
-    <row r="471" spans="7:8">
+    <row r="471" spans="7:8" ht="12.5">
       <c r="G471" s="2"/>
       <c r="H471" s="2"/>
     </row>
-    <row r="472" spans="7:8">
+    <row r="472" spans="7:8" ht="12.5">
       <c r="G472" s="2"/>
       <c r="H472" s="2"/>
     </row>
-    <row r="473" spans="7:8">
+    <row r="473" spans="7:8" ht="12.5">
       <c r="G473" s="2"/>
       <c r="H473" s="2"/>
     </row>
-    <row r="474" spans="7:8">
+    <row r="474" spans="7:8" ht="12.5">
       <c r="G474" s="2"/>
       <c r="H474" s="2"/>
     </row>
-    <row r="475" spans="7:8">
+    <row r="475" spans="7:8" ht="12.5">
       <c r="G475" s="2"/>
       <c r="H475" s="2"/>
     </row>
-    <row r="476" spans="7:8">
+    <row r="476" spans="7:8" ht="12.5">
       <c r="G476" s="2"/>
       <c r="H476" s="2"/>
     </row>
-    <row r="477" spans="7:8">
+    <row r="477" spans="7:8" ht="12.5">
       <c r="G477" s="2"/>
       <c r="H477" s="2"/>
     </row>
-    <row r="478" spans="7:8">
+    <row r="478" spans="7:8" ht="12.5">
       <c r="G478" s="2"/>
       <c r="H478" s="2"/>
     </row>
-    <row r="479" spans="7:8">
+    <row r="479" spans="7:8" ht="12.5">
       <c r="G479" s="2"/>
       <c r="H479" s="2"/>
     </row>
-    <row r="480" spans="7:8">
+    <row r="480" spans="7:8" ht="12.5">
       <c r="G480" s="2"/>
       <c r="H480" s="2"/>
     </row>
-    <row r="481" spans="7:8">
+    <row r="481" spans="7:8" ht="12.5">
       <c r="G481" s="2"/>
       <c r="H481" s="2"/>
     </row>
-    <row r="482" spans="7:8">
+    <row r="482" spans="7:8" ht="12.5">
       <c r="G482" s="2"/>
       <c r="H482" s="2"/>
     </row>
-    <row r="483" spans="7:8">
+    <row r="483" spans="7:8" ht="12.5">
       <c r="G483" s="2"/>
       <c r="H483" s="2"/>
     </row>
-    <row r="484" spans="7:8">
+    <row r="484" spans="7:8" ht="12.5">
       <c r="G484" s="2"/>
       <c r="H484" s="2"/>
     </row>
-    <row r="485" spans="7:8">
+    <row r="485" spans="7:8" ht="12.5">
       <c r="G485" s="2"/>
       <c r="H485" s="2"/>
     </row>
-    <row r="486" spans="7:8">
+    <row r="486" spans="7:8" ht="12.5">
       <c r="G486" s="2"/>
       <c r="H486" s="2"/>
     </row>
-    <row r="487" spans="7:8">
+    <row r="487" spans="7:8" ht="12.5">
       <c r="G487" s="2"/>
       <c r="H487" s="2"/>
     </row>
-    <row r="488" spans="7:8">
+    <row r="488" spans="7:8" ht="12.5">
       <c r="G488" s="2"/>
       <c r="H488" s="2"/>
     </row>
-    <row r="489" spans="7:8">
+    <row r="489" spans="7:8" ht="12.5">
       <c r="G489" s="2"/>
       <c r="H489" s="2"/>
     </row>
-    <row r="490" spans="7:8">
+    <row r="490" spans="7:8" ht="12.5">
       <c r="G490" s="2"/>
       <c r="H490" s="2"/>
     </row>
-    <row r="491" spans="7:8">
+    <row r="491" spans="7:8" ht="12.5">
       <c r="G491" s="2"/>
       <c r="H491" s="2"/>
     </row>
-    <row r="492" spans="7:8">
+    <row r="492" spans="7:8" ht="12.5">
       <c r="G492" s="2"/>
       <c r="H492" s="2"/>
     </row>
-    <row r="493" spans="7:8">
+    <row r="493" spans="7:8" ht="12.5">
       <c r="G493" s="2"/>
       <c r="H493" s="2"/>
     </row>
-    <row r="494" spans="7:8">
+    <row r="494" spans="7:8" ht="12.5">
       <c r="G494" s="2"/>
       <c r="H494" s="2"/>
     </row>
-    <row r="495" spans="7:8">
+    <row r="495" spans="7:8" ht="12.5">
       <c r="G495" s="2"/>
       <c r="H495" s="2"/>
     </row>
-    <row r="496" spans="7:8">
+    <row r="496" spans="7:8" ht="12.5">
       <c r="G496" s="2"/>
       <c r="H496" s="2"/>
     </row>
-    <row r="497" spans="7:8">
+    <row r="497" spans="7:8" ht="12.5">
       <c r="G497" s="2"/>
       <c r="H497" s="2"/>
     </row>
-    <row r="498" spans="7:8">
+    <row r="498" spans="7:8" ht="12.5">
       <c r="G498" s="2"/>
       <c r="H498" s="2"/>
     </row>
-    <row r="499" spans="7:8">
+    <row r="499" spans="7:8" ht="12.5">
       <c r="G499" s="2"/>
       <c r="H499" s="2"/>
     </row>
-    <row r="500" spans="7:8">
+    <row r="500" spans="7:8" ht="12.5">
       <c r="G500" s="2"/>
       <c r="H500" s="2"/>
     </row>
-    <row r="501" spans="7:8">
+    <row r="501" spans="7:8" ht="12.5">
       <c r="G501" s="2"/>
       <c r="H501" s="2"/>
     </row>
-    <row r="502" spans="7:8">
+    <row r="502" spans="7:8" ht="12.5">
       <c r="G502" s="2"/>
       <c r="H502" s="2"/>
     </row>
-    <row r="503" spans="7:8">
+    <row r="503" spans="7:8" ht="12.5">
       <c r="G503" s="2"/>
       <c r="H503" s="2"/>
     </row>
-    <row r="504" spans="7:8">
+    <row r="504" spans="7:8" ht="12.5">
       <c r="G504" s="2"/>
       <c r="H504" s="2"/>
     </row>
-    <row r="505" spans="7:8">
+    <row r="505" spans="7:8" ht="12.5">
       <c r="G505" s="2"/>
       <c r="H505" s="2"/>
     </row>
-    <row r="506" spans="7:8">
+    <row r="506" spans="7:8" ht="12.5">
       <c r="G506" s="2"/>
       <c r="H506" s="2"/>
     </row>
-    <row r="507" spans="7:8">
+    <row r="507" spans="7:8" ht="12.5">
       <c r="G507" s="2"/>
       <c r="H507" s="2"/>
     </row>
-    <row r="508" spans="7:8">
+    <row r="508" spans="7:8" ht="12.5">
       <c r="G508" s="2"/>
       <c r="H508" s="2"/>
     </row>
-    <row r="509" spans="7:8">
+    <row r="509" spans="7:8" ht="12.5">
       <c r="G509" s="2"/>
       <c r="H509" s="2"/>
     </row>
-    <row r="510" spans="7:8">
+    <row r="510" spans="7:8" ht="12.5">
       <c r="G510" s="2"/>
       <c r="H510" s="2"/>
     </row>
-    <row r="511" spans="7:8">
+    <row r="511" spans="7:8" ht="12.5">
       <c r="G511" s="2"/>
       <c r="H511" s="2"/>
     </row>
-    <row r="512" spans="7:8">
+    <row r="512" spans="7:8" ht="12.5">
       <c r="G512" s="2"/>
       <c r="H512" s="2"/>
     </row>
-    <row r="513" spans="7:8">
+    <row r="513" spans="7:8" ht="12.5">
       <c r="G513" s="2"/>
       <c r="H513" s="2"/>
     </row>
-    <row r="514" spans="7:8">
+    <row r="514" spans="7:8" ht="12.5">
       <c r="G514" s="2"/>
       <c r="H514" s="2"/>
     </row>
-    <row r="515" spans="7:8">
+    <row r="515" spans="7:8" ht="12.5">
       <c r="G515" s="2"/>
       <c r="H515" s="2"/>
     </row>
-    <row r="516" spans="7:8">
+    <row r="516" spans="7:8" ht="12.5">
       <c r="G516" s="2"/>
       <c r="H516" s="2"/>
     </row>
-    <row r="517" spans="7:8">
+    <row r="517" spans="7:8" ht="12.5">
       <c r="G517" s="2"/>
       <c r="H517" s="2"/>
     </row>
-    <row r="518" spans="7:8">
+    <row r="518" spans="7:8" ht="12.5">
       <c r="G518" s="2"/>
       <c r="H518" s="2"/>
     </row>
-    <row r="519" spans="7:8">
+    <row r="519" spans="7:8" ht="12.5">
       <c r="G519" s="2"/>
       <c r="H519" s="2"/>
     </row>
-    <row r="520" spans="7:8">
+    <row r="520" spans="7:8" ht="12.5">
       <c r="G520" s="2"/>
       <c r="H520" s="2"/>
     </row>
-    <row r="521" spans="7:8">
+    <row r="521" spans="7:8" ht="12.5">
       <c r="G521" s="2"/>
       <c r="H521" s="2"/>
     </row>
-    <row r="522" spans="7:8">
+    <row r="522" spans="7:8" ht="12.5">
       <c r="G522" s="2"/>
       <c r="H522" s="2"/>
     </row>
-    <row r="523" spans="7:8">
+    <row r="523" spans="7:8" ht="12.5">
       <c r="G523" s="2"/>
       <c r="H523" s="2"/>
     </row>
-    <row r="524" spans="7:8">
+    <row r="524" spans="7:8" ht="12.5">
       <c r="G524" s="2"/>
       <c r="H524" s="2"/>
     </row>
-    <row r="525" spans="7:8">
+    <row r="525" spans="7:8" ht="12.5">
       <c r="G525" s="2"/>
       <c r="H525" s="2"/>
     </row>
-    <row r="526" spans="7:8">
+    <row r="526" spans="7:8" ht="12.5">
       <c r="G526" s="2"/>
       <c r="H526" s="2"/>
     </row>
-    <row r="527" spans="7:8">
+    <row r="527" spans="7:8" ht="12.5">
       <c r="G527" s="2"/>
       <c r="H527" s="2"/>
     </row>
-    <row r="528" spans="7:8">
+    <row r="528" spans="7:8" ht="12.5">
       <c r="G528" s="2"/>
       <c r="H528" s="2"/>
     </row>
-    <row r="529" spans="7:8">
+    <row r="529" spans="7:8" ht="12.5">
       <c r="G529" s="2"/>
       <c r="H529" s="2"/>
     </row>
-    <row r="530" spans="7:8">
+    <row r="530" spans="7:8" ht="12.5">
       <c r="G530" s="2"/>
       <c r="H530" s="2"/>
     </row>
-    <row r="531" spans="7:8">
+    <row r="531" spans="7:8" ht="12.5">
       <c r="G531" s="2"/>
       <c r="H531" s="2"/>
     </row>
-    <row r="532" spans="7:8">
+    <row r="532" spans="7:8" ht="12.5">
       <c r="G532" s="2"/>
       <c r="H532" s="2"/>
     </row>
-    <row r="533" spans="7:8">
+    <row r="533" spans="7:8" ht="12.5">
       <c r="G533" s="2"/>
       <c r="H533" s="2"/>
     </row>
-    <row r="534" spans="7:8">
+    <row r="534" spans="7:8" ht="12.5">
       <c r="G534" s="2"/>
       <c r="H534" s="2"/>
     </row>
-    <row r="535" spans="7:8">
+    <row r="535" spans="7:8" ht="12.5">
       <c r="G535" s="2"/>
       <c r="H535" s="2"/>
     </row>
-    <row r="536" spans="7:8">
+    <row r="536" spans="7:8" ht="12.5">
       <c r="G536" s="2"/>
       <c r="H536" s="2"/>
     </row>
-    <row r="537" spans="7:8">
+    <row r="537" spans="7:8" ht="12.5">
       <c r="G537" s="2"/>
       <c r="H537" s="2"/>
     </row>
-    <row r="538" spans="7:8">
+    <row r="538" spans="7:8" ht="12.5">
       <c r="G538" s="2"/>
       <c r="H538" s="2"/>
     </row>
-    <row r="539" spans="7:8">
+    <row r="539" spans="7:8" ht="12.5">
       <c r="G539" s="2"/>
       <c r="H539" s="2"/>
     </row>
-    <row r="540" spans="7:8">
+    <row r="540" spans="7:8" ht="12.5">
       <c r="G540" s="2"/>
       <c r="H540" s="2"/>
     </row>
-    <row r="541" spans="7:8">
+    <row r="541" spans="7:8" ht="12.5">
       <c r="G541" s="2"/>
       <c r="H541" s="2"/>
     </row>
-    <row r="542" spans="7:8">
+    <row r="542" spans="7:8" ht="12.5">
       <c r="G542" s="2"/>
       <c r="H542" s="2"/>
     </row>
-    <row r="543" spans="7:8">
+    <row r="543" spans="7:8" ht="12.5">
       <c r="G543" s="2"/>
       <c r="H543" s="2"/>
     </row>
-    <row r="544" spans="7:8">
+    <row r="544" spans="7:8" ht="12.5">
       <c r="G544" s="2"/>
       <c r="H544" s="2"/>
     </row>
-    <row r="545" spans="7:8">
+    <row r="545" spans="7:8" ht="12.5">
       <c r="G545" s="2"/>
       <c r="H545" s="2"/>
     </row>
-    <row r="546" spans="7:8">
+    <row r="546" spans="7:8" ht="12.5">
       <c r="G546" s="2"/>
       <c r="H546" s="2"/>
     </row>
-    <row r="547" spans="7:8">
+    <row r="547" spans="7:8" ht="12.5">
       <c r="G547" s="2"/>
       <c r="H547" s="2"/>
     </row>
-    <row r="548" spans="7:8">
+    <row r="548" spans="7:8" ht="12.5">
       <c r="G548" s="2"/>
       <c r="H548" s="2"/>
     </row>
-    <row r="549" spans="7:8">
+    <row r="549" spans="7:8" ht="12.5">
       <c r="G549" s="2"/>
       <c r="H549" s="2"/>
     </row>
-    <row r="550" spans="7:8">
+    <row r="550" spans="7:8" ht="12.5">
       <c r="G550" s="2"/>
       <c r="H550" s="2"/>
     </row>
-    <row r="551" spans="7:8">
+    <row r="551" spans="7:8" ht="12.5">
       <c r="G551" s="2"/>
       <c r="H551" s="2"/>
     </row>
-    <row r="552" spans="7:8">
+    <row r="552" spans="7:8" ht="12.5">
       <c r="G552" s="2"/>
       <c r="H552" s="2"/>
     </row>
-    <row r="553" spans="7:8">
+    <row r="553" spans="7:8" ht="12.5">
       <c r="G553" s="2"/>
       <c r="H553" s="2"/>
     </row>
-    <row r="554" spans="7:8">
+    <row r="554" spans="7:8" ht="12.5">
       <c r="G554" s="2"/>
       <c r="H554" s="2"/>
     </row>
-    <row r="555" spans="7:8">
+    <row r="555" spans="7:8" ht="12.5">
       <c r="G555" s="2"/>
       <c r="H555" s="2"/>
     </row>
-    <row r="556" spans="7:8">
+    <row r="556" spans="7:8" ht="12.5">
       <c r="G556" s="2"/>
       <c r="H556" s="2"/>
     </row>
-    <row r="557" spans="7:8">
+    <row r="557" spans="7:8" ht="12.5">
       <c r="G557" s="2"/>
       <c r="H557" s="2"/>
     </row>
-    <row r="558" spans="7:8">
+    <row r="558" spans="7:8" ht="12.5">
       <c r="G558" s="2"/>
       <c r="H558" s="2"/>
     </row>
-    <row r="559" spans="7:8">
+    <row r="559" spans="7:8" ht="12.5">
       <c r="G559" s="2"/>
       <c r="H559" s="2"/>
     </row>
-    <row r="560" spans="7:8">
+    <row r="560" spans="7:8" ht="12.5">
       <c r="G560" s="2"/>
       <c r="H560" s="2"/>
     </row>
-    <row r="561" spans="7:8">
+    <row r="561" spans="7:8" ht="12.5">
       <c r="G561" s="2"/>
       <c r="H561" s="2"/>
     </row>
-    <row r="562" spans="7:8">
+    <row r="562" spans="7:8" ht="12.5">
       <c r="G562" s="2"/>
       <c r="H562" s="2"/>
     </row>
-    <row r="563" spans="7:8">
+    <row r="563" spans="7:8" ht="12.5">
       <c r="G563" s="2"/>
       <c r="H563" s="2"/>
     </row>
-    <row r="564" spans="7:8">
+    <row r="564" spans="7:8" ht="12.5">
       <c r="G564" s="2"/>
       <c r="H564" s="2"/>
     </row>
-    <row r="565" spans="7:8">
+    <row r="565" spans="7:8" ht="12.5">
       <c r="G565" s="2"/>
       <c r="H565" s="2"/>
     </row>
-    <row r="566" spans="7:8">
+    <row r="566" spans="7:8" ht="12.5">
       <c r="G566" s="2"/>
       <c r="H566" s="2"/>
     </row>
-    <row r="567" spans="7:8">
+    <row r="567" spans="7:8" ht="12.5">
       <c r="G567" s="2"/>
       <c r="H567" s="2"/>
     </row>
-    <row r="568" spans="7:8">
+    <row r="568" spans="7:8" ht="12.5">
       <c r="G568" s="2"/>
       <c r="H568" s="2"/>
     </row>
-    <row r="569" spans="7:8">
+    <row r="569" spans="7:8" ht="12.5">
       <c r="G569" s="2"/>
       <c r="H569" s="2"/>
     </row>
-    <row r="570" spans="7:8">
+    <row r="570" spans="7:8" ht="12.5">
       <c r="G570" s="2"/>
       <c r="H570" s="2"/>
     </row>
-    <row r="571" spans="7:8">
+    <row r="571" spans="7:8" ht="12.5">
       <c r="G571" s="2"/>
       <c r="H571" s="2"/>
     </row>
-    <row r="572" spans="7:8">
+    <row r="572" spans="7:8" ht="12.5">
       <c r="G572" s="2"/>
       <c r="H572" s="2"/>
     </row>
-    <row r="573" spans="7:8">
+    <row r="573" spans="7:8" ht="12.5">
       <c r="G573" s="2"/>
       <c r="H573" s="2"/>
     </row>
-    <row r="574" spans="7:8">
+    <row r="574" spans="7:8" ht="12.5">
       <c r="G574" s="2"/>
       <c r="H574" s="2"/>
     </row>
-    <row r="575" spans="7:8">
+    <row r="575" spans="7:8" ht="12.5">
       <c r="G575" s="2"/>
       <c r="H575" s="2"/>
     </row>
-    <row r="576" spans="7:8">
+    <row r="576" spans="7:8" ht="12.5">
       <c r="G576" s="2"/>
       <c r="H576" s="2"/>
     </row>
-    <row r="577" spans="7:8">
+    <row r="577" spans="7:8" ht="12.5">
       <c r="G577" s="2"/>
       <c r="H577" s="2"/>
     </row>
-    <row r="578" spans="7:8">
+    <row r="578" spans="7:8" ht="12.5">
       <c r="G578" s="2"/>
       <c r="H578" s="2"/>
     </row>
-    <row r="579" spans="7:8">
+    <row r="579" spans="7:8" ht="12.5">
       <c r="G579" s="2"/>
       <c r="H579" s="2"/>
     </row>
-    <row r="580" spans="7:8">
+    <row r="580" spans="7:8" ht="12.5">
       <c r="G580" s="2"/>
       <c r="H580" s="2"/>
     </row>
-    <row r="581" spans="7:8">
+    <row r="581" spans="7:8" ht="12.5">
       <c r="G581" s="2"/>
       <c r="H581" s="2"/>
     </row>
-    <row r="582" spans="7:8">
+    <row r="582" spans="7:8" ht="12.5">
       <c r="G582" s="2"/>
       <c r="H582" s="2"/>
     </row>
-    <row r="583" spans="7:8">
+    <row r="583" spans="7:8" ht="12.5">
       <c r="G583" s="2"/>
       <c r="H583" s="2"/>
     </row>
-    <row r="584" spans="7:8">
+    <row r="584" spans="7:8" ht="12.5">
       <c r="G584" s="2"/>
       <c r="H584" s="2"/>
     </row>
-    <row r="585" spans="7:8">
+    <row r="585" spans="7:8" ht="12.5">
       <c r="G585" s="2"/>
       <c r="H585" s="2"/>
     </row>
-    <row r="586" spans="7:8">
+    <row r="586" spans="7:8" ht="12.5">
       <c r="G586" s="2"/>
       <c r="H586" s="2"/>
     </row>
-    <row r="587" spans="7:8">
+    <row r="587" spans="7:8" ht="12.5">
       <c r="G587" s="2"/>
       <c r="H587" s="2"/>
     </row>
-    <row r="588" spans="7:8">
+    <row r="588" spans="7:8" ht="12.5">
       <c r="G588" s="2"/>
       <c r="H588" s="2"/>
     </row>
-    <row r="589" spans="7:8">
+    <row r="589" spans="7:8" ht="12.5">
       <c r="G589" s="2"/>
       <c r="H589" s="2"/>
     </row>
-    <row r="590" spans="7:8">
+    <row r="590" spans="7:8" ht="12.5">
       <c r="G590" s="2"/>
       <c r="H590" s="2"/>
     </row>
-    <row r="591" spans="7:8">
+    <row r="591" spans="7:8" ht="12.5">
       <c r="G591" s="2"/>
       <c r="H591" s="2"/>
     </row>
-    <row r="592" spans="7:8">
+    <row r="592" spans="7:8" ht="12.5">
       <c r="G592" s="2"/>
       <c r="H592" s="2"/>
     </row>
-    <row r="593" spans="7:8">
+    <row r="593" spans="7:8" ht="12.5">
       <c r="G593" s="2"/>
       <c r="H593" s="2"/>
     </row>
-    <row r="594" spans="7:8">
+    <row r="594" spans="7:8" ht="12.5">
       <c r="G594" s="2"/>
       <c r="H594" s="2"/>
     </row>
-    <row r="595" spans="7:8">
+    <row r="595" spans="7:8" ht="12.5">
       <c r="G595" s="2"/>
       <c r="H595" s="2"/>
     </row>
-    <row r="596" spans="7:8">
+    <row r="596" spans="7:8" ht="12.5">
       <c r="G596" s="2"/>
       <c r="H596" s="2"/>
     </row>
-    <row r="597" spans="7:8">
+    <row r="597" spans="7:8" ht="12.5">
       <c r="G597" s="2"/>
       <c r="H597" s="2"/>
     </row>
-    <row r="598" spans="7:8">
+    <row r="598" spans="7:8" ht="12.5">
       <c r="G598" s="2"/>
       <c r="H598" s="2"/>
     </row>
-    <row r="599" spans="7:8">
+    <row r="599" spans="7:8" ht="12.5">
       <c r="G599" s="2"/>
       <c r="H599" s="2"/>
     </row>
-    <row r="600" spans="7:8">
+    <row r="600" spans="7:8" ht="12.5">
       <c r="G600" s="2"/>
       <c r="H600" s="2"/>
     </row>
-    <row r="601" spans="7:8">
+    <row r="601" spans="7:8" ht="12.5">
       <c r="G601" s="2"/>
       <c r="H601" s="2"/>
     </row>
-    <row r="602" spans="7:8">
+    <row r="602" spans="7:8" ht="12.5">
       <c r="G602" s="2"/>
       <c r="H602" s="2"/>
     </row>
-    <row r="603" spans="7:8">
+    <row r="603" spans="7:8" ht="12.5">
       <c r="G603" s="2"/>
       <c r="H603" s="2"/>
     </row>
-    <row r="604" spans="7:8">
+    <row r="604" spans="7:8" ht="12.5">
       <c r="G604" s="2"/>
       <c r="H604" s="2"/>
     </row>
-    <row r="605" spans="7:8">
+    <row r="605" spans="7:8" ht="12.5">
       <c r="G605" s="2"/>
       <c r="H605" s="2"/>
     </row>
-    <row r="606" spans="7:8">
+    <row r="606" spans="7:8" ht="12.5">
       <c r="G606" s="2"/>
       <c r="H606" s="2"/>
     </row>
-    <row r="607" spans="7:8">
+    <row r="607" spans="7:8" ht="12.5">
       <c r="G607" s="2"/>
       <c r="H607" s="2"/>
     </row>
-    <row r="608" spans="7:8">
+    <row r="608" spans="7:8" ht="12.5">
       <c r="G608" s="2"/>
       <c r="H608" s="2"/>
     </row>
-    <row r="609" spans="7:8">
+    <row r="609" spans="7:8" ht="12.5">
       <c r="G609" s="2"/>
       <c r="H609" s="2"/>
     </row>
-    <row r="610" spans="7:8">
+    <row r="610" spans="7:8" ht="12.5">
       <c r="G610" s="2"/>
       <c r="H610" s="2"/>
     </row>
-    <row r="611" spans="7:8">
+    <row r="611" spans="7:8" ht="12.5">
       <c r="G611" s="2"/>
       <c r="H611" s="2"/>
     </row>
-    <row r="612" spans="7:8">
+    <row r="612" spans="7:8" ht="12.5">
       <c r="G612" s="2"/>
       <c r="H612" s="2"/>
     </row>
-    <row r="613" spans="7:8">
+    <row r="613" spans="7:8" ht="12.5">
       <c r="G613" s="2"/>
       <c r="H613" s="2"/>
     </row>
-    <row r="614" spans="7:8">
+    <row r="614" spans="7:8" ht="12.5">
       <c r="G614" s="2"/>
       <c r="H614" s="2"/>
     </row>
-    <row r="615" spans="7:8">
+    <row r="615" spans="7:8" ht="12.5">
       <c r="G615" s="2"/>
       <c r="H615" s="2"/>
     </row>
-    <row r="616" spans="7:8">
+    <row r="616" spans="7:8" ht="12.5">
       <c r="G616" s="2"/>
       <c r="H616" s="2"/>
     </row>
-    <row r="617" spans="7:8">
+    <row r="617" spans="7:8" ht="12.5">
       <c r="G617" s="2"/>
       <c r="H617" s="2"/>
     </row>
-    <row r="618" spans="7:8">
+    <row r="618" spans="7:8" ht="12.5">
       <c r="G618" s="2"/>
       <c r="H618" s="2"/>
     </row>
-    <row r="619" spans="7:8">
+    <row r="619" spans="7:8" ht="12.5">
       <c r="G619" s="2"/>
       <c r="H619" s="2"/>
     </row>
-    <row r="620" spans="7:8">
+    <row r="620" spans="7:8" ht="12.5">
       <c r="G620" s="2"/>
       <c r="H620" s="2"/>
     </row>
-    <row r="621" spans="7:8">
+    <row r="621" spans="7:8" ht="12.5">
       <c r="G621" s="2"/>
       <c r="H621" s="2"/>
     </row>
-    <row r="622" spans="7:8">
+    <row r="622" spans="7:8" ht="12.5">
       <c r="G622" s="2"/>
       <c r="H622" s="2"/>
     </row>
-    <row r="623" spans="7:8">
+    <row r="623" spans="7:8" ht="12.5">
       <c r="G623" s="2"/>
       <c r="H623" s="2"/>
     </row>
-    <row r="624" spans="7:8">
+    <row r="624" spans="7:8" ht="12.5">
       <c r="G624" s="2"/>
       <c r="H624" s="2"/>
     </row>
-    <row r="625" spans="7:8">
+    <row r="625" spans="7:8" ht="12.5">
       <c r="G625" s="2"/>
       <c r="H625" s="2"/>
     </row>
-    <row r="626" spans="7:8">
+    <row r="626" spans="7:8" ht="12.5">
       <c r="G626" s="2"/>
       <c r="H626" s="2"/>
     </row>
-    <row r="627" spans="7:8">
+    <row r="627" spans="7:8" ht="12.5">
       <c r="G627" s="2"/>
       <c r="H627" s="2"/>
     </row>
-    <row r="628" spans="7:8">
+    <row r="628" spans="7:8" ht="12.5">
       <c r="G628" s="2"/>
       <c r="H628" s="2"/>
     </row>
-    <row r="629" spans="7:8">
+    <row r="629" spans="7:8" ht="12.5">
       <c r="G629" s="2"/>
       <c r="H629" s="2"/>
     </row>
-    <row r="630" spans="7:8">
+    <row r="630" spans="7:8" ht="12.5">
       <c r="G630" s="2"/>
       <c r="H630" s="2"/>
     </row>
-    <row r="631" spans="7:8">
+    <row r="631" spans="7:8" ht="12.5">
       <c r="G631" s="2"/>
       <c r="H631" s="2"/>
     </row>
-    <row r="632" spans="7:8">
+    <row r="632" spans="7:8" ht="12.5">
       <c r="G632" s="2"/>
       <c r="H632" s="2"/>
     </row>
-    <row r="633" spans="7:8">
+    <row r="633" spans="7:8" ht="12.5">
       <c r="G633" s="2"/>
       <c r="H633" s="2"/>
     </row>
-    <row r="634" spans="7:8">
+    <row r="634" spans="7:8" ht="12.5">
       <c r="G634" s="2"/>
       <c r="H634" s="2"/>
     </row>
-    <row r="635" spans="7:8">
+    <row r="635" spans="7:8" ht="12.5">
       <c r="G635" s="2"/>
       <c r="H635" s="2"/>
     </row>
-    <row r="636" spans="7:8">
+    <row r="636" spans="7:8" ht="12.5">
       <c r="G636" s="2"/>
       <c r="H636" s="2"/>
     </row>
-    <row r="637" spans="7:8">
+    <row r="637" spans="7:8" ht="12.5">
       <c r="G637" s="2"/>
       <c r="H637" s="2"/>
     </row>
-    <row r="638" spans="7:8">
+    <row r="638" spans="7:8" ht="12.5">
       <c r="G638" s="2"/>
       <c r="H638" s="2"/>
     </row>
-    <row r="639" spans="7:8">
+    <row r="639" spans="7:8" ht="12.5">
       <c r="G639" s="2"/>
       <c r="H639" s="2"/>
     </row>
-    <row r="640" spans="7:8">
+    <row r="640" spans="7:8" ht="12.5">
       <c r="G640" s="2"/>
       <c r="H640" s="2"/>
     </row>
-    <row r="641" spans="7:8">
+    <row r="641" spans="7:8" ht="12.5">
       <c r="G641" s="2"/>
       <c r="H641" s="2"/>
     </row>
-    <row r="642" spans="7:8">
+    <row r="642" spans="7:8" ht="12.5">
       <c r="G642" s="2"/>
       <c r="H642" s="2"/>
     </row>
-    <row r="643" spans="7:8">
+    <row r="643" spans="7:8" ht="12.5">
       <c r="G643" s="2"/>
       <c r="H643" s="2"/>
     </row>
-    <row r="644" spans="7:8">
+    <row r="644" spans="7:8" ht="12.5">
       <c r="G644" s="2"/>
       <c r="H644" s="2"/>
     </row>
-    <row r="645" spans="7:8">
+    <row r="645" spans="7:8" ht="12.5">
       <c r="G645" s="2"/>
       <c r="H645" s="2"/>
     </row>
-    <row r="646" spans="7:8">
+    <row r="646" spans="7:8" ht="12.5">
       <c r="G646" s="2"/>
       <c r="H646" s="2"/>
     </row>
-    <row r="647" spans="7:8">
+    <row r="647" spans="7:8" ht="12.5">
       <c r="G647" s="2"/>
       <c r="H647" s="2"/>
     </row>
-    <row r="648" spans="7:8">
+    <row r="648" spans="7:8" ht="12.5">
       <c r="G648" s="2"/>
       <c r="H648" s="2"/>
     </row>
-    <row r="649" spans="7:8">
+    <row r="649" spans="7:8" ht="12.5">
       <c r="G649" s="2"/>
       <c r="H649" s="2"/>
     </row>
-    <row r="650" spans="7:8">
+    <row r="650" spans="7:8" ht="12.5">
       <c r="G650" s="2"/>
       <c r="H650" s="2"/>
     </row>
-    <row r="651" spans="7:8">
+    <row r="651" spans="7:8" ht="12.5">
       <c r="G651" s="2"/>
       <c r="H651" s="2"/>
     </row>
-    <row r="652" spans="7:8">
+    <row r="652" spans="7:8" ht="12.5">
       <c r="G652" s="2"/>
       <c r="H652" s="2"/>
     </row>
-    <row r="653" spans="7:8">
+    <row r="653" spans="7:8" ht="12.5">
       <c r="G653" s="2"/>
       <c r="H653" s="2"/>
     </row>
-    <row r="654" spans="7:8">
+    <row r="654" spans="7:8" ht="12.5">
       <c r="G654" s="2"/>
       <c r="H654" s="2"/>
     </row>
-    <row r="655" spans="7:8">
+    <row r="655" spans="7:8" ht="12.5">
       <c r="G655" s="2"/>
       <c r="H655" s="2"/>
     </row>
-    <row r="656" spans="7:8">
+    <row r="656" spans="7:8" ht="12.5">
       <c r="G656" s="2"/>
       <c r="H656" s="2"/>
     </row>
-    <row r="657" spans="7:8">
+    <row r="657" spans="7:8" ht="12.5">
       <c r="G657" s="2"/>
       <c r="H657" s="2"/>
     </row>
-    <row r="658" spans="7:8">
+    <row r="658" spans="7:8" ht="12.5">
       <c r="G658" s="2"/>
       <c r="H658" s="2"/>
     </row>
-    <row r="659" spans="7:8">
+    <row r="659" spans="7:8" ht="12.5">
       <c r="G659" s="2"/>
       <c r="H659" s="2"/>
     </row>
-    <row r="660" spans="7:8">
+    <row r="660" spans="7:8" ht="12.5">
       <c r="G660" s="2"/>
       <c r="H660" s="2"/>
     </row>
-    <row r="661" spans="7:8">
+    <row r="661" spans="7:8" ht="12.5">
       <c r="G661" s="2"/>
       <c r="H661" s="2"/>
     </row>
-    <row r="662" spans="7:8">
+    <row r="662" spans="7:8" ht="12.5">
       <c r="G662" s="2"/>
       <c r="H662" s="2"/>
     </row>
-    <row r="663" spans="7:8">
+    <row r="663" spans="7:8" ht="12.5">
       <c r="G663" s="2"/>
       <c r="H663" s="2"/>
     </row>
-    <row r="664" spans="7:8">
+    <row r="664" spans="7:8" ht="12.5">
       <c r="G664" s="2"/>
       <c r="H664" s="2"/>
     </row>
-    <row r="665" spans="7:8">
+    <row r="665" spans="7:8" ht="12.5">
       <c r="G665" s="2"/>
       <c r="H665" s="2"/>
     </row>
-    <row r="666" spans="7:8">
+    <row r="666" spans="7:8" ht="12.5">
       <c r="G666" s="2"/>
       <c r="H666" s="2"/>
     </row>
-    <row r="667" spans="7:8">
+    <row r="667" spans="7:8" ht="12.5">
       <c r="G667" s="2"/>
       <c r="H667" s="2"/>
     </row>
-    <row r="668" spans="7:8">
+    <row r="668" spans="7:8" ht="12.5">
       <c r="G668" s="2"/>
       <c r="H668" s="2"/>
     </row>
-    <row r="669" spans="7:8">
+    <row r="669" spans="7:8" ht="12.5">
       <c r="G669" s="2"/>
       <c r="H669" s="2"/>
     </row>
-    <row r="670" spans="7:8">
+    <row r="670" spans="7:8" ht="12.5">
       <c r="G670" s="2"/>
       <c r="H670" s="2"/>
     </row>
-    <row r="671" spans="7:8">
+    <row r="671" spans="7:8" ht="12.5">
       <c r="G671" s="2"/>
       <c r="H671" s="2"/>
     </row>
-    <row r="672" spans="7:8">
+    <row r="672" spans="7:8" ht="12.5">
       <c r="G672" s="2"/>
       <c r="H672" s="2"/>
     </row>
-    <row r="673" spans="7:8">
+    <row r="673" spans="7:8" ht="12.5">
       <c r="G673" s="2"/>
       <c r="H673" s="2"/>
     </row>
-    <row r="674" spans="7:8">
+    <row r="674" spans="7:8" ht="12.5">
       <c r="G674" s="2"/>
       <c r="H674" s="2"/>
     </row>
-    <row r="675" spans="7:8">
+    <row r="675" spans="7:8" ht="12.5">
       <c r="G675" s="2"/>
       <c r="H675" s="2"/>
     </row>
-    <row r="676" spans="7:8">
+    <row r="676" spans="7:8" ht="12.5">
       <c r="G676" s="2"/>
       <c r="H676" s="2"/>
     </row>
-    <row r="677" spans="7:8">
+    <row r="677" spans="7:8" ht="12.5">
       <c r="G677" s="2"/>
       <c r="H677" s="2"/>
     </row>
-    <row r="678" spans="7:8">
+    <row r="678" spans="7:8" ht="12.5">
       <c r="G678" s="2"/>
       <c r="H678" s="2"/>
     </row>
-    <row r="679" spans="7:8">
+    <row r="679" spans="7:8" ht="12.5">
       <c r="G679" s="2"/>
       <c r="H679" s="2"/>
     </row>
-    <row r="680" spans="7:8">
+    <row r="680" spans="7:8" ht="12.5">
       <c r="G680" s="2"/>
       <c r="H680" s="2"/>
     </row>
-    <row r="681" spans="7:8">
+    <row r="681" spans="7:8" ht="12.5">
       <c r="G681" s="2"/>
       <c r="H681" s="2"/>
     </row>
-    <row r="682" spans="7:8">
+    <row r="682" spans="7:8" ht="12.5">
       <c r="G682" s="2"/>
       <c r="H682" s="2"/>
     </row>
-    <row r="683" spans="7:8">
+    <row r="683" spans="7:8" ht="12.5">
       <c r="G683" s="2"/>
       <c r="H683" s="2"/>
     </row>
-    <row r="684" spans="7:8">
+    <row r="684" spans="7:8" ht="12.5">
       <c r="G684" s="2"/>
       <c r="H684" s="2"/>
     </row>
-    <row r="685" spans="7:8">
+    <row r="685" spans="7:8" ht="12.5">
       <c r="G685" s="2"/>
       <c r="H685" s="2"/>
     </row>
-    <row r="686" spans="7:8">
+    <row r="686" spans="7:8" ht="12.5">
       <c r="G686" s="2"/>
       <c r="H686" s="2"/>
     </row>
-    <row r="687" spans="7:8">
+    <row r="687" spans="7:8" ht="12.5">
       <c r="G687" s="2"/>
       <c r="H687" s="2"/>
     </row>
-    <row r="688" spans="7:8">
+    <row r="688" spans="7:8" ht="12.5">
       <c r="G688" s="2"/>
       <c r="H688" s="2"/>
     </row>
-    <row r="689" spans="7:8">
+    <row r="689" spans="7:8" ht="12.5">
       <c r="G689" s="2"/>
       <c r="H689" s="2"/>
     </row>
-    <row r="690" spans="7:8">
+    <row r="690" spans="7:8" ht="12.5">
       <c r="G690" s="2"/>
       <c r="H690" s="2"/>
     </row>
-    <row r="691" spans="7:8">
+    <row r="691" spans="7:8" ht="12.5">
       <c r="G691" s="2"/>
       <c r="H691" s="2"/>
     </row>
-    <row r="692" spans="7:8">
+    <row r="692" spans="7:8" ht="12.5">
       <c r="G692" s="2"/>
       <c r="H692" s="2"/>
     </row>
-    <row r="693" spans="7:8">
+    <row r="693" spans="7:8" ht="12.5">
       <c r="G693" s="2"/>
       <c r="H693" s="2"/>
     </row>
-    <row r="694" spans="7:8">
+    <row r="694" spans="7:8" ht="12.5">
       <c r="G694" s="2"/>
       <c r="H694" s="2"/>
     </row>
-    <row r="695" spans="7:8">
+    <row r="695" spans="7:8" ht="12.5">
       <c r="G695" s="2"/>
       <c r="H695" s="2"/>
     </row>
-    <row r="696" spans="7:8">
+    <row r="696" spans="7:8" ht="12.5">
       <c r="G696" s="2"/>
       <c r="H696" s="2"/>
     </row>
-    <row r="697" spans="7:8">
+    <row r="697" spans="7:8" ht="12.5">
       <c r="G697" s="2"/>
       <c r="H697" s="2"/>
     </row>
-    <row r="698" spans="7:8">
+    <row r="698" spans="7:8" ht="12.5">
       <c r="G698" s="2"/>
       <c r="H698" s="2"/>
     </row>
-    <row r="699" spans="7:8">
+    <row r="699" spans="7:8" ht="12.5">
       <c r="G699" s="2"/>
       <c r="H699" s="2"/>
     </row>
-    <row r="700" spans="7:8">
+    <row r="700" spans="7:8" ht="12.5">
       <c r="G700" s="2"/>
       <c r="H700" s="2"/>
     </row>
-    <row r="701" spans="7:8">
+    <row r="701" spans="7:8" ht="12.5">
       <c r="G701" s="2"/>
       <c r="H701" s="2"/>
     </row>
-    <row r="702" spans="7:8">
+    <row r="702" spans="7:8" ht="12.5">
       <c r="G702" s="2"/>
       <c r="H702" s="2"/>
     </row>
-    <row r="703" spans="7:8">
+    <row r="703" spans="7:8" ht="12.5">
       <c r="G703" s="2"/>
       <c r="H703" s="2"/>
     </row>
-    <row r="704" spans="7:8">
+    <row r="704" spans="7:8" ht="12.5">
       <c r="G704" s="2"/>
       <c r="H704" s="2"/>
     </row>
-    <row r="705" spans="7:8">
+    <row r="705" spans="7:8" ht="12.5">
       <c r="G705" s="2"/>
       <c r="H705" s="2"/>
     </row>
-    <row r="706" spans="7:8">
+    <row r="706" spans="7:8" ht="12.5">
       <c r="G706" s="2"/>
       <c r="H706" s="2"/>
     </row>
-    <row r="707" spans="7:8">
+    <row r="707" spans="7:8" ht="12.5">
       <c r="G707" s="2"/>
       <c r="H707" s="2"/>
     </row>
-    <row r="708" spans="7:8">
+    <row r="708" spans="7:8" ht="12.5">
       <c r="G708" s="2"/>
       <c r="H708" s="2"/>
     </row>
-    <row r="709" spans="7:8">
+    <row r="709" spans="7:8" ht="12.5">
       <c r="G709" s="2"/>
       <c r="H709" s="2"/>
     </row>
-    <row r="710" spans="7:8">
+    <row r="710" spans="7:8" ht="12.5">
       <c r="G710" s="2"/>
       <c r="H710" s="2"/>
     </row>
-    <row r="711" spans="7:8">
+    <row r="711" spans="7:8" ht="12.5">
       <c r="G711" s="2"/>
       <c r="H711" s="2"/>
     </row>
-    <row r="712" spans="7:8">
+    <row r="712" spans="7:8" ht="12.5">
       <c r="G712" s="2"/>
       <c r="H712" s="2"/>
     </row>
-    <row r="713" spans="7:8">
+    <row r="713" spans="7:8" ht="12.5">
       <c r="G713" s="2"/>
       <c r="H713" s="2"/>
     </row>
-    <row r="714" spans="7:8">
+    <row r="714" spans="7:8" ht="12.5">
       <c r="G714" s="2"/>
       <c r="H714" s="2"/>
     </row>
-    <row r="715" spans="7:8">
+    <row r="715" spans="7:8" ht="12.5">
       <c r="G715" s="2"/>
       <c r="H715" s="2"/>
     </row>
-    <row r="716" spans="7:8">
+    <row r="716" spans="7:8" ht="12.5">
       <c r="G716" s="2"/>
       <c r="H716" s="2"/>
     </row>
-    <row r="717" spans="7:8">
+    <row r="717" spans="7:8" ht="12.5">
       <c r="G717" s="2"/>
       <c r="H717" s="2"/>
     </row>
-    <row r="718" spans="7:8">
+    <row r="718" spans="7:8" ht="12.5">
       <c r="G718" s="2"/>
       <c r="H718" s="2"/>
     </row>
-    <row r="719" spans="7:8">
+    <row r="719" spans="7:8" ht="12.5">
       <c r="G719" s="2"/>
       <c r="H719" s="2"/>
     </row>
-    <row r="720" spans="7:8">
+    <row r="720" spans="7:8" ht="12.5">
       <c r="G720" s="2"/>
       <c r="H720" s="2"/>
     </row>
-    <row r="721" spans="7:8">
+    <row r="721" spans="7:8" ht="12.5">
       <c r="G721" s="2"/>
       <c r="H721" s="2"/>
     </row>
-    <row r="722" spans="7:8">
+    <row r="722" spans="7:8" ht="12.5">
       <c r="G722" s="2"/>
       <c r="H722" s="2"/>
     </row>
-    <row r="723" spans="7:8">
+    <row r="723" spans="7:8" ht="12.5">
       <c r="G723" s="2"/>
       <c r="H723" s="2"/>
     </row>
-    <row r="724" spans="7:8">
+    <row r="724" spans="7:8" ht="12.5">
       <c r="G724" s="2"/>
       <c r="H724" s="2"/>
     </row>
-    <row r="725" spans="7:8">
+    <row r="725" spans="7:8" ht="12.5">
       <c r="G725" s="2"/>
       <c r="H725" s="2"/>
     </row>
-    <row r="726" spans="7:8">
+    <row r="726" spans="7:8" ht="12.5">
       <c r="G726" s="2"/>
       <c r="H726" s="2"/>
     </row>
-    <row r="727" spans="7:8">
+    <row r="727" spans="7:8" ht="12.5">
       <c r="G727" s="2"/>
       <c r="H727" s="2"/>
     </row>
-    <row r="728" spans="7:8">
+    <row r="728" spans="7:8" ht="12.5">
       <c r="G728" s="2"/>
       <c r="H728" s="2"/>
     </row>
-    <row r="729" spans="7:8">
+    <row r="729" spans="7:8" ht="12.5">
       <c r="G729" s="2"/>
       <c r="H729" s="2"/>
     </row>
-    <row r="730" spans="7:8">
+    <row r="730" spans="7:8" ht="12.5">
       <c r="G730" s="2"/>
       <c r="H730" s="2"/>
     </row>
-    <row r="731" spans="7:8">
+    <row r="731" spans="7:8" ht="12.5">
       <c r="G731" s="2"/>
       <c r="H731" s="2"/>
     </row>
-    <row r="732" spans="7:8">
+    <row r="732" spans="7:8" ht="12.5">
       <c r="G732" s="2"/>
       <c r="H732" s="2"/>
     </row>
-    <row r="733" spans="7:8">
+    <row r="733" spans="7:8" ht="12.5">
       <c r="G733" s="2"/>
       <c r="H733" s="2"/>
     </row>
-    <row r="734" spans="7:8">
+    <row r="734" spans="7:8" ht="12.5">
       <c r="G734" s="2"/>
       <c r="H734" s="2"/>
     </row>
-    <row r="735" spans="7:8">
+    <row r="735" spans="7:8" ht="12.5">
       <c r="G735" s="2"/>
       <c r="H735" s="2"/>
     </row>
-    <row r="736" spans="7:8">
+    <row r="736" spans="7:8" ht="12.5">
       <c r="G736" s="2"/>
       <c r="H736" s="2"/>
     </row>
-    <row r="737" spans="7:8">
+    <row r="737" spans="7:8" ht="12.5">
       <c r="G737" s="2"/>
       <c r="H737" s="2"/>
     </row>
-    <row r="738" spans="7:8">
+    <row r="738" spans="7:8" ht="12.5">
       <c r="G738" s="2"/>
       <c r="H738" s="2"/>
     </row>
-    <row r="739" spans="7:8">
+    <row r="739" spans="7:8" ht="12.5">
       <c r="G739" s="2"/>
       <c r="H739" s="2"/>
     </row>
-    <row r="740" spans="7:8">
+    <row r="740" spans="7:8" ht="12.5">
       <c r="G740" s="2"/>
       <c r="H740" s="2"/>
     </row>
-    <row r="741" spans="7:8">
+    <row r="741" spans="7:8" ht="12.5">
       <c r="G741" s="2"/>
       <c r="H741" s="2"/>
     </row>
-    <row r="742" spans="7:8">
+    <row r="742" spans="7:8" ht="12.5">
       <c r="G742" s="2"/>
       <c r="H742" s="2"/>
     </row>
-    <row r="743" spans="7:8">
+    <row r="743" spans="7:8" ht="12.5">
       <c r="G743" s="2"/>
       <c r="H743" s="2"/>
     </row>
-    <row r="744" spans="7:8">
+    <row r="744" spans="7:8" ht="12.5">
       <c r="G744" s="2"/>
       <c r="H744" s="2"/>
     </row>
-    <row r="745" spans="7:8">
+    <row r="745" spans="7:8" ht="12.5">
       <c r="G745" s="2"/>
       <c r="H745" s="2"/>
     </row>
-    <row r="746" spans="7:8">
+    <row r="746" spans="7:8" ht="12.5">
       <c r="G746" s="2"/>
       <c r="H746" s="2"/>
     </row>
-    <row r="747" spans="7:8">
+    <row r="747" spans="7:8" ht="12.5">
       <c r="G747" s="2"/>
       <c r="H747" s="2"/>
     </row>
-    <row r="748" spans="7:8">
+    <row r="748" spans="7:8" ht="12.5">
       <c r="G748" s="2"/>
       <c r="H748" s="2"/>
     </row>
-    <row r="749" spans="7:8">
+    <row r="749" spans="7:8" ht="12.5">
       <c r="G749" s="2"/>
       <c r="H749" s="2"/>
     </row>
-    <row r="750" spans="7:8">
+    <row r="750" spans="7:8" ht="12.5">
       <c r="G750" s="2"/>
       <c r="H750" s="2"/>
     </row>
-    <row r="751" spans="7:8">
+    <row r="751" spans="7:8" ht="12.5">
       <c r="G751" s="2"/>
       <c r="H751" s="2"/>
     </row>
-    <row r="752" spans="7:8">
+    <row r="752" spans="7:8" ht="12.5">
       <c r="G752" s="2"/>
       <c r="H752" s="2"/>
     </row>
-    <row r="753" spans="7:8">
+    <row r="753" spans="7:8" ht="12.5">
       <c r="G753" s="2"/>
       <c r="H753" s="2"/>
     </row>
-    <row r="754" spans="7:8">
+    <row r="754" spans="7:8" ht="12.5">
       <c r="G754" s="2"/>
       <c r="H754" s="2"/>
     </row>
-    <row r="755" spans="7:8">
+    <row r="755" spans="7:8" ht="12.5">
       <c r="G755" s="2"/>
       <c r="H755" s="2"/>
     </row>
-    <row r="756" spans="7:8">
+    <row r="756" spans="7:8" ht="12.5">
       <c r="G756" s="2"/>
       <c r="H756" s="2"/>
     </row>
-    <row r="757" spans="7:8">
+    <row r="757" spans="7:8" ht="12.5">
       <c r="G757" s="2"/>
       <c r="H757" s="2"/>
     </row>
-    <row r="758" spans="7:8">
+    <row r="758" spans="7:8" ht="12.5">
       <c r="G758" s="2"/>
       <c r="H758" s="2"/>
     </row>
-    <row r="759" spans="7:8">
+    <row r="759" spans="7:8" ht="12.5">
       <c r="G759" s="2"/>
       <c r="H759" s="2"/>
     </row>
-    <row r="760" spans="7:8">
+    <row r="760" spans="7:8" ht="12.5">
       <c r="G760" s="2"/>
       <c r="H760" s="2"/>
     </row>
-    <row r="761" spans="7:8">
+    <row r="761" spans="7:8" ht="12.5">
       <c r="G761" s="2"/>
       <c r="H761" s="2"/>
     </row>
-    <row r="762" spans="7:8">
+    <row r="762" spans="7:8" ht="12.5">
       <c r="G762" s="2"/>
       <c r="H762" s="2"/>
     </row>
-    <row r="763" spans="7:8">
+    <row r="763" spans="7:8" ht="12.5">
       <c r="G763" s="2"/>
       <c r="H763" s="2"/>
     </row>
-    <row r="764" spans="7:8">
+    <row r="764" spans="7:8" ht="12.5">
       <c r="G764" s="2"/>
       <c r="H764" s="2"/>
     </row>
-    <row r="765" spans="7:8">
+    <row r="765" spans="7:8" ht="12.5">
       <c r="G765" s="2"/>
       <c r="H765" s="2"/>
     </row>
-    <row r="766" spans="7:8">
+    <row r="766" spans="7:8" ht="12.5">
       <c r="G766" s="2"/>
       <c r="H766" s="2"/>
     </row>
-    <row r="767" spans="7:8">
+    <row r="767" spans="7:8" ht="12.5">
       <c r="G767" s="2"/>
       <c r="H767" s="2"/>
     </row>
-    <row r="768" spans="7:8">
+    <row r="768" spans="7:8" ht="12.5">
       <c r="G768" s="2"/>
       <c r="H768" s="2"/>
     </row>
-    <row r="769" spans="7:8">
+    <row r="769" spans="7:8" ht="12.5">
       <c r="G769" s="2"/>
       <c r="H769" s="2"/>
     </row>
-    <row r="770" spans="7:8">
+    <row r="770" spans="7:8" ht="12.5">
       <c r="G770" s="2"/>
       <c r="H770" s="2"/>
     </row>
-    <row r="771" spans="7:8">
+    <row r="771" spans="7:8" ht="12.5">
       <c r="G771" s="2"/>
       <c r="H771" s="2"/>
     </row>
-    <row r="772" spans="7:8">
+    <row r="772" spans="7:8" ht="12.5">
       <c r="G772" s="2"/>
       <c r="H772" s="2"/>
     </row>
-    <row r="773" spans="7:8">
+    <row r="773" spans="7:8" ht="12.5">
       <c r="G773" s="2"/>
       <c r="H773" s="2"/>
     </row>
-    <row r="774" spans="7:8">
+    <row r="774" spans="7:8" ht="12.5">
       <c r="G774" s="2"/>
       <c r="H774" s="2"/>
     </row>
-    <row r="775" spans="7:8">
+    <row r="775" spans="7:8" ht="12.5">
       <c r="G775" s="2"/>
       <c r="H775" s="2"/>
     </row>
-    <row r="776" spans="7:8">
+    <row r="776" spans="7:8" ht="12.5">
       <c r="G776" s="2"/>
       <c r="H776" s="2"/>
     </row>
-    <row r="777" spans="7:8">
+    <row r="777" spans="7:8" ht="12.5">
       <c r="G777" s="2"/>
       <c r="H777" s="2"/>
     </row>
-    <row r="778" spans="7:8">
+    <row r="778" spans="7:8" ht="12.5">
       <c r="G778" s="2"/>
       <c r="H778" s="2"/>
     </row>
-    <row r="779" spans="7:8">
+    <row r="779" spans="7:8" ht="12.5">
       <c r="G779" s="2"/>
       <c r="H779" s="2"/>
     </row>
-    <row r="780" spans="7:8">
+    <row r="780" spans="7:8" ht="12.5">
       <c r="G780" s="2"/>
       <c r="H780" s="2"/>
     </row>
-    <row r="781" spans="7:8">
+    <row r="781" spans="7:8" ht="12.5">
       <c r="G781" s="2"/>
       <c r="H781" s="2"/>
     </row>
-    <row r="782" spans="7:8">
+    <row r="782" spans="7:8" ht="12.5">
       <c r="G782" s="2"/>
       <c r="H782" s="2"/>
     </row>
-    <row r="783" spans="7:8">
+    <row r="783" spans="7:8" ht="12.5">
       <c r="G783" s="2"/>
       <c r="H783" s="2"/>
     </row>
-    <row r="784" spans="7:8">
+    <row r="784" spans="7:8" ht="12.5">
       <c r="G784" s="2"/>
       <c r="H784" s="2"/>
     </row>
-    <row r="785" spans="7:8">
+    <row r="785" spans="7:8" ht="12.5">
       <c r="G785" s="2"/>
       <c r="H785" s="2"/>
     </row>
-    <row r="786" spans="7:8">
+    <row r="786" spans="7:8" ht="12.5">
       <c r="G786" s="2"/>
       <c r="H786" s="2"/>
     </row>
-    <row r="787" spans="7:8">
+    <row r="787" spans="7:8" ht="12.5">
       <c r="G787" s="2"/>
       <c r="H787" s="2"/>
     </row>
-    <row r="788" spans="7:8">
+    <row r="788" spans="7:8" ht="12.5">
       <c r="G788" s="2"/>
       <c r="H788" s="2"/>
     </row>
-    <row r="789" spans="7:8">
+    <row r="789" spans="7:8" ht="12.5">
       <c r="G789" s="2"/>
       <c r="H789" s="2"/>
     </row>
-    <row r="790" spans="7:8">
+    <row r="790" spans="7:8" ht="12.5">
       <c r="G790" s="2"/>
       <c r="H790" s="2"/>
     </row>
-    <row r="791" spans="7:8">
+    <row r="791" spans="7:8" ht="12.5">
       <c r="G791" s="2"/>
       <c r="H791" s="2"/>
     </row>
-    <row r="792" spans="7:8">
+    <row r="792" spans="7:8" ht="12.5">
       <c r="G792" s="2"/>
       <c r="H792" s="2"/>
     </row>
-    <row r="793" spans="7:8">
+    <row r="793" spans="7:8" ht="12.5">
       <c r="G793" s="2"/>
       <c r="H793" s="2"/>
     </row>
-    <row r="794" spans="7:8">
+    <row r="794" spans="7:8" ht="12.5">
       <c r="G794" s="2"/>
       <c r="H794" s="2"/>
     </row>
-    <row r="795" spans="7:8">
+    <row r="795" spans="7:8" ht="12.5">
       <c r="G795" s="2"/>
       <c r="H795" s="2"/>
     </row>
-    <row r="796" spans="7:8">
+    <row r="796" spans="7:8" ht="12.5">
       <c r="G796" s="2"/>
       <c r="H796" s="2"/>
     </row>
-    <row r="797" spans="7:8">
+    <row r="797" spans="7:8" ht="12.5">
       <c r="G797" s="2"/>
       <c r="H797" s="2"/>
     </row>
-    <row r="798" spans="7:8">
+    <row r="798" spans="7:8" ht="12.5">
       <c r="G798" s="2"/>
       <c r="H798" s="2"/>
     </row>
-    <row r="799" spans="7:8">
+    <row r="799" spans="7:8" ht="12.5">
       <c r="G799" s="2"/>
       <c r="H799" s="2"/>
     </row>
-    <row r="800" spans="7:8">
+    <row r="800" spans="7:8" ht="12.5">
       <c r="G800" s="2"/>
       <c r="H800" s="2"/>
     </row>
-    <row r="801" spans="7:8">
+    <row r="801" spans="7:8" ht="12.5">
       <c r="G801" s="2"/>
       <c r="H801" s="2"/>
     </row>
-    <row r="802" spans="7:8">
+    <row r="802" spans="7:8" ht="12.5">
       <c r="G802" s="2"/>
       <c r="H802" s="2"/>
     </row>
-    <row r="803" spans="7:8">
+    <row r="803" spans="7:8" ht="12.5">
       <c r="G803" s="2"/>
       <c r="H803" s="2"/>
     </row>
-    <row r="804" spans="7:8">
+    <row r="804" spans="7:8" ht="12.5">
       <c r="G804" s="2"/>
       <c r="H804" s="2"/>
     </row>
-    <row r="805" spans="7:8">
+    <row r="805" spans="7:8" ht="12.5">
       <c r="G805" s="2"/>
       <c r="H805" s="2"/>
     </row>
-    <row r="806" spans="7:8">
+    <row r="806" spans="7:8" ht="12.5">
       <c r="G806" s="2"/>
       <c r="H806" s="2"/>
     </row>
-    <row r="807" spans="7:8">
+    <row r="807" spans="7:8" ht="12.5">
       <c r="G807" s="2"/>
       <c r="H807" s="2"/>
     </row>
-    <row r="808" spans="7:8">
+    <row r="808" spans="7:8" ht="12.5">
       <c r="G808" s="2"/>
       <c r="H808" s="2"/>
     </row>
-    <row r="809" spans="7:8">
+    <row r="809" spans="7:8" ht="12.5">
       <c r="G809" s="2"/>
       <c r="H809" s="2"/>
     </row>
-    <row r="810" spans="7:8">
+    <row r="810" spans="7:8" ht="12.5">
       <c r="G810" s="2"/>
       <c r="H810" s="2"/>
     </row>
-    <row r="811" spans="7:8">
+    <row r="811" spans="7:8" ht="12.5">
       <c r="G811" s="2"/>
       <c r="H811" s="2"/>
     </row>
-    <row r="812" spans="7:8">
+    <row r="812" spans="7:8" ht="12.5">
       <c r="G812" s="2"/>
       <c r="H812" s="2"/>
     </row>
-    <row r="813" spans="7:8">
+    <row r="813" spans="7:8" ht="12.5">
       <c r="G813" s="2"/>
       <c r="H813" s="2"/>
     </row>
-    <row r="814" spans="7:8">
+    <row r="814" spans="7:8" ht="12.5">
       <c r="G814" s="2"/>
       <c r="H814" s="2"/>
     </row>
-    <row r="815" spans="7:8">
+    <row r="815" spans="7:8" ht="12.5">
       <c r="G815" s="2"/>
       <c r="H815" s="2"/>
     </row>
-    <row r="816" spans="7:8">
+    <row r="816" spans="7:8" ht="12.5">
       <c r="G816" s="2"/>
       <c r="H816" s="2"/>
     </row>
-    <row r="817" spans="7:8">
+    <row r="817" spans="7:8" ht="12.5">
       <c r="G817" s="2"/>
       <c r="H817" s="2"/>
     </row>
-    <row r="818" spans="7:8">
+    <row r="818" spans="7:8" ht="12.5">
       <c r="G818" s="2"/>
       <c r="H818" s="2"/>
     </row>
-    <row r="819" spans="7:8">
+    <row r="819" spans="7:8" ht="12.5">
       <c r="G819" s="2"/>
       <c r="H819" s="2"/>
     </row>
-    <row r="820" spans="7:8">
+    <row r="820" spans="7:8" ht="12.5">
       <c r="G820" s="2"/>
       <c r="H820" s="2"/>
     </row>
-    <row r="821" spans="7:8">
+    <row r="821" spans="7:8" ht="12.5">
       <c r="G821" s="2"/>
       <c r="H821" s="2"/>
     </row>
-    <row r="822" spans="7:8">
+    <row r="822" spans="7:8" ht="12.5">
       <c r="G822" s="2"/>
       <c r="H822" s="2"/>
     </row>
-    <row r="823" spans="7:8">
+    <row r="823" spans="7:8" ht="12.5">
       <c r="G823" s="2"/>
       <c r="H823" s="2"/>
     </row>
-    <row r="824" spans="7:8">
+    <row r="824" spans="7:8" ht="12.5">
       <c r="G824" s="2"/>
       <c r="H824" s="2"/>
     </row>
-    <row r="825" spans="7:8">
+    <row r="825" spans="7:8" ht="12.5">
       <c r="G825" s="2"/>
       <c r="H825" s="2"/>
     </row>
-    <row r="826" spans="7:8">
+    <row r="826" spans="7:8" ht="12.5">
       <c r="G826" s="2"/>
       <c r="H826" s="2"/>
     </row>
-    <row r="827" spans="7:8">
+    <row r="827" spans="7:8" ht="12.5">
       <c r="G827" s="2"/>
       <c r="H827" s="2"/>
     </row>
-    <row r="828" spans="7:8">
+    <row r="828" spans="7:8" ht="12.5">
       <c r="G828" s="2"/>
       <c r="H828" s="2"/>
     </row>
-    <row r="829" spans="7:8">
+    <row r="829" spans="7:8" ht="12.5">
       <c r="G829" s="2"/>
       <c r="H829" s="2"/>
     </row>
-    <row r="830" spans="7:8">
+    <row r="830" spans="7:8" ht="12.5">
       <c r="G830" s="2"/>
       <c r="H830" s="2"/>
     </row>
-    <row r="831" spans="7:8">
+    <row r="831" spans="7:8" ht="12.5">
       <c r="G831" s="2"/>
       <c r="H831" s="2"/>
     </row>
-    <row r="832" spans="7:8">
+    <row r="832" spans="7:8" ht="12.5">
       <c r="G832" s="2"/>
       <c r="H832" s="2"/>
     </row>
-    <row r="833" spans="7:8">
+    <row r="833" spans="7:8" ht="12.5">
       <c r="G833" s="2"/>
       <c r="H833" s="2"/>
     </row>
-    <row r="834" spans="7:8">
+    <row r="834" spans="7:8" ht="12.5">
       <c r="G834" s="2"/>
       <c r="H834" s="2"/>
     </row>
-    <row r="835" spans="7:8">
+    <row r="835" spans="7:8" ht="12.5">
       <c r="G835" s="2"/>
       <c r="H835" s="2"/>
     </row>
-    <row r="836" spans="7:8">
+    <row r="836" spans="7:8" ht="12.5">
       <c r="G836" s="2"/>
       <c r="H836" s="2"/>
     </row>
-    <row r="837" spans="7:8">
+    <row r="837" spans="7:8" ht="12.5">
       <c r="G837" s="2"/>
       <c r="H837" s="2"/>
     </row>
-    <row r="838" spans="7:8">
+    <row r="838" spans="7:8" ht="12.5">
       <c r="G838" s="2"/>
       <c r="H838" s="2"/>
     </row>
-    <row r="839" spans="7:8">
+    <row r="839" spans="7:8" ht="12.5">
       <c r="G839" s="2"/>
       <c r="H839" s="2"/>
     </row>
-    <row r="840" spans="7:8">
+    <row r="840" spans="7:8" ht="12.5">
       <c r="G840" s="2"/>
       <c r="H840" s="2"/>
     </row>
-    <row r="841" spans="7:8">
+    <row r="841" spans="7:8" ht="12.5">
       <c r="G841" s="2"/>
       <c r="H841" s="2"/>
     </row>
-    <row r="842" spans="7:8">
+    <row r="842" spans="7:8" ht="12.5">
       <c r="G842" s="2"/>
       <c r="H842" s="2"/>
     </row>
-    <row r="843" spans="7:8">
+    <row r="843" spans="7:8" ht="12.5">
       <c r="G843" s="2"/>
       <c r="H843" s="2"/>
     </row>
-    <row r="844" spans="7:8">
+    <row r="844" spans="7:8" ht="12.5">
       <c r="G844" s="2"/>
       <c r="H844" s="2"/>
     </row>
-    <row r="845" spans="7:8">
+    <row r="845" spans="7:8" ht="12.5">
       <c r="G845" s="2"/>
       <c r="H845" s="2"/>
     </row>
-    <row r="846" spans="7:8">
+    <row r="846" spans="7:8" ht="12.5">
       <c r="G846" s="2"/>
       <c r="H846" s="2"/>
     </row>
-    <row r="847" spans="7:8">
+    <row r="847" spans="7:8" ht="12.5">
       <c r="G847" s="2"/>
       <c r="H847" s="2"/>
     </row>
-    <row r="848" spans="7:8">
+    <row r="848" spans="7:8" ht="12.5">
       <c r="G848" s="2"/>
       <c r="H848" s="2"/>
     </row>
-    <row r="849" spans="7:8">
+    <row r="849" spans="7:8" ht="12.5">
       <c r="G849" s="2"/>
       <c r="H849" s="2"/>
     </row>
-    <row r="850" spans="7:8">
+    <row r="850" spans="7:8" ht="12.5">
       <c r="G850" s="2"/>
       <c r="H850" s="2"/>
     </row>
-    <row r="851" spans="7:8">
+    <row r="851" spans="7:8" ht="12.5">
       <c r="G851" s="2"/>
       <c r="H851" s="2"/>
     </row>
-    <row r="852" spans="7:8">
+    <row r="852" spans="7:8" ht="12.5">
       <c r="G852" s="2"/>
       <c r="H852" s="2"/>
     </row>
-    <row r="853" spans="7:8">
+    <row r="853" spans="7:8" ht="12.5">
       <c r="G853" s="2"/>
       <c r="H853" s="2"/>
     </row>
-    <row r="854" spans="7:8">
+    <row r="854" spans="7:8" ht="12.5">
       <c r="G854" s="2"/>
       <c r="H854" s="2"/>
     </row>
-    <row r="855" spans="7:8">
+    <row r="855" spans="7:8" ht="12.5">
       <c r="G855" s="2"/>
       <c r="H855" s="2"/>
     </row>
-    <row r="856" spans="7:8">
+    <row r="856" spans="7:8" ht="12.5">
       <c r="G856" s="2"/>
       <c r="H856" s="2"/>
     </row>
-    <row r="857" spans="7:8">
+    <row r="857" spans="7:8" ht="12.5">
       <c r="G857" s="2"/>
       <c r="H857" s="2"/>
     </row>
-    <row r="858" spans="7:8">
+    <row r="858" spans="7:8" ht="12.5">
       <c r="G858" s="2"/>
       <c r="H858" s="2"/>
     </row>
-    <row r="859" spans="7:8">
+    <row r="859" spans="7:8" ht="12.5">
       <c r="G859" s="2"/>
       <c r="H859" s="2"/>
     </row>
-    <row r="860" spans="7:8">
+    <row r="860" spans="7:8" ht="12.5">
       <c r="G860" s="2"/>
       <c r="H860" s="2"/>
     </row>
-    <row r="861" spans="7:8">
+    <row r="861" spans="7:8" ht="12.5">
       <c r="G861" s="2"/>
       <c r="H861" s="2"/>
     </row>
-    <row r="862" spans="7:8">
+    <row r="862" spans="7:8" ht="12.5">
       <c r="G862" s="2"/>
       <c r="H862" s="2"/>
     </row>
-    <row r="863" spans="7:8">
+    <row r="863" spans="7:8" ht="12.5">
       <c r="G863" s="2"/>
       <c r="H863" s="2"/>
     </row>
-    <row r="864" spans="7:8">
+    <row r="864" spans="7:8" ht="12.5">
       <c r="G864" s="2"/>
       <c r="H864" s="2"/>
     </row>
-    <row r="865" spans="7:8">
+    <row r="865" spans="7:8" ht="12.5">
       <c r="G865" s="2"/>
       <c r="H865" s="2"/>
     </row>
-    <row r="866" spans="7:8">
+    <row r="866" spans="7:8" ht="12.5">
       <c r="G866" s="2"/>
       <c r="H866" s="2"/>
     </row>
-    <row r="867" spans="7:8">
+    <row r="867" spans="7:8" ht="12.5">
       <c r="G867" s="2"/>
       <c r="H867" s="2"/>
     </row>
-    <row r="868" spans="7:8">
+    <row r="868" spans="7:8" ht="12.5">
       <c r="G868" s="2"/>
       <c r="H868" s="2"/>
     </row>
-    <row r="869" spans="7:8">
+    <row r="869" spans="7:8" ht="12.5">
       <c r="G869" s="2"/>
       <c r="H869" s="2"/>
     </row>
-    <row r="870" spans="7:8">
+    <row r="870" spans="7:8" ht="12.5">
       <c r="G870" s="2"/>
       <c r="H870" s="2"/>
     </row>
-    <row r="871" spans="7:8">
+    <row r="871" spans="7:8" ht="12.5">
       <c r="G871" s="2"/>
       <c r="H871" s="2"/>
     </row>
-    <row r="872" spans="7:8">
+    <row r="872" spans="7:8" ht="12.5">
       <c r="G872" s="2"/>
       <c r="H872" s="2"/>
     </row>
-    <row r="873" spans="7:8">
+    <row r="873" spans="7:8" ht="12.5">
       <c r="G873" s="2"/>
       <c r="H873" s="2"/>
     </row>
-    <row r="874" spans="7:8">
+    <row r="874" spans="7:8" ht="12.5">
       <c r="G874" s="2"/>
       <c r="H874" s="2"/>
     </row>
-    <row r="875" spans="7:8">
+    <row r="875" spans="7:8" ht="12.5">
       <c r="G875" s="2"/>
       <c r="H875" s="2"/>
     </row>
-    <row r="876" spans="7:8">
+    <row r="876" spans="7:8" ht="12.5">
       <c r="G876" s="2"/>
       <c r="H876" s="2"/>
     </row>
-    <row r="877" spans="7:8">
+    <row r="877" spans="7:8" ht="12.5">
       <c r="G877" s="2"/>
       <c r="H877" s="2"/>
     </row>
-    <row r="878" spans="7:8">
+    <row r="878" spans="7:8" ht="12.5">
       <c r="G878" s="2"/>
       <c r="H878" s="2"/>
     </row>
-    <row r="879" spans="7:8">
+    <row r="879" spans="7:8" ht="12.5">
       <c r="G879" s="2"/>
       <c r="H879" s="2"/>
     </row>
-    <row r="880" spans="7:8">
+    <row r="880" spans="7:8" ht="12.5">
       <c r="G880" s="2"/>
       <c r="H880" s="2"/>
     </row>
-    <row r="881" spans="7:8">
+    <row r="881" spans="7:8" ht="12.5">
       <c r="G881" s="2"/>
       <c r="H881" s="2"/>
     </row>
-    <row r="882" spans="7:8">
+    <row r="882" spans="7:8" ht="12.5">
       <c r="G882" s="2"/>
       <c r="H882" s="2"/>
     </row>
-    <row r="883" spans="7:8">
+    <row r="883" spans="7:8" ht="12.5">
       <c r="G883" s="2"/>
       <c r="H883" s="2"/>
     </row>
-    <row r="884" spans="7:8">
+    <row r="884" spans="7:8" ht="12.5">
       <c r="G884" s="2"/>
       <c r="H884" s="2"/>
     </row>
-    <row r="885" spans="7:8">
+    <row r="885" spans="7:8" ht="12.5">
       <c r="G885" s="2"/>
       <c r="H885" s="2"/>
     </row>
-    <row r="886" spans="7:8">
+    <row r="886" spans="7:8" ht="12.5">
       <c r="G886" s="2"/>
       <c r="H886" s="2"/>
     </row>
-    <row r="887" spans="7:8">
+    <row r="887" spans="7:8" ht="12.5">
       <c r="G887" s="2"/>
       <c r="H887" s="2"/>
     </row>
-    <row r="888" spans="7:8">
+    <row r="888" spans="7:8" ht="12.5">
       <c r="G888" s="2"/>
       <c r="H888" s="2"/>
     </row>
-    <row r="889" spans="7:8">
+    <row r="889" spans="7:8" ht="12.5">
       <c r="G889" s="2"/>
       <c r="H889" s="2"/>
     </row>
-    <row r="890" spans="7:8">
+    <row r="890" spans="7:8" ht="12.5">
       <c r="G890" s="2"/>
       <c r="H890" s="2"/>
     </row>
-    <row r="891" spans="7:8">
+    <row r="891" spans="7:8" ht="12.5">
       <c r="G891" s="2"/>
       <c r="H891" s="2"/>
     </row>
-    <row r="892" spans="7:8">
+    <row r="892" spans="7:8" ht="12.5">
       <c r="G892" s="2"/>
       <c r="H892" s="2"/>
     </row>
-    <row r="893" spans="7:8">
+    <row r="893" spans="7:8" ht="12.5">
       <c r="G893" s="2"/>
       <c r="H893" s="2"/>
     </row>
-    <row r="894" spans="7:8">
+    <row r="894" spans="7:8" ht="12.5">
       <c r="G894" s="2"/>
       <c r="H894" s="2"/>
     </row>
-    <row r="895" spans="7:8">
+    <row r="895" spans="7:8" ht="12.5">
       <c r="G895" s="2"/>
       <c r="H895" s="2"/>
     </row>
-    <row r="896" spans="7:8">
+    <row r="896" spans="7:8" ht="12.5">
       <c r="G896" s="2"/>
       <c r="H896" s="2"/>
     </row>
-    <row r="897" spans="7:8">
+    <row r="897" spans="7:8" ht="12.5">
       <c r="G897" s="2"/>
       <c r="H897" s="2"/>
     </row>
-    <row r="898" spans="7:8">
+    <row r="898" spans="7:8" ht="12.5">
       <c r="G898" s="2"/>
       <c r="H898" s="2"/>
     </row>
-    <row r="899" spans="7:8">
+    <row r="899" spans="7:8" ht="12.5">
       <c r="G899" s="2"/>
       <c r="H899" s="2"/>
     </row>
-    <row r="900" spans="7:8">
+    <row r="900" spans="7:8" ht="12.5">
       <c r="G900" s="2"/>
       <c r="H900" s="2"/>
     </row>
-    <row r="901" spans="7:8">
+    <row r="901" spans="7:8" ht="12.5">
       <c r="G901" s="2"/>
       <c r="H901" s="2"/>
     </row>
-    <row r="902" spans="7:8">
+    <row r="902" spans="7:8" ht="12.5">
       <c r="G902" s="2"/>
       <c r="H902" s="2"/>
     </row>
-    <row r="903" spans="7:8">
+    <row r="903" spans="7:8" ht="12.5">
       <c r="G903" s="2"/>
       <c r="H903" s="2"/>
     </row>
-    <row r="904" spans="7:8">
+    <row r="904" spans="7:8" ht="12.5">
       <c r="G904" s="2"/>
       <c r="H904" s="2"/>
     </row>
-    <row r="905" spans="7:8">
+    <row r="905" spans="7:8" ht="12.5">
       <c r="G905" s="2"/>
       <c r="H905" s="2"/>
     </row>
-    <row r="906" spans="7:8">
+    <row r="906" spans="7:8" ht="12.5">
       <c r="G906" s="2"/>
       <c r="H906" s="2"/>
     </row>
-    <row r="907" spans="7:8">
+    <row r="907" spans="7:8" ht="12.5">
       <c r="G907" s="2"/>
       <c r="H907" s="2"/>
     </row>
-    <row r="908" spans="7:8">
+    <row r="908" spans="7:8" ht="12.5">
       <c r="G908" s="2"/>
       <c r="H908" s="2"/>
     </row>
-    <row r="909" spans="7:8">
+    <row r="909" spans="7:8" ht="12.5">
       <c r="G909" s="2"/>
       <c r="H909" s="2"/>
     </row>
-    <row r="910" spans="7:8">
+    <row r="910" spans="7:8" ht="12.5">
       <c r="G910" s="2"/>
       <c r="H910" s="2"/>
     </row>
-    <row r="911" spans="7:8">
+    <row r="911" spans="7:8" ht="12.5">
       <c r="G911" s="2"/>
       <c r="H911" s="2"/>
     </row>
-    <row r="912" spans="7:8">
+    <row r="912" spans="7:8" ht="12.5">
       <c r="G912" s="2"/>
       <c r="H912" s="2"/>
     </row>
-    <row r="913" spans="7:8">
+    <row r="913" spans="7:8" ht="12.5">
       <c r="G913" s="2"/>
       <c r="H913" s="2"/>
     </row>
-    <row r="914" spans="7:8">
+    <row r="914" spans="7:8" ht="12.5">
       <c r="G914" s="2"/>
       <c r="H914" s="2"/>
     </row>
-    <row r="915" spans="7:8">
+    <row r="915" spans="7:8" ht="12.5">
       <c r="G915" s="2"/>
       <c r="H915" s="2"/>
     </row>
-    <row r="916" spans="7:8">
+    <row r="916" spans="7:8" ht="12.5">
       <c r="G916" s="2"/>
       <c r="H916" s="2"/>
     </row>
-    <row r="917" spans="7:8">
+    <row r="917" spans="7:8" ht="12.5">
       <c r="G917" s="2"/>
       <c r="H917" s="2"/>
     </row>
-    <row r="918" spans="7:8">
+    <row r="918" spans="7:8" ht="12.5">
       <c r="G918" s="2"/>
       <c r="H918" s="2"/>
     </row>
-    <row r="919" spans="7:8">
+    <row r="919" spans="7:8" ht="12.5">
       <c r="G919" s="2"/>
       <c r="H919" s="2"/>
     </row>
-    <row r="920" spans="7:8">
+    <row r="920" spans="7:8" ht="12.5">
       <c r="G920" s="2"/>
       <c r="H920" s="2"/>
     </row>
-    <row r="921" spans="7:8">
+    <row r="921" spans="7:8" ht="12.5">
       <c r="G921" s="2"/>
       <c r="H921" s="2"/>
     </row>
-    <row r="922" spans="7:8">
+    <row r="922" spans="7:8" ht="12.5">
       <c r="G922" s="2"/>
       <c r="H922" s="2"/>
     </row>
-    <row r="923" spans="7:8">
+    <row r="923" spans="7:8" ht="12.5">
       <c r="G923" s="2"/>
       <c r="H923" s="2"/>
     </row>
-    <row r="924" spans="7:8">
+    <row r="924" spans="7:8" ht="12.5">
       <c r="G924" s="2"/>
       <c r="H924" s="2"/>
     </row>
-    <row r="925" spans="7:8">
+    <row r="925" spans="7:8" ht="12.5">
       <c r="G925" s="2"/>
       <c r="H925" s="2"/>
     </row>
-    <row r="926" spans="7:8">
+    <row r="926" spans="7:8" ht="12.5">
       <c r="G926" s="2"/>
       <c r="H926" s="2"/>
     </row>
-    <row r="927" spans="7:8">
+    <row r="927" spans="7:8" ht="12.5">
       <c r="G927" s="2"/>
       <c r="H927" s="2"/>
     </row>
-    <row r="928" spans="7:8">
+    <row r="928" spans="7:8" ht="12.5">
       <c r="G928" s="2"/>
       <c r="H928" s="2"/>
     </row>
-    <row r="929" spans="7:8">
+    <row r="929" spans="7:8" ht="12.5">
       <c r="G929" s="2"/>
       <c r="H929" s="2"/>
     </row>
-    <row r="930" spans="7:8">
+    <row r="930" spans="7:8" ht="12.5">
       <c r="G930" s="2"/>
       <c r="H930" s="2"/>
     </row>
-    <row r="931" spans="7:8">
+    <row r="931" spans="7:8" ht="12.5">
       <c r="G931" s="2"/>
       <c r="H931" s="2"/>
     </row>
-    <row r="932" spans="7:8">
+    <row r="932" spans="7:8" ht="12.5">
       <c r="G932" s="2"/>
       <c r="H932" s="2"/>
     </row>
-    <row r="933" spans="7:8">
+    <row r="933" spans="7:8" ht="12.5">
       <c r="G933" s="2"/>
       <c r="H933" s="2"/>
     </row>
-    <row r="934" spans="7:8">
+    <row r="934" spans="7:8" ht="12.5">
       <c r="G934" s="2"/>
       <c r="H934" s="2"/>
     </row>
-    <row r="935" spans="7:8">
+    <row r="935" spans="7:8" ht="12.5">
       <c r="G935" s="2"/>
       <c r="H935" s="2"/>
     </row>
-    <row r="936" spans="7:8">
+    <row r="936" spans="7:8" ht="12.5">
       <c r="G936" s="2"/>
       <c r="H936" s="2"/>
     </row>
-    <row r="937" spans="7:8">
+    <row r="937" spans="7:8" ht="12.5">
       <c r="G937" s="2"/>
       <c r="H937" s="2"/>
     </row>
-    <row r="938" spans="7:8">
+    <row r="938" spans="7:8" ht="12.5">
       <c r="G938" s="2"/>
       <c r="H938" s="2"/>
     </row>
-    <row r="939" spans="7:8">
+    <row r="939" spans="7:8" ht="12.5">
       <c r="G939" s="2"/>
       <c r="H939" s="2"/>
     </row>
-    <row r="940" spans="7:8">
+    <row r="940" spans="7:8" ht="12.5">
       <c r="G940" s="2"/>
       <c r="H940" s="2"/>
     </row>
-    <row r="941" spans="7:8">
+    <row r="941" spans="7:8" ht="12.5">
       <c r="G941" s="2"/>
       <c r="H941" s="2"/>
     </row>
-    <row r="942" spans="7:8">
+    <row r="942" spans="7:8" ht="12.5">
       <c r="G942" s="2"/>
       <c r="H942" s="2"/>
     </row>
-    <row r="943" spans="7:8">
+    <row r="943" spans="7:8" ht="12.5">
       <c r="G943" s="2"/>
       <c r="H943" s="2"/>
     </row>
-    <row r="944" spans="7:8">
+    <row r="944" spans="7:8" ht="12.5">
       <c r="G944" s="2"/>
       <c r="H944" s="2"/>
     </row>
-    <row r="945" spans="7:8">
+    <row r="945" spans="7:8" ht="12.5">
       <c r="G945" s="2"/>
       <c r="H945" s="2"/>
     </row>
-    <row r="946" spans="7:8">
+    <row r="946" spans="7:8" ht="12.5">
       <c r="G946" s="2"/>
       <c r="H946" s="2"/>
     </row>
-    <row r="947" spans="7:8">
+    <row r="947" spans="7:8" ht="12.5">
       <c r="G947" s="2"/>
       <c r="H947" s="2"/>
     </row>
-    <row r="948" spans="7:8">
+    <row r="948" spans="7:8" ht="12.5">
       <c r="G948" s="2"/>
       <c r="H948" s="2"/>
     </row>
-    <row r="949" spans="7:8">
+    <row r="949" spans="7:8" ht="12.5">
       <c r="G949" s="2"/>
       <c r="H949" s="2"/>
     </row>
-    <row r="950" spans="7:8">
+    <row r="950" spans="7:8" ht="12.5">
       <c r="G950" s="2"/>
       <c r="H950" s="2"/>
     </row>
-    <row r="951" spans="7:8">
+    <row r="951" spans="7:8" ht="12.5">
       <c r="G951" s="2"/>
       <c r="H951" s="2"/>
     </row>
-    <row r="952" spans="7:8">
+    <row r="952" spans="7:8" ht="12.5">
       <c r="G952" s="2"/>
       <c r="H952" s="2"/>
     </row>
-    <row r="953" spans="7:8">
+    <row r="953" spans="7:8" ht="12.5">
       <c r="G953" s="2"/>
       <c r="H953" s="2"/>
     </row>
-    <row r="954" spans="7:8">
+    <row r="954" spans="7:8" ht="12.5">
       <c r="G954" s="2"/>
       <c r="H954" s="2"/>
     </row>
-    <row r="955" spans="7:8">
+    <row r="955" spans="7:8" ht="12.5">
       <c r="G955" s="2"/>
       <c r="H955" s="2"/>
     </row>
-    <row r="956" spans="7:8">
+    <row r="956" spans="7:8" ht="12.5">
       <c r="G956" s="2"/>
       <c r="H956" s="2"/>
     </row>
-    <row r="957" spans="7:8">
+    <row r="957" spans="7:8" ht="12.5">
       <c r="G957" s="2"/>
       <c r="H957" s="2"/>
     </row>
-    <row r="958" spans="7:8">
+    <row r="958" spans="7:8" ht="12.5">
       <c r="G958" s="2"/>
       <c r="H958" s="2"/>
     </row>
-    <row r="959" spans="7:8">
+    <row r="959" spans="7:8" ht="12.5">
       <c r="G959" s="2"/>
       <c r="H959" s="2"/>
     </row>
-    <row r="960" spans="7:8">
+    <row r="960" spans="7:8" ht="12.5">
       <c r="G960" s="2"/>
       <c r="H960" s="2"/>
     </row>
-    <row r="961" spans="7:8">
+    <row r="961" spans="7:8" ht="12.5">
       <c r="G961" s="2"/>
       <c r="H961" s="2"/>
     </row>
-    <row r="962" spans="7:8">
+    <row r="962" spans="7:8" ht="12.5">
       <c r="G962" s="2"/>
       <c r="H962" s="2"/>
     </row>
-    <row r="963" spans="7:8">
+    <row r="963" spans="7:8" ht="12.5">
       <c r="G963" s="2"/>
       <c r="H963" s="2"/>
     </row>
-    <row r="964" spans="7:8">
+    <row r="964" spans="7:8" ht="12.5">
       <c r="G964" s="2"/>
       <c r="H964" s="2"/>
     </row>
-    <row r="965" spans="7:8">
+    <row r="965" spans="7:8" ht="12.5">
       <c r="G965" s="2"/>
       <c r="H965" s="2"/>
     </row>
-    <row r="966" spans="7:8">
+    <row r="966" spans="7:8" ht="12.5">
       <c r="G966" s="2"/>
       <c r="H966" s="2"/>
     </row>
-    <row r="967" spans="7:8">
+    <row r="967" spans="7:8" ht="12.5">
       <c r="G967" s="2"/>
       <c r="H967" s="2"/>
     </row>
-    <row r="968" spans="7:8">
+    <row r="968" spans="7:8" ht="12.5">
       <c r="G968" s="2"/>
       <c r="H968" s="2"/>
     </row>
-    <row r="969" spans="7:8">
+    <row r="969" spans="7:8" ht="12.5">
       <c r="G969" s="2"/>
       <c r="H969" s="2"/>
     </row>
-    <row r="970" spans="7:8">
+    <row r="970" spans="7:8" ht="12.5">
       <c r="G970" s="2"/>
       <c r="H970" s="2"/>
     </row>
-    <row r="971" spans="7:8">
+    <row r="971" spans="7:8" ht="12.5">
       <c r="G971" s="2"/>
       <c r="H971" s="2"/>
     </row>
-    <row r="972" spans="7:8">
+    <row r="972" spans="7:8" ht="12.5">
       <c r="G972" s="2"/>
       <c r="H972" s="2"/>
     </row>
-    <row r="973" spans="7:8">
+    <row r="973" spans="7:8" ht="12.5">
       <c r="G973" s="2"/>
       <c r="H973" s="2"/>
     </row>
-    <row r="974" spans="7:8">
+    <row r="974" spans="7:8" ht="12.5">
       <c r="G974" s="2"/>
       <c r="H974" s="2"/>
     </row>
-    <row r="975" spans="7:8">
+    <row r="975" spans="7:8" ht="12.5">
       <c r="G975" s="2"/>
       <c r="H975" s="2"/>
     </row>
-    <row r="976" spans="7:8">
+    <row r="976" spans="7:8" ht="12.5">
       <c r="G976" s="2"/>
       <c r="H976" s="2"/>
     </row>
-    <row r="977" spans="7:8">
+    <row r="977" spans="7:8" ht="12.5">
       <c r="G977" s="2"/>
       <c r="H977" s="2"/>
     </row>
-    <row r="978" spans="7:8">
+    <row r="978" spans="7:8" ht="12.5">
       <c r="G978" s="2"/>
       <c r="H978" s="2"/>
     </row>
-    <row r="979" spans="7:8">
+    <row r="979" spans="7:8" ht="12.5">
       <c r="G979" s="2"/>
       <c r="H979" s="2"/>
     </row>
-    <row r="980" spans="7:8">
+    <row r="980" spans="7:8" ht="12.5">
       <c r="G980" s="2"/>
       <c r="H980" s="2"/>
     </row>
-    <row r="981" spans="7:8">
+    <row r="981" spans="7:8" ht="12.5">
       <c r="G981" s="2"/>
       <c r="H981" s="2"/>
     </row>
-    <row r="982" spans="7:8">
+    <row r="982" spans="7:8" ht="12.5">
       <c r="G982" s="2"/>
       <c r="H982" s="2"/>
     </row>
-    <row r="983" spans="7:8">
+    <row r="983" spans="7:8" ht="12.5">
       <c r="G983" s="2"/>
       <c r="H983" s="2"/>
     </row>
-    <row r="984" spans="7:8">
+    <row r="984" spans="7:8" ht="12.5">
       <c r="G984" s="2"/>
       <c r="H984" s="2"/>
     </row>
-    <row r="985" spans="7:8">
+    <row r="985" spans="7:8" ht="12.5">
       <c r="G985" s="2"/>
       <c r="H985" s="2"/>
     </row>
-    <row r="986" spans="7:8">
+    <row r="986" spans="7:8" ht="12.5">
       <c r="G986" s="2"/>
       <c r="H986" s="2"/>
     </row>
-    <row r="987" spans="7:8">
+    <row r="987" spans="7:8" ht="12.5">
       <c r="G987" s="2"/>
       <c r="H987" s="2"/>
     </row>
-    <row r="988" spans="7:8">
+    <row r="988" spans="7:8" ht="12.5">
       <c r="G988" s="2"/>
       <c r="H988" s="2"/>
     </row>
-    <row r="989" spans="7:8">
+    <row r="989" spans="7:8" ht="12.5">
       <c r="G989" s="2"/>
       <c r="H989" s="2"/>
     </row>
-    <row r="990" spans="7:8">
+    <row r="990" spans="7:8" ht="12.5">
       <c r="G990" s="2"/>
       <c r="H990" s="2"/>
     </row>
-    <row r="991" spans="7:8">
+    <row r="991" spans="7:8" ht="12.5">
       <c r="G991" s="2"/>
       <c r="H991" s="2"/>
     </row>
-    <row r="992" spans="7:8">
+    <row r="992" spans="7:8" ht="12.5">
       <c r="G992" s="2"/>
       <c r="H992" s="2"/>
     </row>
-    <row r="993" spans="7:8">
+    <row r="993" spans="7:8" ht="12.5">
       <c r="G993" s="2"/>
       <c r="H993" s="2"/>
     </row>
-    <row r="994" spans="7:8">
+    <row r="994" spans="7:8" ht="12.5">
       <c r="G994" s="2"/>
       <c r="H994" s="2"/>
     </row>
-    <row r="995" spans="7:8">
+    <row r="995" spans="7:8" ht="12.5">
       <c r="G995" s="2"/>
       <c r="H995" s="2"/>
     </row>
-    <row r="996" spans="7:8">
+    <row r="996" spans="7:8" ht="12.5">
       <c r="G996" s="2"/>
       <c r="H996" s="2"/>
     </row>
-    <row r="997" spans="7:8">
+    <row r="997" spans="7:8" ht="12.5">
       <c r="G997" s="2"/>
       <c r="H997" s="2"/>
     </row>
-    <row r="998" spans="7:8">
+    <row r="998" spans="7:8" ht="12.5">
       <c r="G998" s="2"/>
       <c r="H998" s="2"/>
     </row>
-    <row r="999" spans="7:8">
+    <row r="999" spans="7:8" ht="12.5">
       <c r="G999" s="2"/>
       <c r="H999" s="2"/>
     </row>
-    <row r="1000" spans="7:8">
+    <row r="1000" spans="7:8" ht="12.5">
       <c r="G1000" s="2"/>
       <c r="H1000" s="2"/>
     </row>
